--- a/analysis(S4)/tables/level2_agent_network_analysis.xlsx
+++ b/analysis(S4)/tables/level2_agent_network_analysis.xlsx
@@ -131,13 +131,13 @@
     <t>level2_core_no_article_count</t>
   </si>
   <si>
-    <t>level2_mechanism_centrality</t>
-  </si>
-  <si>
-    <t>level2_mechanism_repeat_exposure</t>
-  </si>
-  <si>
-    <t>level2_mechanism_network_composition</t>
+    <t>level2_descriptor_centrality</t>
+  </si>
+  <si>
+    <t>level2_descriptor_repeat_exposure</t>
+  </si>
+  <si>
+    <t>level2_descriptor_network_composition</t>
   </si>
   <si>
     <t>ols</t>
@@ -260,7 +260,7 @@
     <t>status</t>
   </si>
   <si>
-    <t>level2_mechanism_predictors</t>
+    <t>level2_descriptor_variables</t>
   </si>
   <si>
     <t>log_article_count_per_agent, agent_deg_centrality_mean, avg_out_degree_centrality_mean, repeat_exposure_1st_nodes_pct, repeat_exposure_2nd_nodes_pct, gender_assortativity_mean</t>

--- a/analysis(S4)/tables/level2_agent_network_analysis.xlsx
+++ b/analysis(S4)/tables/level2_agent_network_analysis.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="93">
   <si>
     <t>variable</t>
   </si>
@@ -68,6 +68,27 @@
     <t>structural_virality_mean</t>
   </si>
   <si>
+    <t>wiener_index_mean</t>
+  </si>
+  <si>
+    <t>centrality_mean</t>
+  </si>
+  <si>
+    <t>agent_deg_centrality_mean</t>
+  </si>
+  <si>
+    <t>avg_out_degree_centrality_mean</t>
+  </si>
+  <si>
+    <t>repeat_exposure_1st_nodes_pct</t>
+  </si>
+  <si>
+    <t>repeat_exposure_2nd_nodes_pct</t>
+  </si>
+  <si>
+    <t>gender_assortativity_mean</t>
+  </si>
+  <si>
     <t>duration_mean_of_means</t>
   </si>
   <si>
@@ -131,15 +152,6 @@
     <t>level2_core_no_article_count</t>
   </si>
   <si>
-    <t>level2_descriptor_centrality</t>
-  </si>
-  <si>
-    <t>level2_descriptor_repeat_exposure</t>
-  </si>
-  <si>
-    <t>level2_descriptor_network_composition</t>
-  </si>
-  <si>
     <t>ols</t>
   </si>
   <si>
@@ -158,6 +170,27 @@
     <t>structural_virality_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
   </si>
   <si>
+    <t>wiener_index_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>centrality_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>agent_deg_centrality_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>avg_out_degree_centrality_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>repeat_exposure_1st_nodes_pct ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>repeat_exposure_2nd_nodes_pct ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>gender_assortativity_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
     <t>duration_mean_of_means ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
   </si>
   <si>
@@ -176,18 +209,30 @@
     <t>structural_virality_mean ~ C(JobCategory) + C(agent_gender)</t>
   </si>
   <si>
+    <t>wiener_index_mean ~ C(JobCategory) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>centrality_mean ~ C(JobCategory) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>agent_deg_centrality_mean ~ C(JobCategory) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>avg_out_degree_centrality_mean ~ C(JobCategory) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>repeat_exposure_1st_nodes_pct ~ C(JobCategory) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>repeat_exposure_2nd_nodes_pct ~ C(JobCategory) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>gender_assortativity_mean ~ C(JobCategory) + C(agent_gender)</t>
+  </si>
+  <si>
     <t>duration_mean_of_means ~ C(JobCategory) + C(agent_gender)</t>
   </si>
   <si>
-    <t>log_agent_cascade_size_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent + z_agent_deg_centrality_mean + z_avg_out_degree_centrality_mean</t>
-  </si>
-  <si>
-    <t>log_agent_cascade_size_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent + z_repeat_exposure_1st_nodes_pct + z_repeat_exposure_2nd_nodes_pct</t>
-  </si>
-  <si>
-    <t>log_agent_cascade_size_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent + z_gender_assortativity_mean</t>
-  </si>
-  <si>
     <t>term</t>
   </si>
   <si>
@@ -230,21 +275,6 @@
     <t>z_log_article_count_per_agent</t>
   </si>
   <si>
-    <t>z_agent_deg_centrality_mean</t>
-  </si>
-  <si>
-    <t>z_avg_out_degree_centrality_mean</t>
-  </si>
-  <si>
-    <t>z_repeat_exposure_1st_nodes_pct</t>
-  </si>
-  <si>
-    <t>z_repeat_exposure_2nd_nodes_pct</t>
-  </si>
-  <si>
-    <t>z_gender_assortativity_mean</t>
-  </si>
-  <si>
     <t>diagnostic</t>
   </si>
   <si>
@@ -260,7 +290,7 @@
     <t>status</t>
   </si>
   <si>
-    <t>level2_descriptor_variables</t>
+    <t>level2_supplementary_outcome_dimensions</t>
   </si>
   <si>
     <t>log_article_count_per_agent, agent_deg_centrality_mean, avg_out_degree_centrality_mean, repeat_exposure_1st_nodes_pct, repeat_exposure_2nd_nodes_pct, gender_assortativity_mean</t>
@@ -598,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="11" width="12.7109375" customWidth="1"/>
@@ -822,10 +852,10 @@
         <v>592</v>
       </c>
       <c r="C7">
-        <v>1580.223627031909</v>
+        <v>114511.6372330066</v>
       </c>
       <c r="D7">
-        <v>8660.374944433901</v>
+        <v>1325707.132991847</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -834,19 +864,19 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>393.354301948052</v>
+        <v>48.49999999999999</v>
       </c>
       <c r="H7">
-        <v>616.6726915261116</v>
+        <v>326.0595238095238</v>
       </c>
       <c r="I7">
-        <v>1017.635605355392</v>
+        <v>1706.944852941176</v>
       </c>
       <c r="J7">
-        <v>13888.24362729939</v>
+        <v>487929.7740000038</v>
       </c>
       <c r="K7">
-        <v>183600</v>
+        <v>23074266.33333333</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -857,31 +887,31 @@
         <v>592</v>
       </c>
       <c r="C8">
-        <v>11.07601351351351</v>
+        <v>0.7104352922378984</v>
       </c>
       <c r="D8">
-        <v>18.26425592944677</v>
+        <v>0.2912848965353282</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>0.5261450155670289</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>0.7434425398362245</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>0.9089186373496665</v>
       </c>
       <c r="J8">
-        <v>106.09</v>
+        <v>1.337069696969698</v>
       </c>
       <c r="K8">
-        <v>131</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -892,30 +922,275 @@
         <v>592</v>
       </c>
       <c r="C9">
+        <v>0.610083434151328</v>
+      </c>
+      <c r="D9">
+        <v>0.2346699843034141</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0.4734376581229107</v>
+      </c>
+      <c r="H9">
+        <v>0.6437604515050167</v>
+      </c>
+      <c r="I9">
+        <v>0.7846520146520147</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>592</v>
+      </c>
+      <c r="C10">
+        <v>0.1040713395438377</v>
+      </c>
+      <c r="D10">
+        <v>0.07294262327189995</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0.05504336983449293</v>
+      </c>
+      <c r="H10">
+        <v>0.08854757539186345</v>
+      </c>
+      <c r="I10">
+        <v>0.1382198686689618</v>
+      </c>
+      <c r="J10">
+        <v>0.345760442773601</v>
+      </c>
+      <c r="K10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>592</v>
+      </c>
+      <c r="C11">
+        <v>0.3118984746963827</v>
+      </c>
+      <c r="D11">
+        <v>0.3902773561730213</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0.02644521791767554</v>
+      </c>
+      <c r="H11">
+        <v>0.1165857605177993</v>
+      </c>
+      <c r="I11">
+        <v>0.4105722154222767</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>592</v>
+      </c>
+      <c r="C12">
+        <v>0.1594799952425974</v>
+      </c>
+      <c r="D12">
+        <v>0.3416236835408861</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0.0625</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>592</v>
+      </c>
+      <c r="C13">
+        <v>-0.0673092124051768</v>
+      </c>
+      <c r="D13">
+        <v>0.05235748834219615</v>
+      </c>
+      <c r="E13">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="F13">
+        <v>-0.2126930815897366</v>
+      </c>
+      <c r="G13">
+        <v>-0.09348976950718174</v>
+      </c>
+      <c r="H13">
+        <v>-0.06479872095406181</v>
+      </c>
+      <c r="I13">
+        <v>-0.03178522957843647</v>
+      </c>
+      <c r="J13">
+        <v>0.03889847188318172</v>
+      </c>
+      <c r="K13">
+        <v>0.06314409677611554</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <v>592</v>
+      </c>
+      <c r="C14">
+        <v>1580.223627031909</v>
+      </c>
+      <c r="D14">
+        <v>8660.374944433901</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>393.354301948052</v>
+      </c>
+      <c r="H14">
+        <v>616.6726915261116</v>
+      </c>
+      <c r="I14">
+        <v>1017.635605355392</v>
+      </c>
+      <c r="J14">
+        <v>13888.24362729939</v>
+      </c>
+      <c r="K14">
+        <v>183600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>592</v>
+      </c>
+      <c r="C15">
+        <v>11.07601351351351</v>
+      </c>
+      <c r="D15">
+        <v>18.26425592944677</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <v>106.09</v>
+      </c>
+      <c r="K15">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>592</v>
+      </c>
+      <c r="C16">
         <v>1.995905485963873</v>
       </c>
-      <c r="D9">
+      <c r="D16">
         <v>0.8646063785398878</v>
       </c>
-      <c r="E9">
+      <c r="E16">
         <v>0.6931471805599453</v>
       </c>
-      <c r="F9">
+      <c r="F16">
         <v>0.6931471805599453</v>
       </c>
-      <c r="G9">
+      <c r="G16">
         <v>1.386294361119891</v>
       </c>
-      <c r="H9">
+      <c r="H16">
         <v>1.791759469228055</v>
       </c>
-      <c r="I9">
+      <c r="I16">
         <v>2.397895272798371</v>
       </c>
-      <c r="J9">
+      <c r="J16">
         <v>4.673666049801515</v>
       </c>
-      <c r="K9">
+      <c r="K16">
         <v>4.882801922586371</v>
       </c>
     </row>
@@ -935,15 +1210,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>400</v>
@@ -951,7 +1226,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>69</v>
@@ -959,7 +1234,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>62</v>
@@ -967,7 +1242,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>60</v>
@@ -975,7 +1250,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -988,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="12.7109375" customWidth="1"/>
@@ -996,42 +1271,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>592</v>
@@ -1046,18 +1321,18 @@
         <v>0.1879215395098323</v>
       </c>
       <c r="I2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D3">
         <v>592</v>
@@ -1072,18 +1347,18 @@
         <v>0.02624373600031182</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>592</v>
@@ -1098,18 +1373,18 @@
         <v>0.1174013120892701</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>592</v>
@@ -1124,18 +1399,18 @@
         <v>0.2402500083892802</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D6">
         <v>592</v>
@@ -1150,267 +1425,553 @@
         <v>0.07325759903729168</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D7">
         <v>592</v>
       </c>
       <c r="E7">
-        <v>12411.87220504295</v>
+        <v>18379.56213881192</v>
       </c>
       <c r="F7">
-        <v>12442.55675148713</v>
+        <v>18410.24668525611</v>
       </c>
       <c r="G7">
-        <v>0.01651921089452346</v>
+        <v>-0.002015647558125444</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D8">
         <v>592</v>
       </c>
       <c r="E8">
-        <v>1704.097495534252</v>
+        <v>135.0932468713695</v>
       </c>
       <c r="F8">
-        <v>1730.398535343556</v>
+        <v>165.7777933155575</v>
       </c>
       <c r="G8">
-        <v>0.1567801877439871</v>
+        <v>0.143178738853398</v>
       </c>
       <c r="I8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D9">
         <v>592</v>
       </c>
       <c r="E9">
-        <v>-1284.046234719973</v>
+        <v>-133.7510497451565</v>
       </c>
       <c r="F9">
-        <v>-1257.745194910669</v>
+        <v>-103.0665033009684</v>
       </c>
       <c r="G9">
-        <v>0.02263028852656712</v>
+        <v>0.1617271265036677</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>592</v>
       </c>
       <c r="E10">
-        <v>1668.583946409904</v>
+        <v>-1466.477954215737</v>
       </c>
       <c r="F10">
-        <v>1694.884986219208</v>
+        <v>-1435.793407771549</v>
       </c>
       <c r="G10">
-        <v>0.1187368925429509</v>
+        <v>0.08664018570785981</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D11">
         <v>592</v>
       </c>
       <c r="E11">
-        <v>4726.502551324539</v>
+        <v>287.9345728706755</v>
       </c>
       <c r="F11">
-        <v>4752.803591133843</v>
+        <v>318.6191193148636</v>
       </c>
       <c r="G11">
-        <v>0.2415464560030287</v>
+        <v>0.3821191959473504</v>
       </c>
       <c r="I11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D12">
         <v>592</v>
       </c>
       <c r="E12">
-        <v>1146.734311028757</v>
+        <v>316.6192648373155</v>
       </c>
       <c r="F12">
-        <v>1173.035350838062</v>
+        <v>347.3038112815036</v>
       </c>
       <c r="G12">
-        <v>0.06725628703558473</v>
+        <v>0.1535550496771568</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D13">
         <v>592</v>
       </c>
       <c r="E13">
-        <v>12410.27141954738</v>
+        <v>-1855.070009385509</v>
       </c>
       <c r="F13">
-        <v>12436.57245935668</v>
+        <v>-1824.385462941321</v>
       </c>
       <c r="G13">
-        <v>0.01753520511231776</v>
+        <v>0.0804533629656693</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D14">
         <v>592</v>
       </c>
       <c r="E14">
-        <v>1551.781598299493</v>
+        <v>12411.87220504295</v>
       </c>
       <c r="F14">
-        <v>1591.233158013449</v>
+        <v>12442.55675148713</v>
       </c>
       <c r="G14">
-        <v>0.3513230836168076</v>
+        <v>0.01651921089452346</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D15">
         <v>592</v>
       </c>
       <c r="E15">
-        <v>1629.249382277164</v>
+        <v>1704.097495534252</v>
       </c>
       <c r="F15">
-        <v>1668.70094199112</v>
+        <v>1730.398535343556</v>
       </c>
       <c r="G15">
-        <v>0.2606344021038742</v>
+        <v>0.1567801877439871</v>
       </c>
       <c r="I15" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D16">
         <v>592</v>
       </c>
       <c r="E16">
-        <v>1681.460643277031</v>
+        <v>-1284.046234719973</v>
       </c>
       <c r="F16">
-        <v>1716.528696356103</v>
+        <v>-1257.745194910669</v>
       </c>
       <c r="G16">
-        <v>0.1911190106434428</v>
+        <v>0.02263028852656712</v>
       </c>
       <c r="I16" t="s">
-        <v>55</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17">
+        <v>592</v>
+      </c>
+      <c r="E17">
+        <v>1668.583946409904</v>
+      </c>
+      <c r="F17">
+        <v>1694.884986219208</v>
+      </c>
+      <c r="G17">
+        <v>0.1187368925429509</v>
+      </c>
+      <c r="I17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18">
+        <v>592</v>
+      </c>
+      <c r="E18">
+        <v>4726.502551324539</v>
+      </c>
+      <c r="F18">
+        <v>4752.803591133843</v>
+      </c>
+      <c r="G18">
+        <v>0.2415464560030287</v>
+      </c>
+      <c r="I18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19">
+        <v>592</v>
+      </c>
+      <c r="E19">
+        <v>1146.734311028757</v>
+      </c>
+      <c r="F19">
+        <v>1173.035350838062</v>
+      </c>
+      <c r="G19">
+        <v>0.06725628703558473</v>
+      </c>
+      <c r="I19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20">
+        <v>592</v>
+      </c>
+      <c r="E20">
+        <v>18377.64196954389</v>
+      </c>
+      <c r="F20">
+        <v>18403.9430093532</v>
+      </c>
+      <c r="G20">
+        <v>-0.0004406227761815096</v>
+      </c>
+      <c r="I20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21">
+        <v>592</v>
+      </c>
+      <c r="E21">
+        <v>148.6850518228562</v>
+      </c>
+      <c r="F21">
+        <v>174.9860916321602</v>
+      </c>
+      <c r="G21">
+        <v>0.121813575713323</v>
+      </c>
+      <c r="I21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22">
+        <v>592</v>
+      </c>
+      <c r="E22">
+        <v>-111.8379388847816</v>
+      </c>
+      <c r="F22">
+        <v>-85.53689907547755</v>
+      </c>
+      <c r="G22">
+        <v>0.12866240351921</v>
+      </c>
+      <c r="I22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23">
+        <v>592</v>
+      </c>
+      <c r="E23">
+        <v>-1461.616772264873</v>
+      </c>
+      <c r="F23">
+        <v>-1435.315732455569</v>
+      </c>
+      <c r="G23">
+        <v>0.0775697197668922</v>
+      </c>
+      <c r="I23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24">
+        <v>592</v>
+      </c>
+      <c r="E24">
+        <v>552.4223784124376</v>
+      </c>
+      <c r="F24">
+        <v>578.7234182217417</v>
+      </c>
+      <c r="G24">
+        <v>0.03248014855708414</v>
+      </c>
+      <c r="I24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25">
+        <v>592</v>
+      </c>
+      <c r="E25">
+        <v>406.4485505008395</v>
+      </c>
+      <c r="F25">
+        <v>432.7495903101435</v>
+      </c>
+      <c r="G25">
+        <v>0.0132129497441057</v>
+      </c>
+      <c r="I25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26">
+        <v>592</v>
+      </c>
+      <c r="E26">
+        <v>-1851.736413295326</v>
+      </c>
+      <c r="F26">
+        <v>-1825.435373486022</v>
+      </c>
+      <c r="G26">
+        <v>0.0737147123043056</v>
+      </c>
+      <c r="I26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27">
+        <v>592</v>
+      </c>
+      <c r="E27">
+        <v>12410.27141954738</v>
+      </c>
+      <c r="F27">
+        <v>12436.57245935668</v>
+      </c>
+      <c r="G27">
+        <v>0.01753520511231776</v>
+      </c>
+      <c r="I27" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="12.7109375" customWidth="1"/>
@@ -1429,48 +1990,48 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>2.581554485848208</v>
@@ -1490,16 +2051,16 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E3">
         <v>1.436155757853252</v>
@@ -1519,16 +2080,16 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E4">
         <v>-0.1752569525442766</v>
@@ -1548,16 +2109,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E5">
         <v>0.02604499294026585</v>
@@ -1577,16 +2138,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E6">
         <v>0.1041268872209697</v>
@@ -1606,16 +2167,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>-0.1157206030890144</v>
@@ -1635,16 +2196,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>0.2159646841937136</v>
@@ -1667,16 +2228,16 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E9">
         <v>0.1135080265542597</v>
@@ -1696,16 +2257,16 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E10">
         <v>0.005808476058976752</v>
@@ -1725,16 +2286,16 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>-0.04449582851830746</v>
@@ -1754,16 +2315,16 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E12">
         <v>-0.02605155174812224</v>
@@ -1783,16 +2344,16 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E13">
         <v>-0.04054193484077751</v>
@@ -1812,16 +2373,16 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E14">
         <v>0.009030108174118772</v>
@@ -1841,16 +2402,16 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E15">
         <v>-0.006475280580781555</v>
@@ -1873,16 +2434,16 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E16">
         <v>1.809111659956468</v>
@@ -1902,16 +2463,16 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E17">
         <v>0.982930583597903</v>
@@ -1931,16 +2492,16 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E18">
         <v>-0.3641120961743143</v>
@@ -1960,16 +2521,16 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E19">
         <v>-0.2326640363730444</v>
@@ -1989,16 +2550,16 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E20">
         <v>-0.2080371525167505</v>
@@ -2018,16 +2579,16 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E21">
         <v>-0.005654401352396664</v>
@@ -2047,16 +2608,16 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E22">
         <v>0.01484534470383334</v>
@@ -2079,16 +2640,16 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E23">
         <v>5.555179445128314</v>
@@ -2108,16 +2669,16 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E24">
         <v>22.7653808121892</v>
@@ -2137,16 +2698,16 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E25">
         <v>-3.650547796457277</v>
@@ -2166,16 +2727,16 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E26">
         <v>-1.604761416427841</v>
@@ -2195,16 +2756,16 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E27">
         <v>-1.182119877387055</v>
@@ -2224,16 +2785,16 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E28">
         <v>0.5199145452824512</v>
@@ -2253,16 +2814,16 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E29">
         <v>-0.003770545471494469</v>
@@ -2285,16 +2846,16 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E30">
         <v>1.776708439799271</v>
@@ -2314,16 +2875,16 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E31">
         <v>0.4771734174308322</v>
@@ -2343,16 +2904,16 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E32">
         <v>-0.1084186575223765</v>
@@ -2372,16 +2933,16 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E33">
         <v>-0.1015786929438795</v>
@@ -2401,16 +2962,16 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E34">
         <v>0.003519269899969979</v>
@@ -2430,16 +2991,16 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E35">
         <v>-0.06239983100885005</v>
@@ -2459,16 +3020,16 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E36">
         <v>0.06191857209475883</v>
@@ -2491,2030 +3052,3912 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E37">
-        <v>1545.242123982607</v>
+        <v>-102827.1851616676</v>
       </c>
       <c r="F37">
-        <v>65755.32010664341</v>
+        <v>5136968.056213175</v>
       </c>
       <c r="G37">
-        <v>0.9812515343012286</v>
+        <v>0.9840297342843385</v>
       </c>
       <c r="H37">
-        <v>-127332.8170769409</v>
+        <v>-10171099.56507222</v>
       </c>
       <c r="I37">
-        <v>130423.3013249062</v>
+        <v>9965445.194748884</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E38">
-        <v>4292.510035215521</v>
+        <v>481427.2835337015</v>
       </c>
       <c r="F38">
-        <v>65803.86155861642</v>
+        <v>5142903.629850134</v>
       </c>
       <c r="G38">
-        <v>0.9479893733486578</v>
+        <v>0.9254189541031496</v>
       </c>
       <c r="H38">
-        <v>-124680.6886633324</v>
+        <v>-9598478.606932875</v>
       </c>
       <c r="I38">
-        <v>133265.7087337635</v>
+        <v>10561333.17400028</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E39">
-        <v>-715.4455176357422</v>
+        <v>55003.06184529857</v>
       </c>
       <c r="F39">
-        <v>65760.94959776412</v>
+        <v>5136213.467865487</v>
       </c>
       <c r="G39">
-        <v>0.991319595061072</v>
+        <v>0.9914557182401269</v>
       </c>
       <c r="H39">
-        <v>-129604.5383184072</v>
+        <v>-10011790.35208063</v>
       </c>
       <c r="I39">
-        <v>128173.6472831357</v>
+        <v>10121796.47577123</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E40">
-        <v>-252.2710765379041</v>
+        <v>157694.8357359517</v>
       </c>
       <c r="F40">
-        <v>65755.6884536649</v>
+        <v>5137036.535599635</v>
       </c>
       <c r="G40">
-        <v>0.99693893094162</v>
+        <v>0.9755106829871953</v>
       </c>
       <c r="H40">
-        <v>-129131.0522243574</v>
+        <v>-9910711.761305744</v>
       </c>
       <c r="I40">
-        <v>128626.5100712816</v>
+        <v>10226101.43277765</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E41">
-        <v>170.1991345541716</v>
+        <v>57717.2396474963</v>
       </c>
       <c r="F41">
-        <v>65752.50134401995</v>
+        <v>5136284.839304442</v>
       </c>
       <c r="G41">
-        <v>0.9979346928664422</v>
+        <v>0.9910342345333821</v>
       </c>
       <c r="H41">
-        <v>-128702.3353931464</v>
+        <v>-10009216.05972831</v>
       </c>
       <c r="I41">
-        <v>129042.7336622548</v>
+        <v>10124650.5390233</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E42">
-        <v>-269.0605205296978</v>
+        <v>76323.78172176723</v>
       </c>
       <c r="F42">
-        <v>586.3669207870287</v>
+        <v>98354.75623228958</v>
       </c>
       <c r="G42">
-        <v>0.646334465632133</v>
+        <v>0.4377460389810169</v>
       </c>
       <c r="H42">
-        <v>-1418.318566997925</v>
+        <v>-116447.9982017368</v>
       </c>
       <c r="I42">
-        <v>880.197525938529</v>
+        <v>269095.5616452713</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E43">
-        <v>-241.353436703274</v>
+        <v>16674.08522827138</v>
       </c>
       <c r="F43">
-        <v>505.4224382132981</v>
+        <v>16636.12038859932</v>
       </c>
       <c r="G43">
-        <v>0.6329860878312678</v>
+        <v>0.316207378339653</v>
       </c>
       <c r="H43">
-        <v>-1231.963212579759</v>
+        <v>-15932.11157585578</v>
       </c>
       <c r="I43">
-        <v>749.256339173211</v>
+        <v>49280.28203239854</v>
       </c>
       <c r="J43">
-        <v>-241.353436703274</v>
+        <v>16674.08522827138</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E44">
-        <v>2.944196898961016</v>
+        <v>0.5800381206477045</v>
       </c>
       <c r="F44">
-        <v>6.476725308627175</v>
+        <v>3.105397551453294</v>
       </c>
       <c r="G44">
-        <v>0.6494106362271979</v>
+        <v>0.8518301073234911</v>
       </c>
       <c r="H44">
-        <v>-9.749951443707314</v>
+        <v>-5.506429237879621</v>
       </c>
       <c r="I44">
-        <v>15.63834524162935</v>
+        <v>6.666505479175029</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E45">
-        <v>1.048793694320441</v>
+        <v>-0.1493253721405085</v>
       </c>
       <c r="F45">
-        <v>6.47912814584881</v>
+        <v>3.10547608071022</v>
       </c>
       <c r="G45">
-        <v>0.8714061345991726</v>
+        <v>0.9616488715267716</v>
       </c>
       <c r="H45">
-        <v>-11.650064122763</v>
+        <v>-6.235946645183142</v>
       </c>
       <c r="I45">
-        <v>13.74765151140389</v>
+        <v>5.937295900902124</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E46">
-        <v>-0.653521883171244</v>
+        <v>0.2056800663871909</v>
       </c>
       <c r="F46">
-        <v>6.477001489548555</v>
+        <v>3.105597999172989</v>
       </c>
       <c r="G46">
-        <v>0.9196307705499716</v>
+        <v>0.9471956583758823</v>
       </c>
       <c r="H46">
-        <v>-13.34821153049869</v>
+        <v>-5.881180162451519</v>
       </c>
       <c r="I46">
-        <v>12.04116776415621</v>
+        <v>6.292540295225901</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E47">
-        <v>-0.3418603726593014</v>
+        <v>0.1524124546691054</v>
       </c>
       <c r="F47">
-        <v>6.476471094116025</v>
+        <v>3.105333279061516</v>
       </c>
       <c r="G47">
-        <v>0.9579032320556015</v>
+        <v>0.9608548496655319</v>
       </c>
       <c r="H47">
-        <v>-13.03551046404143</v>
+        <v>-5.933928932285136</v>
       </c>
       <c r="I47">
-        <v>12.35178971872283</v>
+        <v>6.238753841623346</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E48">
-        <v>-0.04318746933618201</v>
+        <v>0.217273779128076</v>
       </c>
       <c r="F48">
-        <v>6.477446583347024</v>
+        <v>3.105417796489343</v>
       </c>
       <c r="G48">
-        <v>0.9946802556748717</v>
+        <v>0.9442206912277334</v>
       </c>
       <c r="H48">
-        <v>-12.73874948447837</v>
+        <v>-5.869233258940771</v>
       </c>
       <c r="I48">
-        <v>12.65237454580601</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>6.303780817196923</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E49">
-        <v>-0.1273438380100369</v>
+        <v>-0.006652054254323341</v>
       </c>
       <c r="F49">
-        <v>0.08323244266282433</v>
+        <v>0.02245545438087213</v>
       </c>
       <c r="G49">
-        <v>0.1260220798612615</v>
+        <v>0.7670518891367741</v>
       </c>
       <c r="H49">
-        <v>-0.2904764279744676</v>
+        <v>-0.05066393609731489</v>
       </c>
       <c r="I49">
-        <v>0.03578875195439388</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>0.03735982758866821</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="E50">
-        <v>0.1026348998476229</v>
+        <v>0.04765786585252259</v>
       </c>
       <c r="F50">
-        <v>1.413707206249518</v>
+        <v>0.01227265075143458</v>
       </c>
       <c r="G50">
-        <v>0.9421245636916359</v>
+        <v>0.0001030662221191778</v>
       </c>
       <c r="H50">
-        <v>-2.668180309086171</v>
+        <v>0.02360391238487237</v>
       </c>
       <c r="I50">
-        <v>2.873450108781417</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>0.0717118193201728</v>
+      </c>
+      <c r="J50">
+        <v>0.04765786585252259</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E51">
-        <v>0.01742277335526768</v>
+        <v>0.4422665439596587</v>
       </c>
       <c r="F51">
-        <v>1.413728409464971</v>
+        <v>1.57912835493748</v>
       </c>
       <c r="G51">
-        <v>0.9901671283606914</v>
+        <v>0.7794237686667369</v>
       </c>
       <c r="H51">
-        <v>-2.753433993117171</v>
+        <v>-2.652768158683785</v>
       </c>
       <c r="I51">
-        <v>2.788279539827706</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>3.537301246603103</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E52">
-        <v>-0.03015598573651412</v>
+        <v>-0.05771776508491929</v>
       </c>
       <c r="F52">
-        <v>1.413724322373517</v>
+        <v>1.579219537021732</v>
       </c>
       <c r="G52">
-        <v>0.9829817097101746</v>
+        <v>0.9708451788620722</v>
       </c>
       <c r="H52">
-        <v>-2.801004741656901</v>
+        <v>-3.152931181329532</v>
       </c>
       <c r="I52">
-        <v>2.740692770183873</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>3.037495651159694</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B53" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E53">
-        <v>-0.01502062565793189</v>
+        <v>0.2634104441453702</v>
       </c>
       <c r="F53">
-        <v>1.413699855069708</v>
+        <v>1.579400091485919</v>
       </c>
       <c r="G53">
-        <v>0.9915225995312187</v>
+        <v>0.8675441040914289</v>
       </c>
       <c r="H53">
-        <v>-2.785821426544054</v>
+        <v>-2.832156852346298</v>
       </c>
       <c r="I53">
-        <v>2.75578017522819</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>3.358977740637039</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E54">
-        <v>-0.03612500067468428</v>
+        <v>0.1871698902850263</v>
       </c>
       <c r="F54">
-        <v>1.413708943644842</v>
+        <v>1.579046644914525</v>
       </c>
       <c r="G54">
-        <v>0.9796135945139743</v>
+        <v>0.9056449706896867</v>
       </c>
       <c r="H54">
-        <v>-2.80694361484074</v>
+        <v>-2.90770466365625</v>
       </c>
       <c r="I54">
-        <v>2.734693613491371</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+        <v>3.282044444226303</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E55">
-        <v>0.009378608243243273</v>
+        <v>0.2261154558727276</v>
       </c>
       <c r="F55">
-        <v>0.006877683488183651</v>
+        <v>1.579175437989217</v>
       </c>
       <c r="G55">
-        <v>0.1726843790968118</v>
+        <v>0.8861434655025966</v>
       </c>
       <c r="H55">
-        <v>-0.004101403690662492</v>
+        <v>-2.869011527856404</v>
       </c>
       <c r="I55">
-        <v>0.02285862017714904</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+        <v>3.321242439601859</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E56">
-        <v>1.834039585774474</v>
+        <v>-0.01039246147832957</v>
       </c>
       <c r="F56">
-        <v>1.668610007067105</v>
+        <v>0.01830487555413695</v>
       </c>
       <c r="G56">
-        <v>0.271706068515189</v>
+        <v>0.5702096182839631</v>
       </c>
       <c r="H56">
-        <v>-1.436375932320176</v>
+        <v>-0.04626935830592566</v>
       </c>
       <c r="I56">
-        <v>5.104455103869124</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+        <v>0.02548443534926652</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E57">
-        <v>0.9563034367576586</v>
+        <v>0.04719828571032152</v>
       </c>
       <c r="F57">
-        <v>1.683439340390516</v>
+        <v>0.01030095979769416</v>
       </c>
       <c r="G57">
-        <v>0.5699906436877451</v>
+        <v>4.607022004654132E-06</v>
       </c>
       <c r="H57">
-        <v>-2.343177040565618</v>
+        <v>0.02700877550064597</v>
       </c>
       <c r="I57">
-        <v>4.255783914080935</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+        <v>0.06738779591999706</v>
+      </c>
+      <c r="J57">
+        <v>0.04719828571032152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E58">
-        <v>-0.396987877607839</v>
+        <v>0.08651299238863024</v>
       </c>
       <c r="F58">
-        <v>1.67032445208994</v>
+        <v>0.7039861632605711</v>
       </c>
       <c r="G58">
-        <v>0.8121361874246488</v>
+        <v>0.9021940550824432</v>
       </c>
       <c r="H58">
-        <v>-3.67076364620072</v>
+        <v>-1.293274533216624</v>
       </c>
       <c r="I58">
-        <v>2.876787890985042</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+        <v>1.466300517993884</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E59">
-        <v>-0.2579537358954739</v>
+        <v>-0.05017673645439282</v>
       </c>
       <c r="F59">
-        <v>1.667554442272197</v>
+        <v>0.7039967918798178</v>
       </c>
       <c r="G59">
-        <v>0.8770658372320717</v>
+        <v>0.9431796094572361</v>
       </c>
       <c r="H59">
-        <v>-3.526300385008756</v>
+        <v>-1.429985093770576</v>
       </c>
       <c r="I59">
-        <v>3.010392913217808</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+        <v>1.32963162086179</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E60">
-        <v>-0.218163495215229</v>
+        <v>0.0282646752407348</v>
       </c>
       <c r="F60">
-        <v>1.670059999846299</v>
+        <v>0.7040479493626299</v>
       </c>
       <c r="G60">
-        <v>0.8960663243504474</v>
+        <v>0.9679767668441579</v>
       </c>
       <c r="H60">
-        <v>-3.491420946934944</v>
+        <v>-1.3516439488993</v>
       </c>
       <c r="I60">
-        <v>3.055093956504486</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>1.408173299380769</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C61" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E61">
-        <v>-0.006453378877913932</v>
+        <v>0.01580678133534455</v>
       </c>
       <c r="F61">
-        <v>0.08050824744525539</v>
+        <v>0.7039749011994658</v>
       </c>
       <c r="G61">
-        <v>0.9361116058318676</v>
+        <v>0.9820861126032137</v>
       </c>
       <c r="H61">
-        <v>-0.1642466443290533</v>
+        <v>-1.363958671035751</v>
       </c>
       <c r="I61">
-        <v>0.1513398865732254</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>1.39557223370644</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C62" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E62">
-        <v>5.548848040928378</v>
+        <v>0.00235558919787493</v>
       </c>
       <c r="F62">
-        <v>129.9089125423122</v>
+        <v>0.7040026999167855</v>
       </c>
       <c r="G62">
-        <v>0.9659300179382395</v>
+        <v>0.9973302875886957</v>
       </c>
       <c r="H62">
-        <v>-249.0679418127672</v>
+        <v>-1.377464347657984</v>
       </c>
       <c r="I62">
-        <v>260.165637894624</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>1.382175526053734</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E63">
-        <v>22.77214379883186</v>
+        <v>0.01345699908705628</v>
       </c>
       <c r="F63">
-        <v>129.9813568994298</v>
+        <v>0.005621256476121317</v>
       </c>
       <c r="G63">
-        <v>0.8609260504382172</v>
+        <v>0.01666808431374018</v>
       </c>
       <c r="H63">
-        <v>-231.9866343856973</v>
+        <v>0.002439538845995962</v>
       </c>
       <c r="I63">
-        <v>277.5309219833611</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
+        <v>0.0244744593281166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C64" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E64">
-        <v>-3.642197729060435</v>
+        <v>0.008143645066237703</v>
       </c>
       <c r="F64">
-        <v>129.9059549680125</v>
+        <v>0.002968318886055052</v>
       </c>
       <c r="G64">
-        <v>0.9776324907709218</v>
+        <v>0.00607841684770863</v>
       </c>
       <c r="H64">
-        <v>-258.2531908436471</v>
+        <v>0.002325846954939747</v>
       </c>
       <c r="I64">
-        <v>250.9687953855262</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
+        <v>0.01396144317753566</v>
+      </c>
+      <c r="J64">
+        <v>0.008143645066237703</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C65" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E65">
-        <v>-1.598338125900563</v>
+        <v>0.4087412092277098</v>
       </c>
       <c r="F65">
-        <v>129.906280298428</v>
+        <v>0.7016066488727929</v>
       </c>
       <c r="G65">
-        <v>0.990183252609351</v>
+        <v>0.5601768326845105</v>
       </c>
       <c r="H65">
-        <v>-256.2099688763847</v>
+        <v>-0.9663825538768038</v>
       </c>
       <c r="I65">
-        <v>253.0132926245835</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+        <v>1.783864972332224</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E66">
-        <v>-1.179547903723482</v>
+        <v>-0.2133041012623642</v>
       </c>
       <c r="F66">
-        <v>129.9079813767329</v>
+        <v>0.7019068490690635</v>
       </c>
       <c r="G66">
-        <v>0.9927554094879457</v>
+        <v>0.7612099285038815</v>
       </c>
       <c r="H66">
-        <v>-255.7945127064201</v>
+        <v>-1.58901624593972</v>
       </c>
       <c r="I66">
-        <v>253.4354168989731</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+        <v>1.162408043414992</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C67" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E67">
-        <v>0.5201174763123944</v>
+        <v>-0.04773374932929657</v>
       </c>
       <c r="F67">
-        <v>1.038456736342283</v>
+        <v>0.7030587516671017</v>
       </c>
       <c r="G67">
-        <v>0.6164723424371549</v>
+        <v>0.9458696997685395</v>
       </c>
       <c r="H67">
-        <v>-1.515220326421486</v>
+        <v>-1.425703581612506</v>
       </c>
       <c r="I67">
-        <v>2.555455279046275</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
+        <v>1.330236082953912</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C68" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E68">
-        <v>1.880680533592171</v>
+        <v>-0.1179302135498788</v>
       </c>
       <c r="F68">
-        <v>1.667511256435842</v>
+        <v>0.7011423107589932</v>
       </c>
       <c r="G68">
-        <v>0.2593888552451064</v>
+        <v>0.8664280986744171</v>
       </c>
       <c r="H68">
-        <v>-1.387581472837214</v>
+        <v>-1.492143890674696</v>
       </c>
       <c r="I68">
-        <v>5.148942540021557</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+        <v>1.256283463574938</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C69" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E69">
-        <v>0.3661140284979758</v>
+        <v>0.03897865428388959</v>
       </c>
       <c r="F69">
-        <v>1.672261788160053</v>
+        <v>0.7015242226132451</v>
       </c>
       <c r="G69">
-        <v>0.8267018957246043</v>
+        <v>0.9556900952221997</v>
       </c>
       <c r="H69">
-        <v>-2.911458849018278</v>
+        <v>-1.33598355632053</v>
       </c>
       <c r="I69">
-        <v>3.64368690601423</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
+        <v>1.413940864888309</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C70" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E70">
-        <v>-0.2455405286189433</v>
+        <v>0.007576557203061434</v>
       </c>
       <c r="F70">
-        <v>1.668750362887774</v>
+        <v>0.02559869735148781</v>
       </c>
       <c r="G70">
-        <v>0.8830212341301098</v>
+        <v>0.7672496880917222</v>
       </c>
       <c r="H70">
-        <v>-3.516231139067127</v>
+        <v>-0.04259596765699555</v>
       </c>
       <c r="I70">
-        <v>3.02515008182924</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
+        <v>0.05774908206311841</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C71" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E71">
-        <v>-0.2070597116992076</v>
+        <v>-0.2502801382188817</v>
       </c>
       <c r="F71">
-        <v>1.667034818298269</v>
+        <v>0.01554489821295188</v>
       </c>
       <c r="G71">
-        <v>0.901150279023283</v>
+        <v>2.531817939933073E-58</v>
       </c>
       <c r="H71">
-        <v>-3.474387916538087</v>
+        <v>-0.2807475788596085</v>
       </c>
       <c r="I71">
-        <v>3.060268493139672</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+        <v>-0.219812697578155</v>
+      </c>
+      <c r="J71">
+        <v>-0.2502801382188817</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C72" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E72">
-        <v>-0.03871677735530765</v>
+        <v>0.2025379475101585</v>
       </c>
       <c r="F72">
-        <v>1.667854757867423</v>
+        <v>3.00021859109196</v>
       </c>
       <c r="G72">
-        <v>0.9814799552726379</v>
+        <v>0.9461775081711313</v>
       </c>
       <c r="H72">
-        <v>-3.30765203421923</v>
+        <v>-5.677782436777585</v>
       </c>
       <c r="I72">
-        <v>3.230218479508615</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+        <v>6.082858331797903</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E73">
-        <v>-0.0657322930366977</v>
+        <v>-0.1214693922414531</v>
       </c>
       <c r="F73">
-        <v>0.053066115011947</v>
+        <v>3.000261478803718</v>
       </c>
       <c r="G73">
-        <v>0.2154615309962814</v>
+        <v>0.9677054540990858</v>
       </c>
       <c r="H73">
-        <v>-0.1697399672595741</v>
+        <v>-6.001873834899623</v>
       </c>
       <c r="I73">
-        <v>0.03827538118617871</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+        <v>5.758935050416717</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C74" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E74">
-        <v>1139.967562422161</v>
+        <v>-0.03771798088469058</v>
       </c>
       <c r="F74">
-        <v>27995.77243266509</v>
+        <v>3.000615104074785</v>
       </c>
       <c r="G74">
-        <v>0.9675196949425966</v>
+        <v>0.989970788967757</v>
       </c>
       <c r="H74">
-        <v>-53730.73812498071</v>
+        <v>-5.918815516338176</v>
       </c>
       <c r="I74">
-        <v>56010.67324982503</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+        <v>5.843379554568795</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E75">
-        <v>4725.410282916476</v>
+        <v>-0.06093009612261693</v>
       </c>
       <c r="F75">
-        <v>28190.04119985375</v>
+        <v>3.000082248349746</v>
       </c>
       <c r="G75">
-        <v>0.866876777749799</v>
+        <v>0.9837964972032148</v>
       </c>
       <c r="H75">
-        <v>-50526.05519149717</v>
+        <v>-5.940983253546069</v>
       </c>
       <c r="I75">
-        <v>59976.87575733012</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+        <v>5.819123061300834</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B76" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E76">
-        <v>-180.9558852570743</v>
+        <v>-0.009563737142023783</v>
       </c>
       <c r="F76">
-        <v>27990.90303796541</v>
+        <v>3.000155973997798</v>
       </c>
       <c r="G76">
-        <v>0.9948418634035252</v>
+        <v>0.997456550475463</v>
       </c>
       <c r="H76">
-        <v>-55042.11773442207</v>
+        <v>-5.889761394180394</v>
       </c>
       <c r="I76">
-        <v>54680.20596390792</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
+        <v>5.870633919896346</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C77" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E77">
-        <v>158.8851488446963</v>
+        <v>0.02387579926767762</v>
       </c>
       <c r="F77">
-        <v>27989.90822586905</v>
+        <v>0.02612229324222231</v>
       </c>
       <c r="G77">
-        <v>0.9954708202199559</v>
+        <v>0.3607163781366759</v>
       </c>
       <c r="H77">
-        <v>-54700.32690444004</v>
+        <v>-0.02732295468067215</v>
       </c>
       <c r="I77">
-        <v>55018.09720212944</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
+        <v>0.07507455321602739</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C78" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E78">
-        <v>334.8317288301375</v>
+        <v>-0.1393011446607439</v>
       </c>
       <c r="F78">
-        <v>27991.56258732806</v>
+        <v>0.01511586804597234</v>
       </c>
       <c r="G78">
-        <v>0.9904560277724772</v>
+        <v>3.096661286636444E-20</v>
       </c>
       <c r="H78">
-        <v>-54527.62281333166</v>
+        <v>-0.1689277016259095</v>
       </c>
       <c r="I78">
-        <v>55197.28627099194</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
+        <v>-0.1096745876955783</v>
+      </c>
+      <c r="J78">
+        <v>-0.1393011446607439</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B79" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C79" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E79">
-        <v>-256.0708611125975</v>
+        <v>-0.06131217980347483</v>
       </c>
       <c r="F79">
-        <v>600.4112400068296</v>
+        <v>0.06933024091959047</v>
       </c>
       <c r="G79">
-        <v>0.669749047904604</v>
+        <v>0.376507451007936</v>
       </c>
       <c r="H79">
-        <v>-1432.855267439018</v>
+        <v>-0.1971969550453573</v>
       </c>
       <c r="I79">
-        <v>920.7135452138231</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
+        <v>0.07457259543840761</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D80" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E80">
-        <v>2.7162845411416</v>
+        <v>0.03010554342343811</v>
       </c>
       <c r="F80">
-        <v>44.00010065263869</v>
+        <v>0.06935861444034848</v>
       </c>
       <c r="G80">
-        <v>0.9507749833706765</v>
+        <v>0.6642475595078163</v>
       </c>
       <c r="H80">
-        <v>-83.52232805416755</v>
+        <v>-0.1058348428972446</v>
       </c>
       <c r="I80">
-        <v>88.95489713645075</v>
+        <v>0.1660459297441208</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E81">
-        <v>1.147459057768995</v>
+        <v>-0.01396117262840306</v>
       </c>
       <c r="F81">
-        <v>44.00036783615029</v>
+        <v>0.0696897773946196</v>
       </c>
       <c r="G81">
-        <v>0.9791948079496906</v>
+        <v>0.8412200380581338</v>
       </c>
       <c r="H81">
-        <v>-85.09167720760016</v>
+        <v>-0.1505506264124711</v>
       </c>
       <c r="I81">
-        <v>87.38659532313815</v>
+        <v>0.1226282811556649</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E82">
-        <v>-0.3813852008381719</v>
+        <v>-0.01606066871130018</v>
       </c>
       <c r="F82">
-        <v>44.00017814581583</v>
+        <v>0.06918265925199919</v>
       </c>
       <c r="G82">
-        <v>0.9930841745209705</v>
+        <v>0.8164224724525926</v>
       </c>
       <c r="H82">
-        <v>-86.62014967998357</v>
+        <v>-0.1516561891999254</v>
       </c>
       <c r="I82">
-        <v>85.85737927830723</v>
+        <v>0.119534851777325</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D83" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E83">
-        <v>-0.1528879814051338</v>
+        <v>-0.01506884882197805</v>
       </c>
       <c r="F83">
-        <v>44.00008338974583</v>
+        <v>0.06922547560337441</v>
       </c>
       <c r="G83">
-        <v>0.9972275799265324</v>
+        <v>0.8276801665823159</v>
       </c>
       <c r="H83">
-        <v>-86.391466742066</v>
+        <v>-0.1507482878172481</v>
       </c>
       <c r="I83">
-        <v>86.08569077925574</v>
+        <v>0.120610590173292</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E84">
-        <v>-0.2391067430611805</v>
+        <v>0.007742278256728424</v>
       </c>
       <c r="F84">
-        <v>44.00021844719036</v>
+        <v>0.00436996911291429</v>
       </c>
       <c r="G84">
-        <v>0.9956641433512601</v>
+        <v>0.07644421843120544</v>
       </c>
       <c r="H84">
-        <v>-86.47795021144918</v>
+        <v>-0.000822703818136033</v>
       </c>
       <c r="I84">
-        <v>85.99973672532681</v>
+        <v>0.01630726033159288</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E85">
-        <v>0.003023852362072745</v>
+        <v>-0.005167876725284576</v>
       </c>
       <c r="F85">
-        <v>0.07367716094033248</v>
+        <v>0.002104377842409861</v>
       </c>
       <c r="G85">
-        <v>0.9672624743248335</v>
+        <v>0.0140581474743386</v>
       </c>
       <c r="H85">
-        <v>-0.1413807295641401</v>
+        <v>-0.009292381506272009</v>
       </c>
       <c r="I85">
-        <v>0.1474284342882856</v>
+        <v>-0.001043371944297143</v>
+      </c>
+      <c r="J85">
+        <v>-0.005167876725284576</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C86" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E86">
-        <v>0.2024029573129226</v>
+        <v>1545.242123982607</v>
       </c>
       <c r="F86">
-        <v>0.03717938052915809</v>
+        <v>65755.32010664341</v>
       </c>
       <c r="G86">
-        <v>5.210973794810996E-08</v>
+        <v>0.9812515343012286</v>
       </c>
       <c r="H86">
-        <v>0.129532710508263</v>
+        <v>-127332.8170769409</v>
       </c>
       <c r="I86">
-        <v>0.2752732041175822</v>
-      </c>
-      <c r="J86">
-        <v>0.2024029573129226</v>
+        <v>130423.3013249062</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C87" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D87" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E87">
-        <v>0.3747759513281315</v>
+        <v>4292.510035215521</v>
       </c>
       <c r="F87">
-        <v>0.06255945581970154</v>
+        <v>65803.86155861642</v>
       </c>
       <c r="G87">
-        <v>2.089188159248791E-09</v>
+        <v>0.9479893733486578</v>
       </c>
       <c r="H87">
-        <v>0.2521616710290918</v>
+        <v>-124680.6886633324</v>
       </c>
       <c r="I87">
-        <v>0.4973902316271712</v>
-      </c>
-      <c r="J87">
-        <v>0.3747759513281315</v>
+        <v>133265.7087337635</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C88" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E88">
-        <v>-0.5536817643527414</v>
+        <v>-715.4455176357422</v>
       </c>
       <c r="F88">
-        <v>0.04486855679367153</v>
+        <v>65760.94959776412</v>
       </c>
       <c r="G88">
-        <v>5.509830023924621E-35</v>
+        <v>0.991319595061072</v>
       </c>
       <c r="H88">
-        <v>-0.6416225197066275</v>
+        <v>-129604.5383184072</v>
       </c>
       <c r="I88">
-        <v>-0.4657410089988552</v>
-      </c>
-      <c r="J88">
-        <v>-0.5536817643527414</v>
+        <v>128173.6472831357</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C89" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E89">
-        <v>2.561429425578734</v>
+        <v>-252.2710765379041</v>
       </c>
       <c r="F89">
-        <v>7.704296918455099</v>
+        <v>65755.6884536649</v>
       </c>
       <c r="G89">
-        <v>0.7395361697515522</v>
+        <v>0.99693893094162</v>
       </c>
       <c r="H89">
-        <v>-12.53871506079618</v>
+        <v>-129131.0522243574</v>
       </c>
       <c r="I89">
-        <v>17.66157391195365</v>
+        <v>128626.5100712816</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C90" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E90">
-        <v>1.510166983183804</v>
+        <v>170.1991345541716</v>
       </c>
       <c r="F90">
-        <v>7.705773579785895</v>
+        <v>65752.50134401995</v>
       </c>
       <c r="G90">
-        <v>0.8446268889924547</v>
+        <v>0.9979346928664422</v>
       </c>
       <c r="H90">
-        <v>-13.59287170621683</v>
+        <v>-128702.3353931464</v>
       </c>
       <c r="I90">
-        <v>16.61320567258444</v>
+        <v>129042.7336622548</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C91" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E91">
-        <v>-0.1469513369326111</v>
+        <v>-269.0605205296978</v>
       </c>
       <c r="F91">
-        <v>7.704826717606168</v>
+        <v>586.3669207870287</v>
       </c>
       <c r="G91">
-        <v>0.9847831626823926</v>
+        <v>0.646334465632133</v>
       </c>
       <c r="H91">
-        <v>-15.24813421056266</v>
+        <v>-1418.318566997925</v>
       </c>
       <c r="I91">
-        <v>14.95423153669744</v>
+        <v>880.197525938529</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C92" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E92">
-        <v>0.06002273129157396</v>
+        <v>-241.353436703274</v>
       </c>
       <c r="F92">
-        <v>7.704157838758015</v>
+        <v>505.4224382132981</v>
       </c>
       <c r="G92">
-        <v>0.993783781808411</v>
+        <v>0.6329860878312678</v>
       </c>
       <c r="H92">
-        <v>-15.03984916388608</v>
+        <v>-1231.963212579759</v>
       </c>
       <c r="I92">
-        <v>15.15989462646922</v>
+        <v>749.256339173211</v>
+      </c>
+      <c r="J92">
+        <v>-241.353436703274</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E93">
-        <v>0.1260046265727748</v>
+        <v>2.944196898961016</v>
       </c>
       <c r="F93">
-        <v>7.704695385506313</v>
+        <v>6.476725308627175</v>
       </c>
       <c r="G93">
-        <v>0.9869517664699349</v>
+        <v>0.6494106362271979</v>
       </c>
       <c r="H93">
-        <v>-14.97492084087155</v>
+        <v>-9.749951443707314</v>
       </c>
       <c r="I93">
-        <v>15.2269300940171</v>
+        <v>15.63834524162935</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B94" t="s">
         <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E94">
-        <v>-0.1401535337244975</v>
+        <v>1.048793694320441</v>
       </c>
       <c r="F94">
-        <v>0.07780186755053851</v>
+        <v>6.47912814584881</v>
       </c>
       <c r="G94">
-        <v>0.07163732665693559</v>
+        <v>0.8714061345991726</v>
       </c>
       <c r="H94">
-        <v>-0.2926423920535084</v>
+        <v>-11.650064122763</v>
       </c>
       <c r="I94">
-        <v>0.01233532460451353</v>
+        <v>13.74765151140389</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B95" t="s">
         <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E95">
-        <v>0.2992110871416774</v>
+        <v>-0.653521883171244</v>
       </c>
       <c r="F95">
-        <v>0.05714436570209453</v>
+        <v>6.477001489548555</v>
       </c>
       <c r="G95">
-        <v>1.640443814132817E-07</v>
+        <v>0.9196307705499716</v>
       </c>
       <c r="H95">
-        <v>0.1872101884461863</v>
+        <v>-13.34821153049869</v>
       </c>
       <c r="I95">
-        <v>0.4112119858371686</v>
-      </c>
-      <c r="J95">
-        <v>0.2992110871416774</v>
+        <v>12.04116776415621</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B96" t="s">
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E96">
-        <v>-0.1123157034365138</v>
+        <v>-0.3418603726593014</v>
       </c>
       <c r="F96">
-        <v>0.05986383663728886</v>
+        <v>6.476471094116025</v>
       </c>
       <c r="G96">
-        <v>0.06062971804943806</v>
+        <v>0.9579032320556015</v>
       </c>
       <c r="H96">
-        <v>-0.2296466672219893</v>
+        <v>-13.03551046404143</v>
       </c>
       <c r="I96">
-        <v>0.005015260348961784</v>
-      </c>
-      <c r="J96">
-        <v>-0.1123157034365138</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
+        <v>12.35178971872283</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B97" t="s">
         <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E97">
-        <v>0.3807934908006717</v>
+        <v>-0.04318746933618201</v>
       </c>
       <c r="F97">
-        <v>0.0465735326871382</v>
+        <v>6.477446583347024</v>
       </c>
       <c r="G97">
-        <v>2.929892057211692E-16</v>
+        <v>0.9946802556748717</v>
       </c>
       <c r="H97">
-        <v>0.2895110441010818</v>
+        <v>-12.73874948447837</v>
       </c>
       <c r="I97">
-        <v>0.4720759375002615</v>
-      </c>
-      <c r="J97">
-        <v>0.3807934908006717</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
+        <v>12.65237454580601</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B98" t="s">
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E98">
-        <v>2.572615624127507</v>
+        <v>-0.1273438380100369</v>
       </c>
       <c r="F98">
-        <v>21.33358542821301</v>
+        <v>0.08323244266282433</v>
       </c>
       <c r="G98">
-        <v>0.9040158434458944</v>
+        <v>0.1260220798612615</v>
       </c>
       <c r="H98">
-        <v>-39.24044347627849</v>
+        <v>-0.2904764279744676</v>
       </c>
       <c r="I98">
-        <v>44.38567472453351</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
+        <v>0.03578875195439388</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B99" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E99">
-        <v>1.391282016527721</v>
+        <v>0.1026348998476229</v>
       </c>
       <c r="F99">
-        <v>21.33417282844994</v>
+        <v>1.413707206249518</v>
       </c>
       <c r="G99">
-        <v>0.9480037910042083</v>
+        <v>0.9421245636916359</v>
       </c>
       <c r="H99">
-        <v>-40.42292836718719</v>
+        <v>-2.668180309086171</v>
       </c>
       <c r="I99">
-        <v>43.20549240024263</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
+        <v>2.873450108781417</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E100">
-        <v>-0.1544471621241104</v>
+        <v>0.01742277335526768</v>
       </c>
       <c r="F100">
-        <v>21.33377182768572</v>
+        <v>1.413728409464971</v>
       </c>
       <c r="G100">
-        <v>0.9942237157745103</v>
+        <v>0.9901671283606914</v>
       </c>
       <c r="H100">
-        <v>-41.96787159878335</v>
+        <v>-2.753433993117171</v>
       </c>
       <c r="I100">
-        <v>41.65897727453514</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
+        <v>2.788279539827706</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E101">
-        <v>0.04998418191712636</v>
+        <v>-0.03015598573651412</v>
       </c>
       <c r="F101">
-        <v>21.33350006440048</v>
+        <v>1.413724322373517</v>
       </c>
       <c r="G101">
-        <v>0.9981305659912043</v>
+        <v>0.9829817097101746</v>
       </c>
       <c r="H101">
-        <v>-41.76290760849073</v>
+        <v>-2.801004741656901</v>
       </c>
       <c r="I101">
-        <v>41.86287597232498</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
+        <v>2.740692770183873</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E102">
-        <v>0.1265877215795793</v>
+        <v>-0.01502062565793189</v>
       </c>
       <c r="F102">
-        <v>21.3337223578023</v>
+        <v>1.413699855069708</v>
       </c>
       <c r="G102">
-        <v>0.9952656271488372</v>
+        <v>0.9915225995312187</v>
       </c>
       <c r="H102">
-        <v>-41.68673975588986</v>
+        <v>-2.785821426544054</v>
       </c>
       <c r="I102">
-        <v>41.93991519904903</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
+        <v>2.75578017522819</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E103">
-        <v>-0.1272608362904527</v>
+        <v>-0.03612500067468428</v>
       </c>
       <c r="F103">
-        <v>0.08202126947916348</v>
+        <v>1.413708943644842</v>
       </c>
       <c r="G103">
-        <v>0.1207677873078864</v>
+        <v>0.9796135945139743</v>
       </c>
       <c r="H103">
-        <v>-0.2880195704358675</v>
+        <v>-2.80694361484074</v>
       </c>
       <c r="I103">
-        <v>0.03349789785496204</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
+        <v>2.734693613491371</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E104">
-        <v>0.2236676497276942</v>
+        <v>0.009378608243243273</v>
       </c>
       <c r="F104">
-        <v>0.04308959877793096</v>
+        <v>0.006877683488183651</v>
       </c>
       <c r="G104">
-        <v>2.09440471188536E-07</v>
+        <v>0.1726843790968118</v>
       </c>
       <c r="H104">
-        <v>0.1392135880146684</v>
+        <v>-0.004101403690662492</v>
       </c>
       <c r="I104">
-        <v>0.30812171144072</v>
-      </c>
-      <c r="J104">
-        <v>0.2236676497276942</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
+        <v>0.02285862017714904</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E105">
-        <v>0.07804132133657951</v>
+        <v>1.834039585774474</v>
       </c>
       <c r="F105">
-        <v>0.03908522525613052</v>
+        <v>1.668610007067105</v>
       </c>
       <c r="G105">
-        <v>0.04585819354270763</v>
+        <v>0.271706068515189</v>
       </c>
       <c r="H105">
-        <v>0.001435687506928379</v>
+        <v>-1.436375932320176</v>
       </c>
       <c r="I105">
-        <v>0.1546469551662306</v>
-      </c>
-      <c r="J105">
-        <v>0.07804132133657951</v>
+        <v>5.104455103869124</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
+        <v>43</v>
+      </c>
+      <c r="B106" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" t="s">
+        <v>44</v>
+      </c>
+      <c r="D106" t="s">
+        <v>79</v>
+      </c>
+      <c r="E106">
+        <v>0.9563034367576586</v>
+      </c>
+      <c r="F106">
+        <v>1.683439340390516</v>
+      </c>
+      <c r="G106">
+        <v>0.5699906436877451</v>
+      </c>
+      <c r="H106">
+        <v>-2.343177040565618</v>
+      </c>
+      <c r="I106">
+        <v>4.255783914080935</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B107" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" t="s">
+        <v>44</v>
+      </c>
+      <c r="D107" t="s">
+        <v>80</v>
+      </c>
+      <c r="E107">
+        <v>-0.396987877607839</v>
+      </c>
+      <c r="F107">
+        <v>1.67032445208994</v>
+      </c>
+      <c r="G107">
+        <v>0.8121361874246488</v>
+      </c>
+      <c r="H107">
+        <v>-3.67076364620072</v>
+      </c>
+      <c r="I107">
+        <v>2.876787890985042</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>43</v>
+      </c>
+      <c r="B108" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" t="s">
+        <v>44</v>
+      </c>
+      <c r="D108" t="s">
+        <v>81</v>
+      </c>
+      <c r="E108">
+        <v>-0.2579537358954739</v>
+      </c>
+      <c r="F108">
+        <v>1.667554442272197</v>
+      </c>
+      <c r="G108">
+        <v>0.8770658372320717</v>
+      </c>
+      <c r="H108">
+        <v>-3.526300385008756</v>
+      </c>
+      <c r="I108">
+        <v>3.010392913217808</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>43</v>
+      </c>
+      <c r="B109" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" t="s">
+        <v>44</v>
+      </c>
+      <c r="D109" t="s">
+        <v>82</v>
+      </c>
+      <c r="E109">
+        <v>-0.218163495215229</v>
+      </c>
+      <c r="F109">
+        <v>1.670059999846299</v>
+      </c>
+      <c r="G109">
+        <v>0.8960663243504474</v>
+      </c>
+      <c r="H109">
+        <v>-3.491420946934944</v>
+      </c>
+      <c r="I109">
+        <v>3.055093956504486</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>43</v>
+      </c>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
+        <v>44</v>
+      </c>
+      <c r="D110" t="s">
+        <v>83</v>
+      </c>
+      <c r="E110">
+        <v>-0.006453378877913932</v>
+      </c>
+      <c r="F110">
+        <v>0.08050824744525539</v>
+      </c>
+      <c r="G110">
+        <v>0.9361116058318676</v>
+      </c>
+      <c r="H110">
+        <v>-0.1642466443290533</v>
+      </c>
+      <c r="I110">
+        <v>0.1513398865732254</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>43</v>
+      </c>
+      <c r="B111" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111" t="s">
+        <v>44</v>
+      </c>
+      <c r="D111" t="s">
+        <v>78</v>
+      </c>
+      <c r="E111">
+        <v>5.548848040928378</v>
+      </c>
+      <c r="F111">
+        <v>129.9089125423122</v>
+      </c>
+      <c r="G111">
+        <v>0.9659300179382395</v>
+      </c>
+      <c r="H111">
+        <v>-249.0679418127672</v>
+      </c>
+      <c r="I111">
+        <v>260.165637894624</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" t="s">
+        <v>43</v>
+      </c>
+      <c r="B112" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112" t="s">
+        <v>44</v>
+      </c>
+      <c r="D112" t="s">
+        <v>79</v>
+      </c>
+      <c r="E112">
+        <v>22.77214379883186</v>
+      </c>
+      <c r="F112">
+        <v>129.9813568994298</v>
+      </c>
+      <c r="G112">
+        <v>0.8609260504382172</v>
+      </c>
+      <c r="H112">
+        <v>-231.9866343856973</v>
+      </c>
+      <c r="I112">
+        <v>277.5309219833611</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" t="s">
+        <v>43</v>
+      </c>
+      <c r="B113" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113" t="s">
+        <v>44</v>
+      </c>
+      <c r="D113" t="s">
+        <v>80</v>
+      </c>
+      <c r="E113">
+        <v>-3.642197729060435</v>
+      </c>
+      <c r="F113">
+        <v>129.9059549680125</v>
+      </c>
+      <c r="G113">
+        <v>0.9776324907709218</v>
+      </c>
+      <c r="H113">
+        <v>-258.2531908436471</v>
+      </c>
+      <c r="I113">
+        <v>250.9687953855262</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>43</v>
+      </c>
+      <c r="B114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" t="s">
+        <v>44</v>
+      </c>
+      <c r="D114" t="s">
+        <v>81</v>
+      </c>
+      <c r="E114">
+        <v>-1.598338125900563</v>
+      </c>
+      <c r="F114">
+        <v>129.906280298428</v>
+      </c>
+      <c r="G114">
+        <v>0.990183252609351</v>
+      </c>
+      <c r="H114">
+        <v>-256.2099688763847</v>
+      </c>
+      <c r="I114">
+        <v>253.0132926245835</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" t="s">
+        <v>43</v>
+      </c>
+      <c r="B115" t="s">
+        <v>14</v>
+      </c>
+      <c r="C115" t="s">
+        <v>44</v>
+      </c>
+      <c r="D115" t="s">
+        <v>82</v>
+      </c>
+      <c r="E115">
+        <v>-1.179547903723482</v>
+      </c>
+      <c r="F115">
+        <v>129.9079813767329</v>
+      </c>
+      <c r="G115">
+        <v>0.9927554094879457</v>
+      </c>
+      <c r="H115">
+        <v>-255.7945127064201</v>
+      </c>
+      <c r="I115">
+        <v>253.4354168989731</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" t="s">
+        <v>43</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" t="s">
+        <v>44</v>
+      </c>
+      <c r="D116" t="s">
+        <v>83</v>
+      </c>
+      <c r="E116">
+        <v>0.5201174763123944</v>
+      </c>
+      <c r="F116">
+        <v>1.038456736342283</v>
+      </c>
+      <c r="G116">
+        <v>0.6164723424371549</v>
+      </c>
+      <c r="H116">
+        <v>-1.515220326421486</v>
+      </c>
+      <c r="I116">
+        <v>2.555455279046275</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" t="s">
+        <v>43</v>
+      </c>
+      <c r="B117" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117" t="s">
+        <v>44</v>
+      </c>
+      <c r="D117" t="s">
+        <v>78</v>
+      </c>
+      <c r="E117">
+        <v>1.880680533592171</v>
+      </c>
+      <c r="F117">
+        <v>1.667511256435842</v>
+      </c>
+      <c r="G117">
+        <v>0.2593888552451064</v>
+      </c>
+      <c r="H117">
+        <v>-1.387581472837214</v>
+      </c>
+      <c r="I117">
+        <v>5.148942540021557</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" t="s">
+        <v>43</v>
+      </c>
+      <c r="B118" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118" t="s">
+        <v>44</v>
+      </c>
+      <c r="D118" t="s">
+        <v>79</v>
+      </c>
+      <c r="E118">
+        <v>0.3661140284979758</v>
+      </c>
+      <c r="F118">
+        <v>1.672261788160053</v>
+      </c>
+      <c r="G118">
+        <v>0.8267018957246043</v>
+      </c>
+      <c r="H118">
+        <v>-2.911458849018278</v>
+      </c>
+      <c r="I118">
+        <v>3.64368690601423</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" t="s">
+        <v>43</v>
+      </c>
+      <c r="B119" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" t="s">
+        <v>44</v>
+      </c>
+      <c r="D119" t="s">
+        <v>80</v>
+      </c>
+      <c r="E119">
+        <v>-0.2455405286189433</v>
+      </c>
+      <c r="F119">
+        <v>1.668750362887774</v>
+      </c>
+      <c r="G119">
+        <v>0.8830212341301098</v>
+      </c>
+      <c r="H119">
+        <v>-3.516231139067127</v>
+      </c>
+      <c r="I119">
+        <v>3.02515008182924</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" t="s">
+        <v>43</v>
+      </c>
+      <c r="B120" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" t="s">
+        <v>44</v>
+      </c>
+      <c r="D120" t="s">
+        <v>81</v>
+      </c>
+      <c r="E120">
+        <v>-0.2070597116992076</v>
+      </c>
+      <c r="F120">
+        <v>1.667034818298269</v>
+      </c>
+      <c r="G120">
+        <v>0.901150279023283</v>
+      </c>
+      <c r="H120">
+        <v>-3.474387916538087</v>
+      </c>
+      <c r="I120">
+        <v>3.060268493139672</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" t="s">
+        <v>43</v>
+      </c>
+      <c r="B121" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121" t="s">
+        <v>44</v>
+      </c>
+      <c r="D121" t="s">
+        <v>82</v>
+      </c>
+      <c r="E121">
+        <v>-0.03871677735530765</v>
+      </c>
+      <c r="F121">
+        <v>1.667854757867423</v>
+      </c>
+      <c r="G121">
+        <v>0.9814799552726379</v>
+      </c>
+      <c r="H121">
+        <v>-3.30765203421923</v>
+      </c>
+      <c r="I121">
+        <v>3.230218479508615</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" t="s">
+        <v>43</v>
+      </c>
+      <c r="B122" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122" t="s">
+        <v>44</v>
+      </c>
+      <c r="D122" t="s">
+        <v>83</v>
+      </c>
+      <c r="E122">
+        <v>-0.0657322930366977</v>
+      </c>
+      <c r="F122">
+        <v>0.053066115011947</v>
+      </c>
+      <c r="G122">
+        <v>0.2154615309962814</v>
+      </c>
+      <c r="H122">
+        <v>-0.1697399672595741</v>
+      </c>
+      <c r="I122">
+        <v>0.03827538118617871</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" t="s">
+        <v>43</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="s">
+        <v>44</v>
+      </c>
+      <c r="D123" t="s">
+        <v>78</v>
+      </c>
+      <c r="E123">
+        <v>-74828.48469726639</v>
+      </c>
+      <c r="F123">
+        <v>2889994.284240374</v>
+      </c>
+      <c r="G123">
+        <v>0.9793432732474506</v>
+      </c>
+      <c r="H123">
+        <v>-5739113.197335011</v>
+      </c>
+      <c r="I123">
+        <v>5589456.227940478</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" t="s">
+        <v>43</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="s">
+        <v>44</v>
+      </c>
+      <c r="D124" t="s">
+        <v>79</v>
+      </c>
+      <c r="E124">
+        <v>451520.0415896832</v>
+      </c>
+      <c r="F124">
+        <v>2898318.695782662</v>
+      </c>
+      <c r="G124">
+        <v>0.8762010085926516</v>
+      </c>
+      <c r="H124">
+        <v>-5229080.217863437</v>
+      </c>
+      <c r="I124">
+        <v>6132120.301042803</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" t="s">
+        <v>43</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="s">
+        <v>44</v>
+      </c>
+      <c r="D125" t="s">
+        <v>80</v>
+      </c>
+      <c r="E125">
+        <v>18077.44021072563</v>
+      </c>
+      <c r="F125">
+        <v>2888414.954359802</v>
+      </c>
+      <c r="G125">
+        <v>0.9950063905261524</v>
+      </c>
+      <c r="H125">
+        <v>-5643111.842741391</v>
+      </c>
+      <c r="I125">
+        <v>5679266.723162841</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>43</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="s">
+        <v>44</v>
+      </c>
+      <c r="D126" t="s">
+        <v>81</v>
+      </c>
+      <c r="E126">
+        <v>129289.7960654707</v>
+      </c>
+      <c r="F126">
+        <v>2890081.668964487</v>
+      </c>
+      <c r="G126">
+        <v>0.9643179860855474</v>
+      </c>
+      <c r="H126">
+        <v>-5535166.187484335</v>
+      </c>
+      <c r="I126">
+        <v>5793745.779615276</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>43</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="s">
+        <v>44</v>
+      </c>
+      <c r="D127" t="s">
+        <v>82</v>
+      </c>
+      <c r="E127">
+        <v>46343.47200695744</v>
+      </c>
+      <c r="F127">
+        <v>2888729.046101908</v>
+      </c>
+      <c r="G127">
+        <v>0.9872001997619876</v>
+      </c>
+      <c r="H127">
+        <v>-5615461.419447528</v>
+      </c>
+      <c r="I127">
+        <v>5708148.363461442</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>43</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="s">
+        <v>44</v>
+      </c>
+      <c r="D128" t="s">
+        <v>83</v>
+      </c>
+      <c r="E128">
+        <v>75426.38124897706</v>
+      </c>
+      <c r="F128">
+        <v>98538.06625395556</v>
+      </c>
+      <c r="G128">
+        <v>0.4440011013922995</v>
+      </c>
+      <c r="H128">
+        <v>-117704.6797149975</v>
+      </c>
+      <c r="I128">
+        <v>268557.4422129517</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
+        <v>43</v>
+      </c>
+      <c r="B129" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" t="s">
+        <v>44</v>
+      </c>
+      <c r="D129" t="s">
+        <v>78</v>
+      </c>
+      <c r="E129">
+        <v>0.6600639986799826</v>
+      </c>
+      <c r="F129">
+        <v>0.6908481881082845</v>
+      </c>
+      <c r="G129">
+        <v>0.3393552297023528</v>
+      </c>
+      <c r="H129">
+        <v>-0.6939735687970077</v>
+      </c>
+      <c r="I129">
+        <v>2.014101566156973</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" t="s">
+        <v>43</v>
+      </c>
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" t="s">
+        <v>44</v>
+      </c>
+      <c r="D130" t="s">
+        <v>79</v>
+      </c>
+      <c r="E130">
+        <v>-0.2348062429093807</v>
+      </c>
+      <c r="F130">
+        <v>0.6912162504008155</v>
+      </c>
+      <c r="G130">
+        <v>0.7340823716903562</v>
+      </c>
+      <c r="H130">
+        <v>-1.589565199223799</v>
+      </c>
+      <c r="I130">
+        <v>1.119952713405037</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" t="s">
+        <v>43</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" t="s">
+        <v>44</v>
+      </c>
+      <c r="D131" t="s">
+        <v>80</v>
+      </c>
+      <c r="E131">
+        <v>0.1001392647006459</v>
+      </c>
+      <c r="F131">
+        <v>0.6915305142099607</v>
+      </c>
+      <c r="G131">
+        <v>0.8848623355606682</v>
+      </c>
+      <c r="H131">
+        <v>-1.255235637361341</v>
+      </c>
+      <c r="I131">
+        <v>1.455514166762633</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" t="s">
+        <v>43</v>
+      </c>
+      <c r="B132" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" t="s">
+        <v>44</v>
+      </c>
+      <c r="D132" t="s">
+        <v>81</v>
+      </c>
+      <c r="E132">
+        <v>0.07122517802881691</v>
+      </c>
+      <c r="F132">
+        <v>0.6906924783436718</v>
+      </c>
+      <c r="G132">
+        <v>0.9178666177278576</v>
+      </c>
+      <c r="H132">
+        <v>-1.282507203917491</v>
+      </c>
+      <c r="I132">
+        <v>1.424957559975125</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" t="s">
+        <v>43</v>
+      </c>
+      <c r="B133" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" t="s">
+        <v>44</v>
+      </c>
+      <c r="D133" t="s">
+        <v>82</v>
+      </c>
+      <c r="E133">
+        <v>0.1847652795594426</v>
+      </c>
+      <c r="F133">
+        <v>0.6911050206378032</v>
+      </c>
+      <c r="G133">
+        <v>0.7892015283497416</v>
+      </c>
+      <c r="H133">
+        <v>-1.169775670425462</v>
+      </c>
+      <c r="I133">
+        <v>1.539306229544348</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" t="s">
+        <v>43</v>
+      </c>
+      <c r="B134" t="s">
+        <v>17</v>
+      </c>
+      <c r="C134" t="s">
+        <v>44</v>
+      </c>
+      <c r="D134" t="s">
+        <v>83</v>
+      </c>
+      <c r="E134">
+        <v>-0.00921700404093569</v>
+      </c>
+      <c r="F134">
+        <v>0.0226682464691811</v>
+      </c>
+      <c r="G134">
+        <v>0.68429871783719</v>
+      </c>
+      <c r="H134">
+        <v>-0.05364595071320789</v>
+      </c>
+      <c r="I134">
+        <v>0.03521194263133652</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" t="s">
+        <v>43</v>
+      </c>
+      <c r="B135" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" t="s">
+        <v>44</v>
+      </c>
+      <c r="D135" t="s">
+        <v>78</v>
+      </c>
+      <c r="E135">
+        <v>0.5215207066885346</v>
+      </c>
+      <c r="F135">
+        <v>0.1676983892720567</v>
+      </c>
+      <c r="G135">
+        <v>0.001871677481952087</v>
+      </c>
+      <c r="H135">
+        <v>0.1928379034499252</v>
+      </c>
+      <c r="I135">
+        <v>0.8502035099271439</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" t="s">
+        <v>43</v>
+      </c>
+      <c r="B136" t="s">
+        <v>18</v>
+      </c>
+      <c r="C136" t="s">
+        <v>44</v>
+      </c>
+      <c r="D136" t="s">
+        <v>79</v>
+      </c>
+      <c r="E136">
+        <v>-0.142374316299386</v>
+      </c>
+      <c r="F136">
+        <v>0.1686811485576504</v>
+      </c>
+      <c r="G136">
+        <v>0.39864480237002</v>
+      </c>
+      <c r="H136">
+        <v>-0.4729832923432312</v>
+      </c>
+      <c r="I136">
+        <v>0.1882346597444592</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" t="s">
+        <v>43</v>
+      </c>
+      <c r="B137" t="s">
+        <v>18</v>
+      </c>
+      <c r="C137" t="s">
+        <v>44</v>
+      </c>
+      <c r="D137" t="s">
+        <v>80</v>
+      </c>
+      <c r="E137">
+        <v>0.1588874063846637</v>
+      </c>
+      <c r="F137">
+        <v>0.1696082348838405</v>
+      </c>
+      <c r="G137">
+        <v>0.3488662625055297</v>
+      </c>
+      <c r="H137">
+        <v>-0.1735386254690736</v>
+      </c>
+      <c r="I137">
+        <v>0.4913134382384011</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" t="s">
+        <v>43</v>
+      </c>
+      <c r="B138" t="s">
+        <v>18</v>
+      </c>
+      <c r="C138" t="s">
+        <v>44</v>
+      </c>
+      <c r="D138" t="s">
+        <v>81</v>
+      </c>
+      <c r="E138">
+        <v>0.1067655286887886</v>
+      </c>
+      <c r="F138">
+        <v>0.167218366071189</v>
+      </c>
+      <c r="G138">
+        <v>0.5231614780044167</v>
+      </c>
+      <c r="H138">
+        <v>-0.2209764463643763</v>
+      </c>
+      <c r="I138">
+        <v>0.4345075037419535</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" t="s">
+        <v>43</v>
+      </c>
+      <c r="B139" t="s">
+        <v>18</v>
+      </c>
+      <c r="C139" t="s">
+        <v>44</v>
+      </c>
+      <c r="D139" t="s">
+        <v>82</v>
+      </c>
+      <c r="E139">
+        <v>0.1939204462304111</v>
+      </c>
+      <c r="F139">
+        <v>0.1685389999680956</v>
+      </c>
+      <c r="G139">
+        <v>0.2498981203159278</v>
+      </c>
+      <c r="H139">
+        <v>-0.1364099236974536</v>
+      </c>
+      <c r="I139">
+        <v>0.5242508161582758</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" t="s">
+        <v>43</v>
+      </c>
+      <c r="B140" t="s">
+        <v>18</v>
+      </c>
+      <c r="C140" t="s">
+        <v>44</v>
+      </c>
+      <c r="D140" t="s">
+        <v>83</v>
+      </c>
+      <c r="E140">
+        <v>-0.01293267662845365</v>
+      </c>
+      <c r="F140">
+        <v>0.01857342151205529</v>
+      </c>
+      <c r="G140">
+        <v>0.4862408643127029</v>
+      </c>
+      <c r="H140">
+        <v>-0.0493359138617635</v>
+      </c>
+      <c r="I140">
+        <v>0.0234705606048562</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" t="s">
+        <v>43</v>
+      </c>
+      <c r="B141" t="s">
+        <v>19</v>
+      </c>
+      <c r="C141" t="s">
+        <v>44</v>
+      </c>
+      <c r="D141" t="s">
+        <v>78</v>
+      </c>
+      <c r="E141">
+        <v>0.1001875943698771</v>
+      </c>
+      <c r="F141">
+        <v>0.202459677824482</v>
+      </c>
+      <c r="G141">
+        <v>0.6207045328798254</v>
+      </c>
+      <c r="H141">
+        <v>-0.2966260824876903</v>
+      </c>
+      <c r="I141">
+        <v>0.4970012712274445</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" t="s">
+        <v>43</v>
+      </c>
+      <c r="B142" t="s">
+        <v>19</v>
+      </c>
+      <c r="C142" t="s">
+        <v>44</v>
+      </c>
+      <c r="D142" t="s">
+        <v>79</v>
+      </c>
+      <c r="E142">
+        <v>-0.06478347259421054</v>
+      </c>
+      <c r="F142">
+        <v>0.2024850306138875</v>
+      </c>
+      <c r="G142">
+        <v>0.7490122725591715</v>
+      </c>
+      <c r="H142">
+        <v>-0.4616468400059203</v>
+      </c>
+      <c r="I142">
+        <v>0.3320798948174993</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" t="s">
+        <v>43</v>
+      </c>
+      <c r="B143" t="s">
+        <v>19</v>
+      </c>
+      <c r="C143" t="s">
+        <v>44</v>
+      </c>
+      <c r="D143" t="s">
+        <v>80</v>
+      </c>
+      <c r="E143">
+        <v>0.01023015326694155</v>
+      </c>
+      <c r="F143">
+        <v>0.2026185626144762</v>
+      </c>
+      <c r="G143">
+        <v>0.9597321460321661</v>
+      </c>
+      <c r="H143">
+        <v>-0.3868949320567058</v>
+      </c>
+      <c r="I143">
+        <v>0.4073552385905889</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" t="s">
+        <v>43</v>
+      </c>
+      <c r="B144" t="s">
+        <v>19</v>
+      </c>
+      <c r="C144" t="s">
+        <v>44</v>
+      </c>
+      <c r="D144" t="s">
+        <v>81</v>
+      </c>
+      <c r="E144">
+        <v>0.001933722753600135</v>
+      </c>
+      <c r="F144">
+        <v>0.2024303247788858</v>
+      </c>
+      <c r="G144">
+        <v>0.9923782957568649</v>
+      </c>
+      <c r="H144">
+        <v>-0.3948224231917621</v>
+      </c>
+      <c r="I144">
+        <v>0.3986898686989624</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" t="s">
+        <v>43</v>
+      </c>
+      <c r="B145" t="s">
+        <v>19</v>
+      </c>
+      <c r="C145" t="s">
+        <v>44</v>
+      </c>
+      <c r="D145" t="s">
+        <v>82</v>
+      </c>
+      <c r="E145">
+        <v>-0.003199373815830464</v>
+      </c>
+      <c r="F145">
+        <v>0.2025568640052744</v>
+      </c>
+      <c r="G145">
+        <v>0.9873979840388695</v>
+      </c>
+      <c r="H145">
+        <v>-0.4002035320875459</v>
+      </c>
+      <c r="I145">
+        <v>0.393804784455885</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" t="s">
+        <v>43</v>
+      </c>
+      <c r="B146" t="s">
+        <v>19</v>
+      </c>
+      <c r="C146" t="s">
+        <v>44</v>
+      </c>
+      <c r="D146" t="s">
+        <v>83</v>
+      </c>
+      <c r="E146">
+        <v>0.01301870752067498</v>
+      </c>
+      <c r="F146">
+        <v>0.005645463503713164</v>
+      </c>
+      <c r="G146">
+        <v>0.02110797317987211</v>
+      </c>
+      <c r="H146">
+        <v>0.001953802377361868</v>
+      </c>
+      <c r="I146">
+        <v>0.02408361266398808</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" t="s">
+        <v>43</v>
+      </c>
+      <c r="B147" t="s">
+        <v>20</v>
+      </c>
+      <c r="C147" t="s">
+        <v>44</v>
+      </c>
+      <c r="D147" t="s">
+        <v>78</v>
+      </c>
+      <c r="E147">
+        <v>-0.01152284281744822</v>
+      </c>
+      <c r="F147">
+        <v>4.042172075885884</v>
+      </c>
+      <c r="G147">
+        <v>0.9977255085246146</v>
+      </c>
+      <c r="H147">
+        <v>-7.934034530867287</v>
+      </c>
+      <c r="I147">
+        <v>7.910988845232391</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" t="s">
+        <v>43</v>
+      </c>
+      <c r="B148" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" t="s">
+        <v>44</v>
+      </c>
+      <c r="D148" t="s">
+        <v>79</v>
+      </c>
+      <c r="E148">
+        <v>0.2356074009292737</v>
+      </c>
+      <c r="F148">
+        <v>4.042245906364694</v>
+      </c>
+      <c r="G148">
+        <v>0.9535206108454313</v>
+      </c>
+      <c r="H148">
+        <v>-7.687048992199994</v>
+      </c>
+      <c r="I148">
+        <v>8.158263794058541</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" t="s">
+        <v>43</v>
+      </c>
+      <c r="B149" t="s">
+        <v>20</v>
+      </c>
+      <c r="C149" t="s">
+        <v>44</v>
+      </c>
+      <c r="D149" t="s">
+        <v>80</v>
+      </c>
+      <c r="E149">
+        <v>0.5065245239131636</v>
+      </c>
+      <c r="F149">
+        <v>4.042458594568733</v>
+      </c>
+      <c r="G149">
+        <v>0.9002851783760809</v>
+      </c>
+      <c r="H149">
+        <v>-7.416548730435957</v>
+      </c>
+      <c r="I149">
+        <v>8.429597778262284</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>43</v>
+      </c>
+      <c r="B150" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" t="s">
+        <v>44</v>
+      </c>
+      <c r="D150" t="s">
+        <v>81</v>
+      </c>
+      <c r="E150">
+        <v>0.3084330416161181</v>
+      </c>
+      <c r="F150">
+        <v>4.042105982248443</v>
+      </c>
+      <c r="G150">
+        <v>0.9391764195511929</v>
+      </c>
+      <c r="H150">
+        <v>-7.613949105284728</v>
+      </c>
+      <c r="I150">
+        <v>8.230815188516965</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>43</v>
+      </c>
+      <c r="B151" t="s">
+        <v>20</v>
+      </c>
+      <c r="C151" t="s">
+        <v>44</v>
+      </c>
+      <c r="D151" t="s">
+        <v>82</v>
+      </c>
+      <c r="E151">
+        <v>0.2097003519466311</v>
+      </c>
+      <c r="F151">
+        <v>4.042252536274446</v>
+      </c>
+      <c r="G151">
+        <v>0.9586266187107996</v>
+      </c>
+      <c r="H151">
+        <v>-7.712969035566971</v>
+      </c>
+      <c r="I151">
+        <v>8.132369739460232</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" t="s">
+        <v>43</v>
+      </c>
+      <c r="B152" t="s">
+        <v>20</v>
+      </c>
+      <c r="C152" t="s">
+        <v>44</v>
+      </c>
+      <c r="D152" t="s">
+        <v>83</v>
+      </c>
+      <c r="E152">
+        <v>0.02104665234127659</v>
+      </c>
+      <c r="F152">
+        <v>0.03283771863448939</v>
+      </c>
+      <c r="G152">
+        <v>0.5215686911247464</v>
+      </c>
+      <c r="H152">
+        <v>-0.04331409351678242</v>
+      </c>
+      <c r="I152">
+        <v>0.0854073981993356</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" t="s">
+        <v>43</v>
+      </c>
+      <c r="B153" t="s">
+        <v>21</v>
+      </c>
+      <c r="C153" t="s">
+        <v>44</v>
+      </c>
+      <c r="D153" t="s">
+        <v>78</v>
+      </c>
+      <c r="E153">
+        <v>-0.03137299694702543</v>
+      </c>
+      <c r="F153">
+        <v>0.8947943967751777</v>
+      </c>
+      <c r="G153">
+        <v>0.9720305556335496</v>
+      </c>
+      <c r="H153">
+        <v>-1.785137788194617</v>
+      </c>
+      <c r="I153">
+        <v>1.722391794300566</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" t="s">
+        <v>43</v>
+      </c>
+      <c r="B154" t="s">
+        <v>21</v>
+      </c>
+      <c r="C154" t="s">
+        <v>44</v>
+      </c>
+      <c r="D154" t="s">
+        <v>79</v>
+      </c>
+      <c r="E154">
+        <v>0.1283861758099778</v>
+      </c>
+      <c r="F154">
+        <v>0.8950949954291174</v>
+      </c>
+      <c r="G154">
+        <v>0.8859482086542759</v>
+      </c>
+      <c r="H154">
+        <v>-1.625967777973137</v>
+      </c>
+      <c r="I154">
+        <v>1.882740129593092</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" t="s">
+        <v>43</v>
+      </c>
+      <c r="B155" t="s">
+        <v>21</v>
+      </c>
+      <c r="C155" t="s">
+        <v>44</v>
+      </c>
+      <c r="D155" t="s">
+        <v>80</v>
+      </c>
+      <c r="E155">
+        <v>0.2707715878434497</v>
+      </c>
+      <c r="F155">
+        <v>0.896147938117747</v>
+      </c>
+      <c r="G155">
+        <v>0.7625373026612176</v>
+      </c>
+      <c r="H155">
+        <v>-1.485646095687163</v>
+      </c>
+      <c r="I155">
+        <v>2.027189271374063</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" t="s">
+        <v>43</v>
+      </c>
+      <c r="B156" t="s">
+        <v>21</v>
+      </c>
+      <c r="C156" t="s">
+        <v>44</v>
+      </c>
+      <c r="D156" t="s">
+        <v>81</v>
+      </c>
+      <c r="E156">
+        <v>0.1763755482987656</v>
+      </c>
+      <c r="F156">
+        <v>0.8945844214120052</v>
+      </c>
+      <c r="G156">
+        <v>0.8437029580653098</v>
+      </c>
+      <c r="H156">
+        <v>-1.576977698799367</v>
+      </c>
+      <c r="I156">
+        <v>1.929728795396898</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" t="s">
+        <v>43</v>
+      </c>
+      <c r="B157" t="s">
+        <v>21</v>
+      </c>
+      <c r="C157" t="s">
+        <v>44</v>
+      </c>
+      <c r="D157" t="s">
+        <v>82</v>
+      </c>
+      <c r="E157">
+        <v>0.0854566990463536</v>
+      </c>
+      <c r="F157">
+        <v>0.8949035178291247</v>
+      </c>
+      <c r="G157">
+        <v>0.9239235363452356</v>
+      </c>
+      <c r="H157">
+        <v>-1.668521965536929</v>
+      </c>
+      <c r="I157">
+        <v>1.839435363629636</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" t="s">
+        <v>43</v>
+      </c>
+      <c r="B158" t="s">
+        <v>21</v>
+      </c>
+      <c r="C158" t="s">
+        <v>44</v>
+      </c>
+      <c r="D158" t="s">
+        <v>83</v>
+      </c>
+      <c r="E158">
+        <v>0.0313729969470296</v>
+      </c>
+      <c r="F158">
+        <v>0.02834797341302443</v>
+      </c>
+      <c r="G158">
+        <v>0.2684191581930727</v>
+      </c>
+      <c r="H158">
+        <v>-0.02418800997719728</v>
+      </c>
+      <c r="I158">
+        <v>0.08693400387125648</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" t="s">
+        <v>43</v>
+      </c>
+      <c r="B159" t="s">
+        <v>22</v>
+      </c>
+      <c r="C159" t="s">
+        <v>44</v>
+      </c>
+      <c r="D159" t="s">
+        <v>78</v>
+      </c>
+      <c r="E159">
+        <v>-0.06998994715846395</v>
+      </c>
+      <c r="F159">
+        <v>0.04781731928592453</v>
+      </c>
+      <c r="G159">
+        <v>0.1432774394327555</v>
+      </c>
+      <c r="H159">
+        <v>-0.1637101707961286</v>
+      </c>
+      <c r="I159">
+        <v>0.02373027647920067</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" t="s">
+        <v>43</v>
+      </c>
+      <c r="B160" t="s">
+        <v>22</v>
+      </c>
+      <c r="C160" t="s">
+        <v>44</v>
+      </c>
+      <c r="D160" t="s">
+        <v>79</v>
+      </c>
+      <c r="E160">
+        <v>0.03937483390888542</v>
+      </c>
+      <c r="F160">
+        <v>0.04788330303635917</v>
+      </c>
+      <c r="G160">
+        <v>0.4109014969605207</v>
+      </c>
+      <c r="H160">
+        <v>-0.05447471550319597</v>
+      </c>
+      <c r="I160">
+        <v>0.1332243833209668</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" t="s">
+        <v>43</v>
+      </c>
+      <c r="B161" t="s">
+        <v>22</v>
+      </c>
+      <c r="C161" t="s">
+        <v>44</v>
+      </c>
+      <c r="D161" t="s">
+        <v>80</v>
+      </c>
+      <c r="E161">
+        <v>-0.00251664310852109</v>
+      </c>
+      <c r="F161">
+        <v>0.04835828364506665</v>
+      </c>
+      <c r="G161">
+        <v>0.9584955355165712</v>
+      </c>
+      <c r="H161">
+        <v>-0.09729713740702405</v>
+      </c>
+      <c r="I161">
+        <v>0.09226385118998186</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" t="s">
+        <v>43</v>
+      </c>
+      <c r="B162" t="s">
+        <v>22</v>
+      </c>
+      <c r="C162" t="s">
+        <v>44</v>
+      </c>
+      <c r="D162" t="s">
+        <v>81</v>
+      </c>
+      <c r="E162">
+        <v>-0.007256962757765945</v>
+      </c>
+      <c r="F162">
+        <v>0.04770609123094292</v>
+      </c>
+      <c r="G162">
+        <v>0.8790937422921308</v>
+      </c>
+      <c r="H162">
+        <v>-0.1007591834135961</v>
+      </c>
+      <c r="I162">
+        <v>0.08624525789806427</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" t="s">
+        <v>43</v>
+      </c>
+      <c r="B163" t="s">
+        <v>22</v>
+      </c>
+      <c r="C163" t="s">
+        <v>44</v>
+      </c>
+      <c r="D163" t="s">
+        <v>82</v>
+      </c>
+      <c r="E163">
+        <v>-0.01154372415914611</v>
+      </c>
+      <c r="F163">
+        <v>0.04781793282483224</v>
+      </c>
+      <c r="G163">
+        <v>0.809237411726385</v>
+      </c>
+      <c r="H163">
+        <v>-0.1052651503109729</v>
+      </c>
+      <c r="I163">
+        <v>0.08217770199268074</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" t="s">
+        <v>43</v>
+      </c>
+      <c r="B164" t="s">
+        <v>22</v>
+      </c>
+      <c r="C164" t="s">
+        <v>44</v>
+      </c>
+      <c r="D164" t="s">
+        <v>83</v>
+      </c>
+      <c r="E164">
+        <v>0.008020413755803771</v>
+      </c>
+      <c r="F164">
+        <v>0.004349980177762456</v>
+      </c>
+      <c r="G164">
+        <v>0.06521496378610095</v>
+      </c>
+      <c r="H164">
+        <v>-0.0005053907260737858</v>
+      </c>
+      <c r="I164">
+        <v>0.01654621823768133</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" t="s">
+        <v>43</v>
+      </c>
+      <c r="B165" t="s">
+        <v>23</v>
+      </c>
+      <c r="C165" t="s">
+        <v>44</v>
+      </c>
+      <c r="D165" t="s">
+        <v>78</v>
+      </c>
+      <c r="E165">
+        <v>1139.967562422161</v>
+      </c>
+      <c r="F165">
+        <v>27995.77243266509</v>
+      </c>
+      <c r="G165">
+        <v>0.9675196949425966</v>
+      </c>
+      <c r="H165">
+        <v>-53730.73812498071</v>
+      </c>
+      <c r="I165">
+        <v>56010.67324982503</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" t="s">
+        <v>43</v>
+      </c>
+      <c r="B166" t="s">
+        <v>23</v>
+      </c>
+      <c r="C166" t="s">
+        <v>44</v>
+      </c>
+      <c r="D166" t="s">
+        <v>79</v>
+      </c>
+      <c r="E166">
+        <v>4725.410282916476</v>
+      </c>
+      <c r="F166">
+        <v>28190.04119985375</v>
+      </c>
+      <c r="G166">
+        <v>0.866876777749799</v>
+      </c>
+      <c r="H166">
+        <v>-50526.05519149717</v>
+      </c>
+      <c r="I166">
+        <v>59976.87575733012</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" t="s">
+        <v>43</v>
+      </c>
+      <c r="B167" t="s">
+        <v>23</v>
+      </c>
+      <c r="C167" t="s">
+        <v>44</v>
+      </c>
+      <c r="D167" t="s">
+        <v>80</v>
+      </c>
+      <c r="E167">
+        <v>-180.9558852570743</v>
+      </c>
+      <c r="F167">
+        <v>27990.90303796541</v>
+      </c>
+      <c r="G167">
+        <v>0.9948418634035252</v>
+      </c>
+      <c r="H167">
+        <v>-55042.11773442207</v>
+      </c>
+      <c r="I167">
+        <v>54680.20596390792</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" t="s">
+        <v>43</v>
+      </c>
+      <c r="B168" t="s">
+        <v>23</v>
+      </c>
+      <c r="C168" t="s">
+        <v>44</v>
+      </c>
+      <c r="D168" t="s">
+        <v>81</v>
+      </c>
+      <c r="E168">
+        <v>158.8851488446963</v>
+      </c>
+      <c r="F168">
+        <v>27989.90822586905</v>
+      </c>
+      <c r="G168">
+        <v>0.9954708202199559</v>
+      </c>
+      <c r="H168">
+        <v>-54700.32690444004</v>
+      </c>
+      <c r="I168">
+        <v>55018.09720212944</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>43</v>
+      </c>
+      <c r="B169" t="s">
+        <v>23</v>
+      </c>
+      <c r="C169" t="s">
+        <v>44</v>
+      </c>
+      <c r="D169" t="s">
+        <v>82</v>
+      </c>
+      <c r="E169">
+        <v>334.8317288301375</v>
+      </c>
+      <c r="F169">
+        <v>27991.56258732806</v>
+      </c>
+      <c r="G169">
+        <v>0.9904560277724772</v>
+      </c>
+      <c r="H169">
+        <v>-54527.62281333166</v>
+      </c>
+      <c r="I169">
+        <v>55197.28627099194</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>43</v>
+      </c>
+      <c r="B170" t="s">
+        <v>23</v>
+      </c>
+      <c r="C170" t="s">
+        <v>44</v>
+      </c>
+      <c r="D170" t="s">
+        <v>83</v>
+      </c>
+      <c r="E170">
+        <v>-256.0708611125975</v>
+      </c>
+      <c r="F170">
+        <v>600.4112400068296</v>
+      </c>
+      <c r="G170">
+        <v>0.669749047904604</v>
+      </c>
+      <c r="H170">
+        <v>-1432.855267439018</v>
+      </c>
+      <c r="I170">
+        <v>920.7135452138231</v>
       </c>
     </row>
   </sheetData>
@@ -4535,33 +6978,33 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B2">
         <v>592</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D2">
         <v>49.35401878167119</v>
@@ -4570,7 +7013,7 @@
         <v>0.6952339291357703</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/analysis(S4)/tables/level2_agent_network_analysis.xlsx
+++ b/analysis(S4)/tables/level2_agent_network_analysis.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="92">
   <si>
     <t>variable</t>
   </si>
@@ -155,82 +155,82 @@
     <t>ols</t>
   </si>
   <si>
-    <t>log_agent_cascade_size_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>reshare_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>depth_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>second_layer_width_avg ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>structural_virality_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>wiener_index_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>centrality_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>agent_deg_centrality_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>avg_out_degree_centrality_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>repeat_exposure_1st_nodes_pct ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>repeat_exposure_2nd_nodes_pct ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>gender_assortativity_mean ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>duration_mean_of_means ~ C(JobCategory) + C(agent_gender) + z_log_article_count_per_agent</t>
-  </si>
-  <si>
-    <t>log_agent_cascade_size_mean ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>reshare_mean ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>depth_mean ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>second_layer_width_avg ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>structural_virality_mean ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>wiener_index_mean ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>centrality_mean ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>agent_deg_centrality_mean ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>avg_out_degree_centrality_mean ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>repeat_exposure_1st_nodes_pct ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>repeat_exposure_2nd_nodes_pct ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>gender_assortativity_mean ~ C(JobCategory) + C(agent_gender)</t>
-  </si>
-  <si>
-    <t>duration_mean_of_means ~ C(JobCategory) + C(agent_gender)</t>
+    <t>log_agent_cascade_size_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>reshare_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>depth_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>second_layer_width_avg ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>structural_virality_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>wiener_index_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>centrality_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>agent_deg_centrality_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>avg_out_degree_centrality_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>repeat_exposure_1st_nodes_pct ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>repeat_exposure_2nd_nodes_pct ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>gender_assortativity_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>duration_mean_of_means ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender) + z_log_article_count_per_agent</t>
+  </si>
+  <si>
+    <t>log_agent_cascade_size_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>reshare_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>depth_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>second_layer_width_avg ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>structural_virality_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>wiener_index_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>centrality_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>agent_deg_centrality_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>avg_out_degree_centrality_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>repeat_exposure_1st_nodes_pct ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>repeat_exposure_2nd_nodes_pct ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>gender_assortativity_mean ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
+  </si>
+  <si>
+    <t>duration_mean_of_means ~ C(JobCategory, Treatment(reference='3')) + C(agent_gender)</t>
   </si>
   <si>
     <t>term</t>
@@ -257,16 +257,13 @@
     <t>Intercept</t>
   </si>
   <si>
-    <t>C(JobCategory)[T.1]</t>
-  </si>
-  <si>
-    <t>C(JobCategory)[T.2]</t>
-  </si>
-  <si>
-    <t>C(JobCategory)[T.3]</t>
-  </si>
-  <si>
-    <t>C(JobCategory)[T.4]</t>
+    <t>C(JobCategory, Treatment(reference='3'))[T.1]</t>
+  </si>
+  <si>
+    <t>C(JobCategory, Treatment(reference='3'))[T.2]</t>
+  </si>
+  <si>
+    <t>C(JobCategory, Treatment(reference='3'))[T.4]</t>
   </si>
   <si>
     <t>C(agent_gender)[T.1]</t>
@@ -1309,16 +1306,16 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E2">
-        <v>1682.809011980455</v>
+        <v>1678.989232768039</v>
       </c>
       <c r="F2">
-        <v>1713.493558424643</v>
+        <v>1705.280128872475</v>
       </c>
       <c r="G2">
-        <v>0.1879215395098323</v>
+        <v>0.1892691619296732</v>
       </c>
       <c r="I2" t="s">
         <v>45</v>
@@ -1335,16 +1332,16 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E3">
-        <v>-1285.250084137164</v>
+        <v>-1284.056250011543</v>
       </c>
       <c r="F3">
-        <v>-1254.565537692976</v>
+        <v>-1257.765353907106</v>
       </c>
       <c r="G3">
-        <v>0.02624373600031182</v>
+        <v>0.02780317985218261</v>
       </c>
       <c r="I3" t="s">
         <v>46</v>
@@ -1361,16 +1358,16 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E4">
-        <v>1670.469358975709</v>
+        <v>1666.670423771747</v>
       </c>
       <c r="F4">
-        <v>1701.153905419897</v>
+        <v>1692.961319876184</v>
       </c>
       <c r="G4">
-        <v>0.1174013120892701</v>
+        <v>0.1188673394577592</v>
       </c>
       <c r="I4" t="s">
         <v>47</v>
@@ -1387,16 +1384,16 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E5">
-        <v>4728.502509114405</v>
+        <v>4719.537977373047</v>
       </c>
       <c r="F5">
-        <v>4759.187055558593</v>
+        <v>4745.828873477484</v>
       </c>
       <c r="G5">
-        <v>0.2402500083892802</v>
+        <v>0.2415339526797949</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -1413,16 +1410,16 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E6">
-        <v>1143.901950142811</v>
+        <v>1140.992486913229</v>
       </c>
       <c r="F6">
-        <v>1174.586496586999</v>
+        <v>1167.283383017666</v>
       </c>
       <c r="G6">
-        <v>0.07325759903729168</v>
+        <v>0.07478173654277764</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
@@ -1439,16 +1436,16 @@
         <v>44</v>
       </c>
       <c r="D7">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E7">
-        <v>18379.56213881192</v>
+        <v>18347.5383847231</v>
       </c>
       <c r="F7">
-        <v>18410.24668525611</v>
+        <v>18373.82928082754</v>
       </c>
       <c r="G7">
-        <v>-0.002015647558125444</v>
+        <v>-0.000332707993218051</v>
       </c>
       <c r="I7" t="s">
         <v>50</v>
@@ -1465,16 +1462,16 @@
         <v>44</v>
       </c>
       <c r="D8">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E8">
-        <v>135.0932468713695</v>
+        <v>133.8878523973137</v>
       </c>
       <c r="F8">
-        <v>165.7777933155575</v>
+        <v>160.1787485017503</v>
       </c>
       <c r="G8">
-        <v>0.143178738853398</v>
+        <v>0.144567844826054</v>
       </c>
       <c r="I8" t="s">
         <v>51</v>
@@ -1491,16 +1488,16 @@
         <v>44</v>
       </c>
       <c r="D9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E9">
-        <v>-133.7510497451565</v>
+        <v>-134.5023153397919</v>
       </c>
       <c r="F9">
-        <v>-103.0665033009684</v>
+        <v>-108.2114192353554</v>
       </c>
       <c r="G9">
-        <v>0.1617271265036677</v>
+        <v>0.1628801171073966</v>
       </c>
       <c r="I9" t="s">
         <v>52</v>
@@ -1517,16 +1514,16 @@
         <v>44</v>
       </c>
       <c r="D10">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E10">
-        <v>-1466.477954215737</v>
+        <v>-1464.9779919312</v>
       </c>
       <c r="F10">
-        <v>-1435.793407771549</v>
+        <v>-1438.687095826763</v>
       </c>
       <c r="G10">
-        <v>0.08664018570785981</v>
+        <v>0.088161394742166</v>
       </c>
       <c r="I10" t="s">
         <v>53</v>
@@ -1543,16 +1540,16 @@
         <v>44</v>
       </c>
       <c r="D11">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E11">
-        <v>287.9345728706755</v>
+        <v>286.4710004810806</v>
       </c>
       <c r="F11">
-        <v>318.6191193148636</v>
+        <v>312.7618965855172</v>
       </c>
       <c r="G11">
-        <v>0.3821191959473504</v>
+        <v>0.3825364734455585</v>
       </c>
       <c r="I11" t="s">
         <v>54</v>
@@ -1569,16 +1566,16 @@
         <v>44</v>
       </c>
       <c r="D12">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E12">
-        <v>316.6192648373155</v>
+        <v>315.1072385761552</v>
       </c>
       <c r="F12">
-        <v>347.3038112815036</v>
+        <v>341.3981346805917</v>
       </c>
       <c r="G12">
-        <v>0.1535550496771568</v>
+        <v>0.1546750357948845</v>
       </c>
       <c r="I12" t="s">
         <v>55</v>
@@ -1595,16 +1592,16 @@
         <v>44</v>
       </c>
       <c r="D13">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E13">
-        <v>-1855.070009385509</v>
+        <v>-1852.913641602374</v>
       </c>
       <c r="F13">
-        <v>-1824.385462941321</v>
+        <v>-1826.622745497938</v>
       </c>
       <c r="G13">
-        <v>0.0804533629656693</v>
+        <v>0.08199309620462147</v>
       </c>
       <c r="I13" t="s">
         <v>56</v>
@@ -1621,16 +1618,16 @@
         <v>44</v>
       </c>
       <c r="D14">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E14">
-        <v>12411.87220504295</v>
+        <v>12389.92900827468</v>
       </c>
       <c r="F14">
-        <v>12442.55675148713</v>
+        <v>12416.21990437912</v>
       </c>
       <c r="G14">
-        <v>0.01651921089452346</v>
+        <v>0.01817254890106201</v>
       </c>
       <c r="I14" t="s">
         <v>57</v>
@@ -1647,16 +1644,16 @@
         <v>44</v>
       </c>
       <c r="D15">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E15">
-        <v>1704.097495534252</v>
+        <v>1700.238377667185</v>
       </c>
       <c r="F15">
-        <v>1730.398535343556</v>
+        <v>1722.147457754216</v>
       </c>
       <c r="G15">
-        <v>0.1567801877439871</v>
+        <v>0.1581794884016653</v>
       </c>
       <c r="I15" t="s">
         <v>58</v>
@@ -1673,16 +1670,16 @@
         <v>44</v>
       </c>
       <c r="D16">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E16">
-        <v>-1284.046234719973</v>
+        <v>-1282.857812502151</v>
       </c>
       <c r="F16">
-        <v>-1257.745194910669</v>
+        <v>-1260.948732415121</v>
       </c>
       <c r="G16">
-        <v>0.02263028852656712</v>
+        <v>0.0241955192150981</v>
       </c>
       <c r="I16" t="s">
         <v>59</v>
@@ -1699,16 +1696,16 @@
         <v>44</v>
       </c>
       <c r="D17">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E17">
-        <v>1668.583946409904</v>
+        <v>1664.784817646088</v>
       </c>
       <c r="F17">
-        <v>1694.884986219208</v>
+        <v>1686.693897733118</v>
       </c>
       <c r="G17">
-        <v>0.1187368925429509</v>
+        <v>0.1202007014654748</v>
       </c>
       <c r="I17" t="s">
         <v>60</v>
@@ -1725,16 +1722,16 @@
         <v>44</v>
       </c>
       <c r="D18">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E18">
-        <v>4726.502551324539</v>
+        <v>4717.538019511881</v>
       </c>
       <c r="F18">
-        <v>4752.803591133843</v>
+        <v>4739.447099598911</v>
       </c>
       <c r="G18">
-        <v>0.2415464560030287</v>
+        <v>0.2428282093537207</v>
       </c>
       <c r="I18" t="s">
         <v>61</v>
@@ -1751,16 +1748,16 @@
         <v>44</v>
       </c>
       <c r="D19">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E19">
-        <v>1146.734311028757</v>
+        <v>1143.816685027409</v>
       </c>
       <c r="F19">
-        <v>1173.035350838062</v>
+        <v>1165.725765114439</v>
       </c>
       <c r="G19">
-        <v>0.06725628703558473</v>
+        <v>0.06879029440857054</v>
       </c>
       <c r="I19" t="s">
         <v>62</v>
@@ -1777,16 +1774,16 @@
         <v>44</v>
       </c>
       <c r="D20">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E20">
-        <v>18377.64196954389</v>
+        <v>18345.61808060587</v>
       </c>
       <c r="F20">
-        <v>18403.9430093532</v>
+        <v>18367.52716069289</v>
       </c>
       <c r="G20">
-        <v>-0.0004406227761815096</v>
+        <v>0.001239671449276059</v>
       </c>
       <c r="I20" t="s">
         <v>63</v>
@@ -1803,16 +1800,16 @@
         <v>44</v>
       </c>
       <c r="D21">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E21">
-        <v>148.6850518228562</v>
+        <v>147.4533198404365</v>
       </c>
       <c r="F21">
-        <v>174.9860916321602</v>
+        <v>169.362399927467</v>
       </c>
       <c r="G21">
-        <v>0.121813575713323</v>
+        <v>0.123237319570297</v>
       </c>
       <c r="I21" t="s">
         <v>64</v>
@@ -1829,16 +1826,16 @@
         <v>44</v>
       </c>
       <c r="D22">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E22">
-        <v>-111.8379388847816</v>
+        <v>-112.6295982477627</v>
       </c>
       <c r="F22">
-        <v>-85.53689907547755</v>
+        <v>-90.72051816073223</v>
       </c>
       <c r="G22">
-        <v>0.12866240351921</v>
+        <v>0.1298608725299364</v>
       </c>
       <c r="I22" t="s">
         <v>65</v>
@@ -1855,16 +1852,16 @@
         <v>44</v>
       </c>
       <c r="D23">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E23">
-        <v>-1461.616772264873</v>
+        <v>-1460.128399814712</v>
       </c>
       <c r="F23">
-        <v>-1435.315732455569</v>
+        <v>-1438.219319727681</v>
       </c>
       <c r="G23">
-        <v>0.0775697197668922</v>
+        <v>0.07910603574428776</v>
       </c>
       <c r="I23" t="s">
         <v>66</v>
@@ -1881,16 +1878,16 @@
         <v>44</v>
       </c>
       <c r="D24">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E24">
-        <v>552.4223784124376</v>
+        <v>550.5086577026707</v>
       </c>
       <c r="F24">
-        <v>578.7234182217417</v>
+        <v>572.4177377897012</v>
       </c>
       <c r="G24">
-        <v>0.03248014855708414</v>
+        <v>0.0331335500876524</v>
       </c>
       <c r="I24" t="s">
         <v>67</v>
@@ -1907,16 +1904,16 @@
         <v>44</v>
       </c>
       <c r="D25">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E25">
-        <v>406.4485505008395</v>
+        <v>404.7814072030853</v>
       </c>
       <c r="F25">
-        <v>432.7495903101435</v>
+        <v>426.6904872901158</v>
       </c>
       <c r="G25">
-        <v>0.0132129497441057</v>
+        <v>0.01451863158084887</v>
       </c>
       <c r="I25" t="s">
         <v>68</v>
@@ -1933,16 +1930,16 @@
         <v>44</v>
       </c>
       <c r="D26">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E26">
-        <v>-1851.736413295326</v>
+        <v>-1849.589054965046</v>
       </c>
       <c r="F26">
-        <v>-1825.435373486022</v>
+        <v>-1827.679974878015</v>
       </c>
       <c r="G26">
-        <v>0.0737147123043056</v>
+        <v>0.07526572906493134</v>
       </c>
       <c r="I26" t="s">
         <v>69</v>
@@ -1959,16 +1956,16 @@
         <v>44</v>
       </c>
       <c r="D27">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E27">
-        <v>12410.27141954738</v>
+        <v>12388.32754843029</v>
       </c>
       <c r="F27">
-        <v>12436.57245935668</v>
+        <v>12410.23662851732</v>
       </c>
       <c r="G27">
-        <v>0.01753520511231776</v>
+        <v>0.01918683512224539</v>
       </c>
       <c r="I27" t="s">
         <v>70</v>
@@ -1981,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J170"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="12.7109375" customWidth="1"/>
@@ -2034,19 +2031,19 @@
         <v>78</v>
       </c>
       <c r="E2">
-        <v>2.581554485848208</v>
+        <v>2.607599478788469</v>
       </c>
       <c r="F2">
-        <v>4.843220189873866</v>
+        <v>0.06687571807104922</v>
       </c>
       <c r="G2">
-        <v>0.5940166971211924</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-6.910982655501811</v>
+        <v>2.476525479928958</v>
       </c>
       <c r="I2">
-        <v>12.07409162719823</v>
+        <v>2.73867347764798</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2063,19 +2060,19 @@
         <v>79</v>
       </c>
       <c r="E3">
-        <v>1.436155757853252</v>
+        <v>1.410110764912985</v>
       </c>
       <c r="F3">
-        <v>4.84582362806476</v>
+        <v>0.1900019605308207</v>
       </c>
       <c r="G3">
-        <v>0.7669476894057112</v>
+        <v>1.157496479587797E-13</v>
       </c>
       <c r="H3">
-        <v>-8.061484028586895</v>
+        <v>1.037713765280575</v>
       </c>
       <c r="I3">
-        <v>10.9337955442934</v>
+        <v>1.782507764545394</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2092,19 +2089,19 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>-0.1752569525442766</v>
+        <v>-0.2013019454845434</v>
       </c>
       <c r="F4">
-        <v>4.844031006719916</v>
+        <v>0.1155982400412816</v>
       </c>
       <c r="G4">
-        <v>0.971138847931409</v>
+        <v>0.08161474549535815</v>
       </c>
       <c r="H4">
-        <v>-9.669383265710614</v>
+        <v>-0.4278703326416713</v>
       </c>
       <c r="I4">
-        <v>9.31886936062206</v>
+        <v>0.02526644167258443</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2121,19 +2118,19 @@
         <v>81</v>
       </c>
       <c r="E5">
-        <v>0.02604499294026585</v>
+        <v>0.07808189428070071</v>
       </c>
       <c r="F5">
-        <v>4.842828629449699</v>
+        <v>0.13836250753343</v>
       </c>
       <c r="G5">
-        <v>0.9957089545867054</v>
+        <v>0.5725306481775643</v>
       </c>
       <c r="H5">
-        <v>-9.465724704080616</v>
+        <v>-0.1931036372954739</v>
       </c>
       <c r="I5">
-        <v>9.517814689961147</v>
+        <v>0.3492674258568754</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2150,19 +2147,19 @@
         <v>82</v>
       </c>
       <c r="E6">
-        <v>0.1041268872209697</v>
+        <v>-0.1157206030890138</v>
       </c>
       <c r="F6">
-        <v>4.843780556781342</v>
+        <v>0.08197539506374624</v>
       </c>
       <c r="G6">
-        <v>0.9828491740696684</v>
+        <v>0.1580529106711772</v>
       </c>
       <c r="H6">
-        <v>-9.389508553085831</v>
+        <v>-0.2763894250323989</v>
       </c>
       <c r="I6">
-        <v>9.59776232752777</v>
+        <v>0.04494821885437138</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2179,19 +2176,22 @@
         <v>83</v>
       </c>
       <c r="E7">
-        <v>-0.1157206030890144</v>
+        <v>0.2159646841937135</v>
       </c>
       <c r="F7">
-        <v>0.08197539506374638</v>
+        <v>0.04312303627184774</v>
       </c>
       <c r="G7">
-        <v>0.1580529106711759</v>
+        <v>5.496860876284848E-07</v>
       </c>
       <c r="H7">
-        <v>-0.2763894250323998</v>
+        <v>0.1314450861968775</v>
       </c>
       <c r="I7">
-        <v>0.04494821885437104</v>
+        <v>0.3004842821905495</v>
+      </c>
+      <c r="J7">
+        <v>0.2159646841937135</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2199,31 +2199,28 @@
         <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E8">
-        <v>0.2159646841937136</v>
+        <v>0.08745647480613739</v>
       </c>
       <c r="F8">
-        <v>0.04312303627184787</v>
+        <v>0.005950383436398843</v>
       </c>
       <c r="G8">
-        <v>5.496860876285195E-07</v>
+        <v>6.676530587269032E-49</v>
       </c>
       <c r="H8">
-        <v>0.1314450861968774</v>
+        <v>0.07579393757659197</v>
       </c>
       <c r="I8">
-        <v>0.3004842821905498</v>
-      </c>
-      <c r="J8">
-        <v>0.2159646841937136</v>
+        <v>0.0991190120356828</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2237,22 +2234,22 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E9">
-        <v>0.1135080265542597</v>
+        <v>0.03186002780709899</v>
       </c>
       <c r="F9">
-        <v>2.65790669570806</v>
+        <v>0.01104368315164425</v>
       </c>
       <c r="G9">
-        <v>0.9659360576211592</v>
+        <v>0.00391526040813439</v>
       </c>
       <c r="H9">
-        <v>-5.095893371301398</v>
+        <v>0.01021480657320447</v>
       </c>
       <c r="I9">
-        <v>5.322909424409917</v>
+        <v>0.05350524904099352</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2266,22 +2263,22 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10">
-        <v>0.005808476058976752</v>
+        <v>-0.01844427677018528</v>
       </c>
       <c r="F10">
-        <v>2.65791707029241</v>
+        <v>0.0111981066554101</v>
       </c>
       <c r="G10">
-        <v>0.9982563452666791</v>
+        <v>0.0995397817179646</v>
       </c>
       <c r="H10">
-        <v>-5.203613255608362</v>
+        <v>-0.04039216250982736</v>
       </c>
       <c r="I10">
-        <v>5.215230207726316</v>
+        <v>0.003503608969456808</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2295,22 +2292,22 @@
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11">
-        <v>-0.04449582851830746</v>
+        <v>-0.01449038309265509</v>
       </c>
       <c r="F11">
-        <v>2.65792247313997</v>
+        <v>0.007932962123554226</v>
       </c>
       <c r="G11">
-        <v>0.9866433740158967</v>
+        <v>0.06775927945099747</v>
       </c>
       <c r="H11">
-        <v>-5.253928149572278</v>
+        <v>-0.03003870314554176</v>
       </c>
       <c r="I11">
-        <v>5.164936492535663</v>
+        <v>0.001057936960231579</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2324,22 +2321,22 @@
         <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12">
-        <v>-0.02605155174812224</v>
+        <v>0.009030108174118864</v>
       </c>
       <c r="F12">
-        <v>2.657899989213237</v>
+        <v>0.006838468690685666</v>
       </c>
       <c r="G12">
-        <v>0.9921796161662582</v>
+        <v>0.1866725141520355</v>
       </c>
       <c r="H12">
-        <v>-5.235439805115464</v>
+        <v>-0.004373044169029821</v>
       </c>
       <c r="I12">
-        <v>5.183336701619219</v>
+        <v>0.02243326051726755</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2353,22 +2350,25 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13">
-        <v>-0.04054193484077751</v>
+        <v>-0.006475280580781524</v>
       </c>
       <c r="F13">
-        <v>2.657904179848838</v>
+        <v>0.003309266646405933</v>
       </c>
       <c r="G13">
-        <v>0.9878300618210633</v>
+        <v>0.05038138010183921</v>
       </c>
       <c r="H13">
-        <v>-5.249938401702971</v>
+        <v>-0.0129613240229768</v>
       </c>
       <c r="I13">
-        <v>5.168854532021416</v>
+        <v>1.076286141375119E-05</v>
+      </c>
+      <c r="J13">
+        <v>-0.006475280580781524</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2376,28 +2376,28 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E14">
-        <v>0.009030108174118772</v>
+        <v>1.576447623583423</v>
       </c>
       <c r="F14">
-        <v>0.00683846869068568</v>
+        <v>0.06410131238767312</v>
       </c>
       <c r="G14">
-        <v>0.1866725141520408</v>
+        <v>1.498609121827094E-133</v>
       </c>
       <c r="H14">
-        <v>-0.004373044169029941</v>
+        <v>1.450811359941832</v>
       </c>
       <c r="I14">
-        <v>0.02243326051726748</v>
+        <v>1.702083887225013</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2405,31 +2405,28 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E15">
-        <v>-0.006475280580781555</v>
+        <v>1.215594619970948</v>
       </c>
       <c r="F15">
-        <v>0.00330926664640594</v>
+        <v>0.2329720079335104</v>
       </c>
       <c r="G15">
-        <v>0.05038138010183867</v>
+        <v>1.810890189076352E-07</v>
       </c>
       <c r="H15">
-        <v>-0.01296132402297684</v>
+        <v>0.7589778750152881</v>
       </c>
       <c r="I15">
-        <v>1.076286141373471E-05</v>
-      </c>
-      <c r="J15">
-        <v>-0.006475280580781555</v>
+        <v>1.672211364926608</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2443,22 +2440,22 @@
         <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E16">
-        <v>1.809111659956468</v>
+        <v>-0.1314480598012699</v>
       </c>
       <c r="F16">
-        <v>3.580286166408491</v>
+        <v>0.1249365235454225</v>
       </c>
       <c r="G16">
-        <v>0.6133495040547507</v>
+        <v>0.2927450676593039</v>
       </c>
       <c r="H16">
-        <v>-5.208120280551152</v>
+        <v>-0.3763191463039385</v>
       </c>
       <c r="I16">
-        <v>8.826343600464089</v>
+        <v>0.1134230267013987</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2472,22 +2469,22 @@
         <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17">
-        <v>0.982930583597903</v>
+        <v>0.02462688385629596</v>
       </c>
       <c r="F17">
-        <v>3.585500979078077</v>
+        <v>0.1152915790038367</v>
       </c>
       <c r="G17">
-        <v>0.7839767469888942</v>
+        <v>0.8308549232447497</v>
       </c>
       <c r="H17">
-        <v>-6.044522201928229</v>
+        <v>-0.2013404587119782</v>
       </c>
       <c r="I17">
-        <v>8.010383369124035</v>
+        <v>0.2505942264245701</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2501,22 +2498,22 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E18">
-        <v>-0.3641120961743143</v>
+        <v>-0.005654401352395965</v>
       </c>
       <c r="F18">
-        <v>3.581609716968195</v>
+        <v>0.08032162641572604</v>
       </c>
       <c r="G18">
-        <v>0.9190253002735208</v>
+        <v>0.9438776807870365</v>
       </c>
       <c r="H18">
-        <v>-7.383938148110673</v>
+        <v>-0.1630818963069001</v>
       </c>
       <c r="I18">
-        <v>6.655713955762044</v>
+        <v>0.1517730936021081</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2530,22 +2527,25 @@
         <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E19">
-        <v>-0.2326640363730444</v>
+        <v>0.01484534470383341</v>
       </c>
       <c r="F19">
-        <v>3.579668318101489</v>
+        <v>0.0416406065252538</v>
       </c>
       <c r="G19">
-        <v>0.948177204106056</v>
+        <v>0.7214577281909047</v>
       </c>
       <c r="H19">
-        <v>-7.248685016451033</v>
+        <v>-0.06676874438006761</v>
       </c>
       <c r="I19">
-        <v>6.783356943704944</v>
+        <v>0.09645943378773442</v>
+      </c>
+      <c r="J19">
+        <v>0.01484534470383341</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2553,28 +2553,28 @@
         <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E20">
-        <v>-0.2080371525167505</v>
+        <v>3.950418028700465</v>
       </c>
       <c r="F20">
-        <v>3.580445018825533</v>
+        <v>0.6962672188964291</v>
       </c>
       <c r="G20">
-        <v>0.9536660162381982</v>
+        <v>1.397379102343999E-08</v>
       </c>
       <c r="H20">
-        <v>-7.225580438040631</v>
+        <v>2.585759356047598</v>
       </c>
       <c r="I20">
-        <v>6.80950613300713</v>
+        <v>5.315076701353332</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -2582,28 +2582,28 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E21">
-        <v>-0.005654401352396664</v>
+        <v>24.37014222861703</v>
       </c>
       <c r="F21">
-        <v>0.08032162641572622</v>
+        <v>4.430676798576509</v>
       </c>
       <c r="G21">
-        <v>0.9438776807870297</v>
+        <v>3.791016106616431E-08</v>
       </c>
       <c r="H21">
-        <v>-0.1630818963069011</v>
+        <v>15.68617527626984</v>
       </c>
       <c r="I21">
-        <v>0.1517730936021078</v>
+        <v>33.05410918096422</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2611,31 +2611,28 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
         <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E22">
-        <v>0.01484534470383334</v>
+        <v>-2.045786380029439</v>
       </c>
       <c r="F22">
-        <v>0.04164060652525391</v>
+        <v>0.729223767127131</v>
       </c>
       <c r="G22">
-        <v>0.7214577281909065</v>
+        <v>0.005024946313200672</v>
       </c>
       <c r="H22">
-        <v>-0.06676874438006788</v>
+        <v>-3.475038700269239</v>
       </c>
       <c r="I22">
-        <v>0.09645943378773456</v>
-      </c>
-      <c r="J22">
-        <v>0.01484534470383334</v>
+        <v>-0.6165340597896385</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2649,22 +2646,22 @@
         <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E23">
-        <v>5.555179445128314</v>
+        <v>0.422641539040771</v>
       </c>
       <c r="F23">
-        <v>269.4764176503293</v>
+        <v>0.9601605605948506</v>
       </c>
       <c r="G23">
-        <v>0.9835530023959146</v>
+        <v>0.6598082045717215</v>
       </c>
       <c r="H23">
-        <v>-522.608893832391</v>
+        <v>-1.459238579100924</v>
       </c>
       <c r="I23">
-        <v>533.7192527226475</v>
+        <v>2.304521657182466</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2678,22 +2675,22 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E24">
-        <v>22.7653808121892</v>
+        <v>0.5199145452824523</v>
       </c>
       <c r="F24">
-        <v>269.5073884561654</v>
+        <v>1.038061922799087</v>
       </c>
       <c r="G24">
-        <v>0.9326824835644835</v>
+        <v>0.6164758588179329</v>
       </c>
       <c r="H24">
-        <v>-505.4593941293408</v>
+        <v>-1.514649437126157</v>
       </c>
       <c r="I24">
-        <v>550.9901557537191</v>
+        <v>2.554478527691062</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2707,22 +2704,25 @@
         <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E25">
-        <v>-3.650547796457277</v>
+        <v>-0.003770545471490936</v>
       </c>
       <c r="F25">
-        <v>269.4758025104354</v>
+        <v>0.415037700642568</v>
       </c>
       <c r="G25">
-        <v>0.9891915095465756</v>
+        <v>0.992751456964142</v>
       </c>
       <c r="H25">
-        <v>-531.8134154219389</v>
+        <v>-0.8172294909572406</v>
       </c>
       <c r="I25">
-        <v>524.5123198290242</v>
+        <v>0.8096884000142588</v>
+      </c>
+      <c r="J25">
+        <v>-0.003770545471490936</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2730,28 +2730,28 @@
         <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
         <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E26">
-        <v>-1.604761416427841</v>
+        <v>1.67512974685539</v>
       </c>
       <c r="F26">
-        <v>269.4751401946498</v>
+        <v>0.04434393101921037</v>
       </c>
       <c r="G26">
-        <v>0.9952485161004991</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>-529.7663309268233</v>
+        <v>1.588217239124809</v>
       </c>
       <c r="I26">
-        <v>526.5568080939676</v>
+        <v>1.762042254585971</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2759,28 +2759,28 @@
         <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
         <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E27">
-        <v>-1.182119877387055</v>
+        <v>0.5787521103747113</v>
       </c>
       <c r="F27">
-        <v>269.4752503130923</v>
+        <v>0.1344697072671422</v>
       </c>
       <c r="G27">
-        <v>0.9964998931329427</v>
+        <v>1.677727051290463E-05</v>
       </c>
       <c r="H27">
-        <v>-529.343905215964</v>
+        <v>0.3151963271194687</v>
       </c>
       <c r="I27">
-        <v>526.9796654611898</v>
+        <v>0.842307893629954</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2788,28 +2788,28 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
         <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E28">
-        <v>0.5199145452824512</v>
+        <v>-0.006839964578498099</v>
       </c>
       <c r="F28">
-        <v>1.03806192279909</v>
+        <v>0.09217810604248823</v>
       </c>
       <c r="G28">
-        <v>0.6164758588179348</v>
+        <v>0.9408482322974836</v>
       </c>
       <c r="H28">
-        <v>-1.514649437126164</v>
+        <v>-0.187505732584889</v>
       </c>
       <c r="I28">
-        <v>2.554478527691066</v>
+        <v>0.1738258034278928</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2817,31 +2817,28 @@
         <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E29">
-        <v>-0.003770545471494469</v>
+        <v>0.1050979628438503</v>
       </c>
       <c r="F29">
-        <v>0.4150377006425692</v>
+        <v>0.06764469476895991</v>
       </c>
       <c r="G29">
-        <v>0.9927514569641352</v>
+        <v>0.1202616357812142</v>
       </c>
       <c r="H29">
-        <v>-0.8172294909572466</v>
+        <v>-0.02748320264851609</v>
       </c>
       <c r="I29">
-        <v>0.8096884000142577</v>
-      </c>
-      <c r="J29">
-        <v>-0.003770545471494469</v>
+        <v>0.2376791283362168</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2855,22 +2852,22 @@
         <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E30">
-        <v>1.776708439799271</v>
+        <v>-0.06239983100884945</v>
       </c>
       <c r="F30">
-        <v>5.789873997688462</v>
+        <v>0.05296431264065519</v>
       </c>
       <c r="G30">
-        <v>0.7589462941354587</v>
+        <v>0.2387373681027691</v>
       </c>
       <c r="H30">
-        <v>-9.571236070695059</v>
+        <v>-0.1662079762504531</v>
       </c>
       <c r="I30">
-        <v>13.1246529502936</v>
+        <v>0.04140831423275425</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2884,22 +2881,25 @@
         <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E31">
-        <v>0.4771734174308322</v>
+        <v>0.06191857209475875</v>
       </c>
       <c r="F31">
-        <v>5.790846134654816</v>
+        <v>0.03029851709217945</v>
       </c>
       <c r="G31">
-        <v>0.9343275792702003</v>
+        <v>0.04099137407260713</v>
       </c>
       <c r="H31">
-        <v>-10.87267644650559</v>
+        <v>0.002534569809115796</v>
       </c>
       <c r="I31">
-        <v>11.82702328136726</v>
+        <v>0.1213025743804017</v>
+      </c>
+      <c r="J31">
+        <v>0.06191857209475875</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2907,28 +2907,28 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E32">
-        <v>-0.1084186575223765</v>
+        <v>54867.65057428425</v>
       </c>
       <c r="F32">
-        <v>5.790404359733468</v>
+        <v>46235.26676806152</v>
       </c>
       <c r="G32">
-        <v>0.9850614027492866</v>
+        <v>0.2353437603961533</v>
       </c>
       <c r="H32">
-        <v>-11.45740265852369</v>
+        <v>-35751.80710671795</v>
       </c>
       <c r="I32">
-        <v>11.24056534347893</v>
+        <v>145487.1082552864</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2936,28 +2936,28 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E33">
-        <v>-0.1015786929438795</v>
+        <v>323732.4477977497</v>
       </c>
       <c r="F33">
-        <v>5.789663400135001</v>
+        <v>261131.7194258108</v>
       </c>
       <c r="G33">
-        <v>0.9860019646490408</v>
+        <v>0.2150758136177654</v>
       </c>
       <c r="H33">
-        <v>-11.44911043981819</v>
+        <v>-188076.3174978578</v>
       </c>
       <c r="I33">
-        <v>11.24595305393043</v>
+        <v>835541.2130933573</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2965,28 +2965,28 @@
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
         <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E34">
-        <v>0.003519269899969979</v>
+        <v>-102691.7738906537</v>
       </c>
       <c r="F34">
-        <v>5.789842981533295</v>
+        <v>82377.17203416531</v>
       </c>
       <c r="G34">
-        <v>0.9995150177725832</v>
+        <v>0.2125424594562081</v>
       </c>
       <c r="H34">
-        <v>-11.34436445004729</v>
+        <v>-264148.0642258778</v>
       </c>
       <c r="I34">
-        <v>11.35140298984723</v>
+        <v>58764.5164445705</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2994,28 +2994,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E35">
-        <v>-0.06239983100885005</v>
+        <v>-99977.59608845606</v>
       </c>
       <c r="F35">
-        <v>0.05296431264065531</v>
+        <v>62446.25631674015</v>
       </c>
       <c r="G35">
-        <v>0.2387373681027658</v>
+        <v>0.109372876780697</v>
       </c>
       <c r="H35">
-        <v>-0.166207976250454</v>
+        <v>-222370.0094386236</v>
       </c>
       <c r="I35">
-        <v>0.04140831423275387</v>
+        <v>22414.81726171149</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -3023,31 +3023,28 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E36">
-        <v>0.06191857209475883</v>
+        <v>76323.78172176713</v>
       </c>
       <c r="F36">
-        <v>0.03029851709217952</v>
+        <v>98354.75623228936</v>
       </c>
       <c r="G36">
-        <v>0.04099137407260735</v>
+        <v>0.4377460389810165</v>
       </c>
       <c r="H36">
-        <v>0.002534569809115733</v>
+        <v>-116447.9982017365</v>
       </c>
       <c r="I36">
-        <v>0.1213025743804019</v>
-      </c>
-      <c r="J36">
-        <v>0.06191857209475883</v>
+        <v>269095.5616452707</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -3061,22 +3058,25 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E37">
-        <v>-102827.1851616676</v>
+        <v>16674.08522827148</v>
       </c>
       <c r="F37">
-        <v>5136968.056213175</v>
+        <v>16636.1203885993</v>
       </c>
       <c r="G37">
-        <v>0.9840297342843385</v>
+        <v>0.3162073783396494</v>
       </c>
       <c r="H37">
-        <v>-10171099.56507222</v>
+        <v>-15932.11157585564</v>
       </c>
       <c r="I37">
-        <v>9965445.194748884</v>
+        <v>49280.2820323986</v>
+      </c>
+      <c r="J37">
+        <v>16674.08522827148</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -3084,28 +3084,28 @@
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
         <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E38">
-        <v>481427.2835337015</v>
+        <v>0.7324505753168096</v>
       </c>
       <c r="F38">
-        <v>5142903.629850134</v>
+        <v>0.01846450762142312</v>
       </c>
       <c r="G38">
-        <v>0.9254189541031496</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>-9598478.606932875</v>
+        <v>0.6962608053865549</v>
       </c>
       <c r="I38">
-        <v>10561333.17400028</v>
+        <v>0.7686403452470643</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -3113,28 +3113,28 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39">
-        <v>55003.06184529857</v>
+        <v>-0.3017378268096143</v>
       </c>
       <c r="F39">
-        <v>5136213.467865487</v>
+        <v>0.03260666435406239</v>
       </c>
       <c r="G39">
-        <v>0.9914557182401269</v>
+        <v>2.165087209099173E-20</v>
       </c>
       <c r="H39">
-        <v>-10011790.35208063</v>
+        <v>-0.3656457145995626</v>
       </c>
       <c r="I39">
-        <v>10121796.47577123</v>
+        <v>-0.237829939019666</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3142,28 +3142,28 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C40" t="s">
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E40">
-        <v>157694.8357359517</v>
+        <v>0.05326761171808512</v>
       </c>
       <c r="F40">
-        <v>5137036.535599635</v>
+        <v>0.04227783279658636</v>
       </c>
       <c r="G40">
-        <v>0.9755106829871953</v>
+        <v>0.2076903329209864</v>
       </c>
       <c r="H40">
-        <v>-9910711.761305744</v>
+        <v>-0.02959541790763046</v>
       </c>
       <c r="I40">
-        <v>10226101.43277765</v>
+        <v>0.1361306413438007</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -3171,28 +3171,28 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
         <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E41">
-        <v>57717.2396474963</v>
+        <v>0.06486132445897048</v>
       </c>
       <c r="F41">
-        <v>5136284.839304442</v>
+        <v>0.0328909354277019</v>
       </c>
       <c r="G41">
-        <v>0.9910342345333821</v>
+        <v>0.04860821893906703</v>
       </c>
       <c r="H41">
-        <v>-10009216.05972831</v>
+        <v>0.0003962756028422498</v>
       </c>
       <c r="I41">
-        <v>10124650.5390233</v>
+        <v>0.1293263733150987</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -3200,28 +3200,28 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
         <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E42">
-        <v>76323.78172176723</v>
+        <v>-0.006652054254323309</v>
       </c>
       <c r="F42">
-        <v>98354.75623228958</v>
+        <v>0.02245545438087208</v>
       </c>
       <c r="G42">
-        <v>0.4377460389810169</v>
+        <v>0.7670518891367748</v>
       </c>
       <c r="H42">
-        <v>-116447.9982017368</v>
+        <v>-0.05066393609731477</v>
       </c>
       <c r="I42">
-        <v>269095.5616452713</v>
+        <v>0.03735982758866815</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -3229,31 +3229,31 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
         <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E43">
-        <v>16674.08522827138</v>
+        <v>0.04765786585252241</v>
       </c>
       <c r="F43">
-        <v>16636.12038859932</v>
+        <v>0.01227265075143456</v>
       </c>
       <c r="G43">
-        <v>0.316207378339653</v>
+        <v>0.0001030662221191807</v>
       </c>
       <c r="H43">
-        <v>-15932.11157585578</v>
+        <v>0.02360391238487225</v>
       </c>
       <c r="I43">
-        <v>49280.28203239854</v>
+        <v>0.07171181932017258</v>
       </c>
       <c r="J43">
-        <v>16674.08522827138</v>
+        <v>0.04765786585252241</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -3261,7 +3261,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
         <v>44</v>
@@ -3270,19 +3270,19 @@
         <v>78</v>
       </c>
       <c r="E44">
-        <v>0.5800381206477045</v>
+        <v>0.6294364342446849</v>
       </c>
       <c r="F44">
-        <v>3.105397551453294</v>
+        <v>0.01522277797901844</v>
       </c>
       <c r="G44">
-        <v>0.8518301073234911</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>-5.506429237879621</v>
+        <v>0.5996003376611593</v>
       </c>
       <c r="I44">
-        <v>6.666505479175029</v>
+        <v>0.6592725308282105</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -3290,7 +3290,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
         <v>44</v>
@@ -3299,19 +3299,19 @@
         <v>79</v>
       </c>
       <c r="E45">
-        <v>-0.1493253721405085</v>
+        <v>-0.2448876553699459</v>
       </c>
       <c r="F45">
-        <v>3.10547608071022</v>
+        <v>0.02598194551651756</v>
       </c>
       <c r="G45">
-        <v>0.9616488715267716</v>
+        <v>4.288739621647559E-21</v>
       </c>
       <c r="H45">
-        <v>-6.235946645183142</v>
+        <v>-0.2958113328306023</v>
       </c>
       <c r="I45">
-        <v>5.937295900902124</v>
+        <v>-0.1939639779092896</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -3319,7 +3319,7 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
         <v>44</v>
@@ -3328,19 +3328,19 @@
         <v>80</v>
       </c>
       <c r="E46">
-        <v>0.2056800663871909</v>
+        <v>0.07624055386034352</v>
       </c>
       <c r="F46">
-        <v>3.105597999172989</v>
+        <v>0.03477552510847508</v>
       </c>
       <c r="G46">
-        <v>0.9471956583758823</v>
+        <v>0.02835334898258488</v>
       </c>
       <c r="H46">
-        <v>-5.881180162451519</v>
+        <v>0.008081777104264012</v>
       </c>
       <c r="I46">
-        <v>6.292540295225901</v>
+        <v>0.144399330616423</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -3348,7 +3348,7 @@
         <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
         <v>44</v>
@@ -3357,19 +3357,19 @@
         <v>81</v>
       </c>
       <c r="E47">
-        <v>0.1524124546691054</v>
+        <v>0.03894556558770097</v>
       </c>
       <c r="F47">
-        <v>3.105333279061516</v>
+        <v>0.02658010286353459</v>
       </c>
       <c r="G47">
-        <v>0.9608548496655319</v>
+        <v>0.1428622666435429</v>
       </c>
       <c r="H47">
-        <v>-5.933928932285136</v>
+        <v>-0.01315047873019678</v>
       </c>
       <c r="I47">
-        <v>6.238753841623346</v>
+        <v>0.0910416099055987</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -3377,7 +3377,7 @@
         <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C48" t="s">
         <v>44</v>
@@ -3386,19 +3386,19 @@
         <v>82</v>
       </c>
       <c r="E48">
-        <v>0.217273779128076</v>
+        <v>-0.01039246147832963</v>
       </c>
       <c r="F48">
-        <v>3.105417796489343</v>
+        <v>0.01830487555413691</v>
       </c>
       <c r="G48">
-        <v>0.9442206912277334</v>
+        <v>0.5702096182839602</v>
       </c>
       <c r="H48">
-        <v>-5.869233258940771</v>
+        <v>-0.04626935830592564</v>
       </c>
       <c r="I48">
-        <v>6.303780817196923</v>
+        <v>0.02548443534926639</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -3406,7 +3406,7 @@
         <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
         <v>44</v>
@@ -3415,19 +3415,22 @@
         <v>83</v>
       </c>
       <c r="E49">
-        <v>-0.006652054254323341</v>
+        <v>0.04719828571032139</v>
       </c>
       <c r="F49">
-        <v>0.02245545438087213</v>
+        <v>0.01030095979769413</v>
       </c>
       <c r="G49">
-        <v>0.7670518891367741</v>
+        <v>4.607022004654193E-06</v>
       </c>
       <c r="H49">
-        <v>-0.05066393609731489</v>
+        <v>0.02700877550064588</v>
       </c>
       <c r="I49">
-        <v>0.03735982758866821</v>
+        <v>0.0673877959199969</v>
+      </c>
+      <c r="J49">
+        <v>0.04719828571032139</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3435,31 +3438,28 @@
         <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C50" t="s">
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E50">
-        <v>0.04765786585252259</v>
+        <v>0.1023197737239748</v>
       </c>
       <c r="F50">
-        <v>0.01227265075143458</v>
+        <v>0.004629507587282407</v>
       </c>
       <c r="G50">
-        <v>0.0001030662221191778</v>
+        <v>3.047008368015059E-108</v>
       </c>
       <c r="H50">
-        <v>0.02360391238487237</v>
+        <v>0.0932461055867464</v>
       </c>
       <c r="I50">
-        <v>0.0717118193201728</v>
-      </c>
-      <c r="J50">
-        <v>0.04765786585252259</v>
+        <v>0.1113934418612033</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -3467,28 +3467,28 @@
         <v>42</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C51" t="s">
         <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E51">
-        <v>0.4422665439596587</v>
+        <v>-0.06598351778973743</v>
       </c>
       <c r="F51">
-        <v>1.57912835493748</v>
+        <v>0.006943989548319156</v>
       </c>
       <c r="G51">
-        <v>0.7794237686667369</v>
+        <v>2.054053186823182E-21</v>
       </c>
       <c r="H51">
-        <v>-2.652768158683785</v>
+        <v>-0.07959348721346554</v>
       </c>
       <c r="I51">
-        <v>3.537301246603103</v>
+        <v>-0.05237354836600933</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -3496,28 +3496,28 @@
         <v>42</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C52" t="s">
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E52">
-        <v>-0.05771776508491929</v>
+        <v>0.01245789390539018</v>
       </c>
       <c r="F52">
-        <v>1.579219537021732</v>
+        <v>0.01040587576464074</v>
       </c>
       <c r="G52">
-        <v>0.9708451788620722</v>
+        <v>0.2312293798072539</v>
       </c>
       <c r="H52">
-        <v>-3.152931181329532</v>
+        <v>-0.007937247820903864</v>
       </c>
       <c r="I52">
-        <v>3.037495651159694</v>
+        <v>0.03285303563168422</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -3525,28 +3525,28 @@
         <v>42</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C53" t="s">
         <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E53">
-        <v>0.2634104441453702</v>
+        <v>-0.01345119213746955</v>
       </c>
       <c r="F53">
-        <v>1.579400091485919</v>
+        <v>0.009478969403696703</v>
       </c>
       <c r="G53">
-        <v>0.8675441040914289</v>
+        <v>0.1558825756163691</v>
       </c>
       <c r="H53">
-        <v>-2.832156852346298</v>
+        <v>-0.0320296307792722</v>
       </c>
       <c r="I53">
-        <v>3.358977740637039</v>
+        <v>0.005127246504333107</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -3554,28 +3554,28 @@
         <v>42</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C54" t="s">
         <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E54">
-        <v>0.1871698902850263</v>
+        <v>0.01345699908705631</v>
       </c>
       <c r="F54">
-        <v>1.579046644914525</v>
+        <v>0.005621256476121304</v>
       </c>
       <c r="G54">
-        <v>0.9056449706896867</v>
+        <v>0.0166680843137397</v>
       </c>
       <c r="H54">
-        <v>-2.90770466365625</v>
+        <v>0.002439538845996016</v>
       </c>
       <c r="I54">
-        <v>3.282044444226303</v>
+        <v>0.0244744593281166</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -3583,28 +3583,31 @@
         <v>42</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C55" t="s">
         <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E55">
-        <v>0.2261154558727276</v>
+        <v>0.008143645066237701</v>
       </c>
       <c r="F55">
-        <v>1.579175437989217</v>
+        <v>0.002968318886055048</v>
       </c>
       <c r="G55">
-        <v>0.8861434655025966</v>
+        <v>0.006078416847708558</v>
       </c>
       <c r="H55">
-        <v>-2.869011527856404</v>
+        <v>0.002325846954939755</v>
       </c>
       <c r="I55">
-        <v>3.321242439601859</v>
+        <v>0.01396144317753565</v>
+      </c>
+      <c r="J55">
+        <v>0.008143645066237701</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -3612,28 +3615,28 @@
         <v>42</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C56" t="s">
         <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E56">
-        <v>-0.01039246147832957</v>
+        <v>0.2908109956778311</v>
       </c>
       <c r="F56">
-        <v>0.01830487555413695</v>
+        <v>0.02141955889086554</v>
       </c>
       <c r="G56">
-        <v>0.5702096182839631</v>
+        <v>5.490880522968274E-42</v>
       </c>
       <c r="H56">
-        <v>-0.04626935830592566</v>
+        <v>0.2488294316869999</v>
       </c>
       <c r="I56">
-        <v>0.02548443534926652</v>
+        <v>0.3327925596686623</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -3641,31 +3644,28 @@
         <v>42</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C57" t="s">
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E57">
-        <v>0.04719828571032152</v>
+        <v>-0.09537388771248528</v>
       </c>
       <c r="F57">
-        <v>0.01030095979769416</v>
+        <v>0.03894714021650424</v>
       </c>
       <c r="G57">
-        <v>4.607022004654132E-06</v>
+        <v>0.01433316758009062</v>
       </c>
       <c r="H57">
-        <v>0.02700877550064597</v>
+        <v>-0.1717088798376651</v>
       </c>
       <c r="I57">
-        <v>0.06738779591999706</v>
-      </c>
-      <c r="J57">
-        <v>0.04719828571032152</v>
+        <v>-0.01903889558730544</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -3673,28 +3673,28 @@
         <v>42</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
         <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E58">
-        <v>0.08651299238863024</v>
+        <v>0.07019646422058243</v>
       </c>
       <c r="F58">
-        <v>0.7039861632605711</v>
+        <v>0.0515581607438702</v>
       </c>
       <c r="G58">
-        <v>0.9021940550824432</v>
+        <v>0.1733555597810249</v>
       </c>
       <c r="H58">
-        <v>-1.293274533216624</v>
+        <v>-0.03085567394653001</v>
       </c>
       <c r="I58">
-        <v>1.466300517993884</v>
+        <v>0.1712486023876948</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -3702,28 +3702,28 @@
         <v>42</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C59" t="s">
         <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E59">
-        <v>-0.05017673645439282</v>
+        <v>0.156908867833769</v>
       </c>
       <c r="F59">
-        <v>0.7039967918798178</v>
+        <v>0.03615554955974869</v>
       </c>
       <c r="G59">
-        <v>0.9431796094572361</v>
+        <v>1.425942551735026E-05</v>
       </c>
       <c r="H59">
-        <v>-1.429985093770576</v>
+        <v>0.08604529285540852</v>
       </c>
       <c r="I59">
-        <v>1.32963162086179</v>
+        <v>0.2277724428121294</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -3731,28 +3731,28 @@
         <v>42</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
         <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E60">
-        <v>0.0282646752407348</v>
+        <v>0.007576557203061413</v>
       </c>
       <c r="F60">
-        <v>0.7040479493626299</v>
+        <v>0.02559869735148776</v>
       </c>
       <c r="G60">
-        <v>0.9679767668441579</v>
+        <v>0.7672496880917226</v>
       </c>
       <c r="H60">
-        <v>-1.3516439488993</v>
+        <v>-0.04259596765699547</v>
       </c>
       <c r="I60">
-        <v>1.408173299380769</v>
+        <v>0.0577490820631183</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -3760,28 +3760,31 @@
         <v>42</v>
       </c>
       <c r="B61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C61" t="s">
         <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E61">
-        <v>0.01580678133534455</v>
+        <v>-0.2502801382188822</v>
       </c>
       <c r="F61">
-        <v>0.7039749011994658</v>
+        <v>0.01554489821295187</v>
       </c>
       <c r="G61">
-        <v>0.9820861126032137</v>
+        <v>2.531817939931266E-58</v>
       </c>
       <c r="H61">
-        <v>-1.363958671035751</v>
+        <v>-0.2807475788596089</v>
       </c>
       <c r="I61">
-        <v>1.39557223370644</v>
+        <v>-0.2198126975781555</v>
+      </c>
+      <c r="J61">
+        <v>-0.2502801382188822</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -3789,28 +3792,28 @@
         <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C62" t="s">
         <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E62">
-        <v>0.00235558919787493</v>
+        <v>0.1416078513875415</v>
       </c>
       <c r="F62">
-        <v>0.7040026999167855</v>
+        <v>0.02197541307181862</v>
       </c>
       <c r="G62">
-        <v>0.9973302875886957</v>
+        <v>1.164248088506843E-10</v>
       </c>
       <c r="H62">
-        <v>-1.377464347657984</v>
+        <v>0.09853683322138623</v>
       </c>
       <c r="I62">
-        <v>1.382175526053734</v>
+        <v>0.1846788695536967</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -3818,28 +3821,28 @@
         <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C63" t="s">
         <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E63">
-        <v>0.01345699908705628</v>
+        <v>-0.06053929611883627</v>
       </c>
       <c r="F63">
-        <v>0.005621256476121317</v>
+        <v>0.03672251667203771</v>
       </c>
       <c r="G63">
-        <v>0.01666808431374018</v>
+        <v>0.09923767494069446</v>
       </c>
       <c r="H63">
-        <v>0.002439538845995962</v>
+        <v>-0.1325141062177019</v>
       </c>
       <c r="I63">
-        <v>0.0244744593281166</v>
+        <v>0.01143551398002932</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -3847,31 +3850,28 @@
         <v>42</v>
       </c>
       <c r="B64" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C64" t="s">
         <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E64">
-        <v>0.008143645066237703</v>
+        <v>0.02321211523792632</v>
       </c>
       <c r="F64">
-        <v>0.002968318886055052</v>
+        <v>0.05731077913161593</v>
       </c>
       <c r="G64">
-        <v>0.00607841684770863</v>
+        <v>0.6854614826838912</v>
       </c>
       <c r="H64">
-        <v>0.002325846954939747</v>
+        <v>-0.08911494778597062</v>
       </c>
       <c r="I64">
-        <v>0.01396144317753566</v>
-      </c>
-      <c r="J64">
-        <v>0.008143645066237703</v>
+        <v>0.1355391782618233</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -3879,28 +3879,28 @@
         <v>42</v>
       </c>
       <c r="B65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C65" t="s">
         <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E65">
-        <v>0.4087412092277098</v>
+        <v>0.05136635898059345</v>
       </c>
       <c r="F65">
-        <v>0.7016066488727929</v>
+        <v>0.03596729202868922</v>
       </c>
       <c r="G65">
-        <v>0.5601768326845105</v>
+        <v>0.1532513219014303</v>
       </c>
       <c r="H65">
-        <v>-0.9663825538768038</v>
+        <v>-0.019128238017072</v>
       </c>
       <c r="I65">
-        <v>1.783864972332224</v>
+        <v>0.1218609559782589</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -3908,28 +3908,28 @@
         <v>42</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66" t="s">
         <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E66">
-        <v>-0.2133041012623642</v>
+        <v>0.02387579926767758</v>
       </c>
       <c r="F66">
-        <v>0.7019068490690635</v>
+        <v>0.02612229324222226</v>
       </c>
       <c r="G66">
-        <v>0.7612099285038815</v>
+        <v>0.3607163781366758</v>
       </c>
       <c r="H66">
-        <v>-1.58901624593972</v>
+        <v>-0.02732295468067208</v>
       </c>
       <c r="I66">
-        <v>1.162408043414992</v>
+        <v>0.07507455321602724</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -3937,28 +3937,31 @@
         <v>42</v>
       </c>
       <c r="B67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C67" t="s">
         <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E67">
-        <v>-0.04773374932929657</v>
+        <v>-0.139301144660744</v>
       </c>
       <c r="F67">
-        <v>0.7030587516671017</v>
+        <v>0.01511586804597232</v>
       </c>
       <c r="G67">
-        <v>0.9458696997685395</v>
+        <v>3.096661286635821E-20</v>
       </c>
       <c r="H67">
-        <v>-1.425703581612506</v>
+        <v>-0.1689277016259096</v>
       </c>
       <c r="I67">
-        <v>1.330236082953912</v>
+        <v>-0.1096745876955784</v>
+      </c>
+      <c r="J67">
+        <v>-0.139301144660744</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -3966,28 +3969,28 @@
         <v>42</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C68" t="s">
         <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E68">
-        <v>-0.1179302135498788</v>
+        <v>-0.07737284851477501</v>
       </c>
       <c r="F68">
-        <v>0.7011423107589932</v>
+        <v>0.004058591682767254</v>
       </c>
       <c r="G68">
-        <v>0.8664280986744171</v>
+        <v>5.031376825833875E-81</v>
       </c>
       <c r="H68">
-        <v>-1.492143890674696</v>
+        <v>-0.08532754204095264</v>
       </c>
       <c r="I68">
-        <v>1.256283463574938</v>
+        <v>-0.06941815498859738</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3995,28 +3998,28 @@
         <v>42</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C69" t="s">
         <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E69">
-        <v>0.03897865428388959</v>
+        <v>0.04616621213473834</v>
       </c>
       <c r="F69">
-        <v>0.7015242226132451</v>
+        <v>0.005497959196493301</v>
       </c>
       <c r="G69">
-        <v>0.9556900952221997</v>
+        <v>4.581373191347267E-17</v>
       </c>
       <c r="H69">
-        <v>-1.33598355632053</v>
+        <v>0.03539041012114069</v>
       </c>
       <c r="I69">
-        <v>1.413940864888309</v>
+        <v>0.05694201414833598</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -4024,28 +4027,28 @@
         <v>42</v>
       </c>
       <c r="B70" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C70" t="s">
         <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E70">
-        <v>0.007576557203061434</v>
+        <v>0.002099496082897155</v>
       </c>
       <c r="F70">
-        <v>0.02559869735148781</v>
+        <v>0.008672696567289201</v>
       </c>
       <c r="G70">
-        <v>0.7672496880917222</v>
+        <v>0.8087173086188963</v>
       </c>
       <c r="H70">
-        <v>-0.04259596765699555</v>
+        <v>-0.01489867683783383</v>
       </c>
       <c r="I70">
-        <v>0.05774908206311841</v>
+        <v>0.01909766900362814</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -4053,31 +4056,28 @@
         <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C71" t="s">
         <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E71">
-        <v>-0.2502801382188817</v>
+        <v>0.0009918198893221607</v>
       </c>
       <c r="F71">
-        <v>0.01554489821295188</v>
+        <v>0.004972733013389714</v>
       </c>
       <c r="G71">
-        <v>2.531817939933073E-58</v>
+        <v>0.8419094478028709</v>
       </c>
       <c r="H71">
-        <v>-0.2807475788596085</v>
+        <v>-0.008754557721655013</v>
       </c>
       <c r="I71">
-        <v>-0.219812697578155</v>
-      </c>
-      <c r="J71">
-        <v>-0.2502801382188817</v>
+        <v>0.01073819750029933</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -4085,28 +4085,28 @@
         <v>42</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C72" t="s">
         <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E72">
-        <v>0.2025379475101585</v>
+        <v>0.007742278256728439</v>
       </c>
       <c r="F72">
-        <v>3.00021859109196</v>
+        <v>0.004369969112914281</v>
       </c>
       <c r="G72">
-        <v>0.9461775081711313</v>
+        <v>0.07644421843120426</v>
       </c>
       <c r="H72">
-        <v>-5.677782436777585</v>
+        <v>-0.0008227038181360009</v>
       </c>
       <c r="I72">
-        <v>6.082858331797903</v>
+        <v>0.01630726033159288</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -4114,28 +4114,31 @@
         <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C73" t="s">
         <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E73">
-        <v>-0.1214693922414531</v>
+        <v>-0.005167876725284562</v>
       </c>
       <c r="F73">
-        <v>3.000261478803718</v>
+        <v>0.002104377842409858</v>
       </c>
       <c r="G73">
-        <v>0.9677054540990858</v>
+        <v>0.01405814747433875</v>
       </c>
       <c r="H73">
-        <v>-6.001873834899623</v>
+        <v>-0.009292381506271988</v>
       </c>
       <c r="I73">
-        <v>5.758935050416717</v>
+        <v>-0.001043371944297134</v>
+      </c>
+      <c r="J73">
+        <v>-0.005167876725284562</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -4143,28 +4146,28 @@
         <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
         <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E74">
-        <v>-0.03771798088469058</v>
+        <v>1292.971047444701</v>
       </c>
       <c r="F74">
-        <v>3.000615104074785</v>
+        <v>544.6440746156383</v>
       </c>
       <c r="G74">
-        <v>0.989970788967757</v>
+        <v>0.01759777428573013</v>
       </c>
       <c r="H74">
-        <v>-5.918815516338176</v>
+        <v>225.4882768049038</v>
       </c>
       <c r="I74">
-        <v>5.843379554568795</v>
+        <v>2360.453818084497</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -4172,28 +4175,28 @@
         <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C75" t="s">
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E75">
-        <v>-0.06093009612261693</v>
+        <v>4544.781111753427</v>
       </c>
       <c r="F75">
-        <v>3.000082248349746</v>
+        <v>3179.976797098646</v>
       </c>
       <c r="G75">
-        <v>0.9837964972032148</v>
+        <v>0.1529505281038266</v>
       </c>
       <c r="H75">
-        <v>-5.940983253546069</v>
+        <v>-1687.858882232955</v>
       </c>
       <c r="I75">
-        <v>5.819123061300834</v>
+        <v>10777.42110573981</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -4201,28 +4204,28 @@
         <v>42</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C76" t="s">
         <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E76">
-        <v>-0.009563737142023783</v>
+        <v>-463.1744410978375</v>
       </c>
       <c r="F76">
-        <v>3.000155973997798</v>
+        <v>456.1393580000275</v>
       </c>
       <c r="G76">
-        <v>0.997456550475463</v>
+        <v>0.3099041861160952</v>
       </c>
       <c r="H76">
-        <v>-5.889761394180394</v>
+        <v>-1357.191154709114</v>
       </c>
       <c r="I76">
-        <v>5.870633919896346</v>
+        <v>430.8422725134386</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -4230,28 +4233,28 @@
         <v>42</v>
       </c>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C77" t="s">
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E77">
-        <v>0.02387579926767762</v>
+        <v>422.4702110920724</v>
       </c>
       <c r="F77">
-        <v>0.02612229324222231</v>
+        <v>654.5998834331955</v>
       </c>
       <c r="G77">
-        <v>0.3607163781366759</v>
+        <v>0.5186764692103929</v>
       </c>
       <c r="H77">
-        <v>-0.02732295468067215</v>
+        <v>-860.5219847211084</v>
       </c>
       <c r="I77">
-        <v>0.07507455321602739</v>
+        <v>1705.462406905253</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -4259,31 +4262,28 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C78" t="s">
         <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E78">
-        <v>-0.1393011446607439</v>
+        <v>-269.0605205296977</v>
       </c>
       <c r="F78">
-        <v>0.01511586804597234</v>
+        <v>586.3669207870266</v>
       </c>
       <c r="G78">
-        <v>3.096661286636444E-20</v>
+        <v>0.6463344656321321</v>
       </c>
       <c r="H78">
-        <v>-0.1689277016259095</v>
+        <v>-1418.318566997921</v>
       </c>
       <c r="I78">
-        <v>-0.1096745876955783</v>
-      </c>
-      <c r="J78">
-        <v>-0.1393011446607439</v>
+        <v>880.1975259385254</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -4291,527 +4291,524 @@
         <v>42</v>
       </c>
       <c r="B79" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C79" t="s">
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E79">
-        <v>-0.06131217980347483</v>
+        <v>-241.3534367032737</v>
       </c>
       <c r="F79">
-        <v>0.06933024091959047</v>
+        <v>505.4224382132962</v>
       </c>
       <c r="G79">
-        <v>0.376507451007936</v>
+        <v>0.6329860878312669</v>
       </c>
       <c r="H79">
-        <v>-0.1971969550453573</v>
+        <v>-1231.963212579755</v>
       </c>
       <c r="I79">
-        <v>0.07457259543840761</v>
+        <v>749.2563391732076</v>
+      </c>
+      <c r="J79">
+        <v>-241.3534367032737</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B80" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
         <v>44</v>
       </c>
       <c r="D80" t="s">
+        <v>78</v>
+      </c>
+      <c r="E80">
+        <v>2.602336526301711</v>
+      </c>
+      <c r="F80">
+        <v>0.0676536122171565</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>2.469737882932045</v>
+      </c>
+      <c r="I80">
+        <v>2.734935169671377</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>43</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>44</v>
+      </c>
+      <c r="D81" t="s">
         <v>79</v>
       </c>
-      <c r="E80">
-        <v>0.03010554342343811</v>
-      </c>
-      <c r="F80">
-        <v>0.06935861444034848</v>
-      </c>
-      <c r="G80">
-        <v>0.6642475595078163</v>
-      </c>
-      <c r="H80">
-        <v>-0.1058348428972446</v>
-      </c>
-      <c r="I80">
-        <v>0.1660459297441208</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
-      <c r="A81" t="s">
-        <v>42</v>
-      </c>
-      <c r="B81" t="s">
-        <v>22</v>
-      </c>
-      <c r="C81" t="s">
-        <v>44</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="E81">
+        <v>1.390654066979748</v>
+      </c>
+      <c r="F81">
+        <v>0.1960180304295014</v>
+      </c>
+      <c r="G81">
+        <v>1.298001039482134E-12</v>
+      </c>
+      <c r="H81">
+        <v>1.006465787017449</v>
+      </c>
+      <c r="I81">
+        <v>1.774842346942047</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>43</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" t="s">
         <v>80</v>
       </c>
-      <c r="E81">
-        <v>-0.01396117262840306</v>
-      </c>
-      <c r="F81">
-        <v>0.0696897773946196</v>
-      </c>
-      <c r="G81">
-        <v>0.8412200380581338</v>
-      </c>
-      <c r="H81">
-        <v>-0.1505506264124711</v>
-      </c>
-      <c r="I81">
-        <v>0.1226282811556649</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
-      <c r="A82" t="s">
-        <v>42</v>
-      </c>
-      <c r="B82" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82" t="s">
-        <v>44</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="E82">
+        <v>-0.31166151051194</v>
+      </c>
+      <c r="F82">
+        <v>0.1121361846392685</v>
+      </c>
+      <c r="G82">
+        <v>0.005447407550216434</v>
+      </c>
+      <c r="H82">
+        <v>-0.5314443937686398</v>
+      </c>
+      <c r="I82">
+        <v>-0.09187862725524007</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>43</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" t="s">
         <v>81</v>
       </c>
-      <c r="E82">
-        <v>-0.01606066871130018</v>
-      </c>
-      <c r="F82">
-        <v>0.06918265925199919</v>
-      </c>
-      <c r="G82">
-        <v>0.8164224724525926</v>
-      </c>
-      <c r="H82">
-        <v>-0.1516561891999254</v>
-      </c>
-      <c r="I82">
-        <v>0.119534851777325</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
-      <c r="A83" t="s">
-        <v>42</v>
-      </c>
-      <c r="B83" t="s">
-        <v>22</v>
-      </c>
-      <c r="C83" t="s">
-        <v>44</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="E83">
+        <v>0.298672903323123</v>
+      </c>
+      <c r="F83">
+        <v>0.1275334050812182</v>
+      </c>
+      <c r="G83">
+        <v>0.01918487854053217</v>
+      </c>
+      <c r="H83">
+        <v>0.04871202253817783</v>
+      </c>
+      <c r="I83">
+        <v>0.5486337841080681</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>43</v>
+      </c>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
+        <v>44</v>
+      </c>
+      <c r="D84" t="s">
         <v>82</v>
       </c>
-      <c r="E83">
-        <v>-0.01506884882197805</v>
-      </c>
-      <c r="F83">
-        <v>0.06922547560337441</v>
-      </c>
-      <c r="G83">
-        <v>0.8276801665823159</v>
-      </c>
-      <c r="H83">
-        <v>-0.1507482878172481</v>
-      </c>
-      <c r="I83">
-        <v>0.120610590173292</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" t="s">
-        <v>42</v>
-      </c>
-      <c r="B84" t="s">
-        <v>22</v>
-      </c>
-      <c r="C84" t="s">
-        <v>44</v>
-      </c>
-      <c r="D84" t="s">
-        <v>83</v>
-      </c>
       <c r="E84">
-        <v>0.007742278256728424</v>
+        <v>-0.1273438380100334</v>
       </c>
       <c r="F84">
-        <v>0.00436996911291429</v>
+        <v>0.08323244266282481</v>
       </c>
       <c r="G84">
-        <v>0.07644421843120544</v>
+        <v>0.1260220798612741</v>
       </c>
       <c r="H84">
-        <v>-0.000822703818136033</v>
+        <v>-0.290476427974465</v>
       </c>
       <c r="I84">
-        <v>0.01630726033159288</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+        <v>0.03578875195439832</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B85" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
         <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E85">
-        <v>-0.005167876725284576</v>
+        <v>0.08761427418969088</v>
       </c>
       <c r="F85">
-        <v>0.002104377842409861</v>
+        <v>0.005974547256266771</v>
       </c>
       <c r="G85">
-        <v>0.0140581474743386</v>
+        <v>1.086747411431796E-48</v>
       </c>
       <c r="H85">
-        <v>-0.009292381506272009</v>
+        <v>0.07590437674347542</v>
       </c>
       <c r="I85">
-        <v>-0.001043371944297143</v>
-      </c>
-      <c r="J85">
-        <v>-0.005167876725284576</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
+        <v>0.09932417163590634</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
         <v>44</v>
       </c>
       <c r="D86" t="s">
+        <v>79</v>
+      </c>
+      <c r="E86">
+        <v>0.03244339901319972</v>
+      </c>
+      <c r="F86">
+        <v>0.01096163055443771</v>
+      </c>
+      <c r="G86">
+        <v>0.003079149469684254</v>
+      </c>
+      <c r="H86">
+        <v>0.01095899791466798</v>
+      </c>
+      <c r="I86">
+        <v>0.05392780011173147</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>43</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" t="s">
+        <v>80</v>
+      </c>
+      <c r="E87">
+        <v>-0.01513536007858212</v>
+      </c>
+      <c r="F87">
+        <v>0.01061202712664654</v>
+      </c>
+      <c r="G87">
+        <v>0.1537973774410893</v>
+      </c>
+      <c r="H87">
+        <v>-0.03593455104977142</v>
+      </c>
+      <c r="I87">
+        <v>0.005663830892607177</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>43</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" t="s">
+        <v>81</v>
+      </c>
+      <c r="E88">
+        <v>-0.02110437501675216</v>
+      </c>
+      <c r="F88">
+        <v>0.007656065726314778</v>
+      </c>
+      <c r="G88">
+        <v>0.005841358360730085</v>
+      </c>
+      <c r="H88">
+        <v>-0.03610998810360062</v>
+      </c>
+      <c r="I88">
+        <v>-0.006098761929903706</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>43</v>
+      </c>
+      <c r="B89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" t="s">
+        <v>82</v>
+      </c>
+      <c r="E89">
+        <v>0.009378608243243406</v>
+      </c>
+      <c r="F89">
+        <v>0.006877683488183683</v>
+      </c>
+      <c r="G89">
+        <v>0.1726843790968077</v>
+      </c>
+      <c r="H89">
+        <v>-0.004101403690662423</v>
+      </c>
+      <c r="I89">
+        <v>0.02285862017714924</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>43</v>
+      </c>
+      <c r="B90" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" t="s">
+        <v>44</v>
+      </c>
+      <c r="D90" t="s">
         <v>78</v>
       </c>
-      <c r="E86">
-        <v>1545.242123982607</v>
-      </c>
-      <c r="F86">
-        <v>65755.32010664341</v>
-      </c>
-      <c r="G86">
-        <v>0.9812515343012286</v>
-      </c>
-      <c r="H86">
-        <v>-127332.8170769409</v>
-      </c>
-      <c r="I86">
-        <v>130423.3013249062</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
-      <c r="A87" t="s">
-        <v>42</v>
-      </c>
-      <c r="B87" t="s">
-        <v>23</v>
-      </c>
-      <c r="C87" t="s">
-        <v>44</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="E90">
+        <v>1.576085849878997</v>
+      </c>
+      <c r="F90">
+        <v>0.06408026754253272</v>
+      </c>
+      <c r="G90">
+        <v>1.411493740577181E-133</v>
+      </c>
+      <c r="H90">
+        <v>1.450490833375942</v>
+      </c>
+      <c r="I90">
+        <v>1.701680866382052</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>43</v>
+      </c>
+      <c r="B91" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" t="s">
+        <v>44</v>
+      </c>
+      <c r="D91" t="s">
         <v>79</v>
       </c>
-      <c r="E87">
-        <v>4292.510035215521</v>
-      </c>
-      <c r="F87">
-        <v>65803.86155861642</v>
-      </c>
-      <c r="G87">
-        <v>0.9479893733486578</v>
-      </c>
-      <c r="H87">
-        <v>-124680.6886633324</v>
-      </c>
-      <c r="I87">
-        <v>133265.7087337635</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
-      <c r="A88" t="s">
-        <v>42</v>
-      </c>
-      <c r="B88" t="s">
-        <v>23</v>
-      </c>
-      <c r="C88" t="s">
-        <v>44</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="E91">
+        <v>1.214257172653137</v>
+      </c>
+      <c r="F91">
+        <v>0.2339616133674048</v>
+      </c>
+      <c r="G91">
+        <v>2.103114627292624E-07</v>
+      </c>
+      <c r="H91">
+        <v>0.7557008366881384</v>
+      </c>
+      <c r="I91">
+        <v>1.672813508618135</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>43</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" t="s">
         <v>80</v>
       </c>
-      <c r="E88">
-        <v>-715.4455176357422</v>
-      </c>
-      <c r="F88">
-        <v>65760.94959776412</v>
-      </c>
-      <c r="G88">
-        <v>0.991319595061072</v>
-      </c>
-      <c r="H88">
-        <v>-129604.5383184072</v>
-      </c>
-      <c r="I88">
-        <v>128173.6472831357</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
-      <c r="A89" t="s">
-        <v>42</v>
-      </c>
-      <c r="B89" t="s">
-        <v>23</v>
-      </c>
-      <c r="C89" t="s">
-        <v>44</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="E92">
+        <v>-0.1390341417123635</v>
+      </c>
+      <c r="F92">
+        <v>0.1210874133774517</v>
+      </c>
+      <c r="G92">
+        <v>0.2508806454812891</v>
+      </c>
+      <c r="H92">
+        <v>-0.3763611109132823</v>
+      </c>
+      <c r="I92">
+        <v>0.09829282748855536</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>43</v>
+      </c>
+      <c r="B93" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" t="s">
+        <v>44</v>
+      </c>
+      <c r="D93" t="s">
         <v>81</v>
       </c>
-      <c r="E89">
-        <v>-252.2710765379041</v>
-      </c>
-      <c r="F89">
-        <v>65755.6884536649</v>
-      </c>
-      <c r="G89">
-        <v>0.99693893094162</v>
-      </c>
-      <c r="H89">
-        <v>-129131.0522243574</v>
-      </c>
-      <c r="I89">
-        <v>128626.5100712816</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
-      <c r="A90" t="s">
-        <v>42</v>
-      </c>
-      <c r="B90" t="s">
-        <v>23</v>
-      </c>
-      <c r="C90" t="s">
-        <v>44</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="E93">
+        <v>0.03979024068024745</v>
+      </c>
+      <c r="F93">
+        <v>0.1038162541662752</v>
+      </c>
+      <c r="G93">
+        <v>0.7015154033242907</v>
+      </c>
+      <c r="H93">
+        <v>-0.1636858784955083</v>
+      </c>
+      <c r="I93">
+        <v>0.2432663598560031</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>43</v>
+      </c>
+      <c r="B94" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" t="s">
         <v>82</v>
       </c>
-      <c r="E90">
-        <v>170.1991345541716</v>
-      </c>
-      <c r="F90">
-        <v>65752.50134401995</v>
-      </c>
-      <c r="G90">
-        <v>0.9979346928664422</v>
-      </c>
-      <c r="H90">
-        <v>-128702.3353931464</v>
-      </c>
-      <c r="I90">
-        <v>129042.7336622548</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
-      <c r="A91" t="s">
-        <v>42</v>
-      </c>
-      <c r="B91" t="s">
-        <v>23</v>
-      </c>
-      <c r="C91" t="s">
-        <v>44</v>
-      </c>
-      <c r="D91" t="s">
-        <v>83</v>
-      </c>
-      <c r="E91">
-        <v>-269.0605205296978</v>
-      </c>
-      <c r="F91">
-        <v>586.3669207870287</v>
-      </c>
-      <c r="G91">
-        <v>0.646334465632133</v>
-      </c>
-      <c r="H91">
-        <v>-1418.318566997925</v>
-      </c>
-      <c r="I91">
-        <v>880.197525938529</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
-      <c r="A92" t="s">
-        <v>42</v>
-      </c>
-      <c r="B92" t="s">
-        <v>23</v>
-      </c>
-      <c r="C92" t="s">
-        <v>44</v>
-      </c>
-      <c r="D92" t="s">
-        <v>84</v>
-      </c>
-      <c r="E92">
-        <v>-241.353436703274</v>
-      </c>
-      <c r="F92">
-        <v>505.4224382132981</v>
-      </c>
-      <c r="G92">
-        <v>0.6329860878312678</v>
-      </c>
-      <c r="H92">
-        <v>-1231.963212579759</v>
-      </c>
-      <c r="I92">
-        <v>749.256339173211</v>
-      </c>
-      <c r="J92">
-        <v>-241.353436703274</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="A93" t="s">
-        <v>43</v>
-      </c>
-      <c r="B93" t="s">
-        <v>11</v>
-      </c>
-      <c r="C93" t="s">
-        <v>44</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="E94">
+        <v>-0.006453378877911373</v>
+      </c>
+      <c r="F94">
+        <v>0.08050824744525584</v>
+      </c>
+      <c r="G94">
+        <v>0.9361116058318932</v>
+      </c>
+      <c r="H94">
+        <v>-0.1642466443290516</v>
+      </c>
+      <c r="I94">
+        <v>0.1513398865732289</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>43</v>
+      </c>
+      <c r="B95" t="s">
+        <v>14</v>
+      </c>
+      <c r="C95" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" t="s">
         <v>78</v>
       </c>
-      <c r="E93">
-        <v>2.944196898961016</v>
-      </c>
-      <c r="F93">
-        <v>6.476725308627175</v>
-      </c>
-      <c r="G93">
-        <v>0.6494106362271979</v>
-      </c>
-      <c r="H93">
-        <v>-9.749951443707314</v>
-      </c>
-      <c r="I93">
-        <v>15.63834524162935</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
-      <c r="A94" t="s">
-        <v>43</v>
-      </c>
-      <c r="B94" t="s">
-        <v>11</v>
-      </c>
-      <c r="C94" t="s">
-        <v>44</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="E95">
+        <v>3.950509915027804</v>
+      </c>
+      <c r="F95">
+        <v>0.6956938947888305</v>
+      </c>
+      <c r="G95">
+        <v>1.358671821240989E-08</v>
+      </c>
+      <c r="H95">
+        <v>2.586974936977299</v>
+      </c>
+      <c r="I95">
+        <v>5.31404489307831</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>43</v>
+      </c>
+      <c r="B96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96" t="s">
+        <v>44</v>
+      </c>
+      <c r="D96" t="s">
         <v>79</v>
       </c>
-      <c r="E94">
-        <v>1.048793694320441</v>
-      </c>
-      <c r="F94">
-        <v>6.47912814584881</v>
-      </c>
-      <c r="G94">
-        <v>0.8714061345991726</v>
-      </c>
-      <c r="H94">
-        <v>-11.650064122763</v>
-      </c>
-      <c r="I94">
-        <v>13.74765151140389</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
-      <c r="A95" t="s">
-        <v>43</v>
-      </c>
-      <c r="B95" t="s">
-        <v>11</v>
-      </c>
-      <c r="C95" t="s">
-        <v>44</v>
-      </c>
-      <c r="D95" t="s">
-        <v>80</v>
-      </c>
-      <c r="E95">
-        <v>-0.653521883171244</v>
-      </c>
-      <c r="F95">
-        <v>6.477001489548555</v>
-      </c>
-      <c r="G95">
-        <v>0.9196307705499716</v>
-      </c>
-      <c r="H95">
-        <v>-13.34821153049869</v>
-      </c>
-      <c r="I95">
-        <v>12.04116776415621</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
-      <c r="A96" t="s">
-        <v>43</v>
-      </c>
-      <c r="B96" t="s">
-        <v>11</v>
-      </c>
-      <c r="C96" t="s">
-        <v>44</v>
-      </c>
-      <c r="D96" t="s">
-        <v>81</v>
-      </c>
       <c r="E96">
-        <v>-0.3418603726593014</v>
+        <v>24.37048192473248</v>
       </c>
       <c r="F96">
-        <v>6.476471094116025</v>
+        <v>4.439472587708584</v>
       </c>
       <c r="G96">
-        <v>0.9579032320556015</v>
+        <v>4.030745801703352E-08</v>
       </c>
       <c r="H96">
-        <v>-13.03551046404143</v>
+        <v>15.66927554247082</v>
       </c>
       <c r="I96">
-        <v>12.35178971872283</v>
+        <v>33.07168830699414</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -4819,28 +4816,28 @@
         <v>43</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C97" t="s">
         <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E97">
-        <v>-0.04318746933618201</v>
+        <v>-2.043859603159869</v>
       </c>
       <c r="F97">
-        <v>6.477446583347024</v>
+        <v>0.675527170145202</v>
       </c>
       <c r="G97">
-        <v>0.9946802556748717</v>
+        <v>0.002481590454075337</v>
       </c>
       <c r="H97">
-        <v>-12.73874948447837</v>
+        <v>-3.367868527222726</v>
       </c>
       <c r="I97">
-        <v>12.65237454580601</v>
+        <v>-0.7198506790970123</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -4848,28 +4845,28 @@
         <v>43</v>
       </c>
       <c r="B98" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C98" t="s">
         <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E98">
-        <v>-0.1273438380100369</v>
+        <v>0.4187902221770857</v>
       </c>
       <c r="F98">
-        <v>0.08323244266282433</v>
+        <v>0.8300168705382908</v>
       </c>
       <c r="G98">
-        <v>0.1260220798612615</v>
+        <v>0.6138705257253836</v>
       </c>
       <c r="H98">
-        <v>-0.2904764279744676</v>
+        <v>-1.208012950638609</v>
       </c>
       <c r="I98">
-        <v>0.03578875195439388</v>
+        <v>2.04559339499278</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -4877,28 +4874,28 @@
         <v>43</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C99" t="s">
         <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E99">
-        <v>0.1026348998476229</v>
+        <v>0.5201174763124116</v>
       </c>
       <c r="F99">
-        <v>1.413707206249518</v>
+        <v>1.038456736342293</v>
       </c>
       <c r="G99">
-        <v>0.9421245636916359</v>
+        <v>0.6164723424371467</v>
       </c>
       <c r="H99">
-        <v>-2.668180309086171</v>
+        <v>-1.515220326421489</v>
       </c>
       <c r="I99">
-        <v>2.873450108781417</v>
+        <v>2.555455279046312</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -4906,28 +4903,28 @@
         <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C100" t="s">
         <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E100">
-        <v>0.01742277335526768</v>
+        <v>1.673620821892963</v>
       </c>
       <c r="F100">
-        <v>1.413728409464971</v>
+        <v>0.0443273433336678</v>
       </c>
       <c r="G100">
-        <v>0.9901671283606914</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>-2.753433993117171</v>
+        <v>1.586740825428632</v>
       </c>
       <c r="I100">
-        <v>2.788279539827706</v>
+        <v>1.760500818357293</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -4935,28 +4932,28 @@
         <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C101" t="s">
         <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E101">
-        <v>-0.03015598573651412</v>
+        <v>0.5731737401971867</v>
       </c>
       <c r="F101">
-        <v>1.413724322373517</v>
+        <v>0.1358745451419268</v>
       </c>
       <c r="G101">
-        <v>0.9829817097101746</v>
+        <v>2.460375606210915E-05</v>
       </c>
       <c r="H101">
-        <v>-2.801004741656901</v>
+        <v>0.3068645253032484</v>
       </c>
       <c r="I101">
-        <v>2.740692770183873</v>
+        <v>0.8394829550911249</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -4964,28 +4961,28 @@
         <v>43</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C102" t="s">
         <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E102">
-        <v>-0.01502062565793189</v>
+        <v>-0.03848081691973465</v>
       </c>
       <c r="F102">
-        <v>1.413699855069708</v>
+        <v>0.08859950592696003</v>
       </c>
       <c r="G102">
-        <v>0.9915225995312187</v>
+        <v>0.6640537918402356</v>
       </c>
       <c r="H102">
-        <v>-2.785821426544054</v>
+        <v>-0.2121326575846194</v>
       </c>
       <c r="I102">
-        <v>2.75578017522819</v>
+        <v>0.1351710237451501</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -4993,28 +4990,28 @@
         <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C103" t="s">
         <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E103">
-        <v>-0.03612500067468428</v>
+        <v>0.168342934343901</v>
       </c>
       <c r="F103">
-        <v>1.413708943644842</v>
+        <v>0.06379477637437284</v>
       </c>
       <c r="G103">
-        <v>0.9796135945139743</v>
+        <v>0.008319513145048673</v>
       </c>
       <c r="H103">
-        <v>-2.80694361484074</v>
+        <v>0.04330747024834353</v>
       </c>
       <c r="I103">
-        <v>2.734693613491371</v>
+        <v>0.2933783984394585</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -5022,28 +5019,28 @@
         <v>43</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C104" t="s">
         <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E104">
-        <v>0.009378608243243273</v>
+        <v>-0.06573229303669535</v>
       </c>
       <c r="F104">
-        <v>0.006877683488183651</v>
+        <v>0.05306611501194726</v>
       </c>
       <c r="G104">
-        <v>0.1726843790968118</v>
+        <v>0.2154615309963002</v>
       </c>
       <c r="H104">
-        <v>-0.004101403690662492</v>
+        <v>-0.1697399672595723</v>
       </c>
       <c r="I104">
-        <v>0.02285862017714904</v>
+        <v>0.03827538118618158</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -5051,7 +5048,7 @@
         <v>43</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C105" t="s">
         <v>44</v>
@@ -5060,19 +5057,19 @@
         <v>78</v>
       </c>
       <c r="E105">
-        <v>1.834039585774474</v>
+        <v>54461.31136820443</v>
       </c>
       <c r="F105">
-        <v>1.668610007067105</v>
+        <v>46196.10542983269</v>
       </c>
       <c r="G105">
-        <v>0.271706068515189</v>
+        <v>0.238431767823327</v>
       </c>
       <c r="H105">
-        <v>-1.436375932320176</v>
+        <v>-36081.39150028288</v>
       </c>
       <c r="I105">
-        <v>5.104455103869124</v>
+        <v>145004.0142366917</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -5080,7 +5077,7 @@
         <v>43</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C106" t="s">
         <v>44</v>
@@ -5089,19 +5086,19 @@
         <v>79</v>
       </c>
       <c r="E106">
-        <v>0.9563034367576586</v>
+        <v>322230.2455242127</v>
       </c>
       <c r="F106">
-        <v>1.683439340390516</v>
+        <v>259974.3285227526</v>
       </c>
       <c r="G106">
-        <v>0.5699906436877451</v>
+        <v>0.2151716849245486</v>
       </c>
       <c r="H106">
-        <v>-2.343177040565618</v>
+        <v>-187310.0752853666</v>
       </c>
       <c r="I106">
-        <v>4.255783914080935</v>
+        <v>831770.5663337919</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -5109,7 +5106,7 @@
         <v>43</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C107" t="s">
         <v>44</v>
@@ -5118,19 +5115,19 @@
         <v>80</v>
       </c>
       <c r="E107">
-        <v>-0.396987877607839</v>
+        <v>-111212.3558547459</v>
       </c>
       <c r="F107">
-        <v>1.67032445208994</v>
+        <v>80606.41732515785</v>
       </c>
       <c r="G107">
-        <v>0.8121361874246488</v>
+        <v>0.1676802486033757</v>
       </c>
       <c r="H107">
-        <v>-3.67076364620072</v>
+        <v>-269198.0307348607</v>
       </c>
       <c r="I107">
-        <v>2.876787890985042</v>
+        <v>46773.31902536888</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -5138,7 +5135,7 @@
         <v>43</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C108" t="s">
         <v>44</v>
@@ -5147,19 +5144,19 @@
         <v>81</v>
       </c>
       <c r="E108">
-        <v>-0.2579537358954739</v>
+        <v>-82946.32405851359</v>
       </c>
       <c r="F108">
-        <v>1.667554442272197</v>
+        <v>61996.82599703559</v>
       </c>
       <c r="G108">
-        <v>0.8770658372320717</v>
+        <v>0.1809249850324981</v>
       </c>
       <c r="H108">
-        <v>-3.526300385008756</v>
+        <v>-204457.8701684999</v>
       </c>
       <c r="I108">
-        <v>3.010392913217808</v>
+        <v>38565.22205147268</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -5167,7 +5164,7 @@
         <v>43</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C109" t="s">
         <v>44</v>
@@ -5176,19 +5173,19 @@
         <v>82</v>
       </c>
       <c r="E109">
-        <v>-0.218163495215229</v>
+        <v>75426.38124897741</v>
       </c>
       <c r="F109">
-        <v>1.670059999846299</v>
+        <v>98538.06625395626</v>
       </c>
       <c r="G109">
-        <v>0.8960663243504474</v>
+        <v>0.4440011013923008</v>
       </c>
       <c r="H109">
-        <v>-3.491420946934944</v>
+        <v>-117704.6797149986</v>
       </c>
       <c r="I109">
-        <v>3.055093956504486</v>
+        <v>268557.4422129533</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -5196,28 +5193,28 @@
         <v>43</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C110" t="s">
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E110">
-        <v>-0.006453378877913932</v>
+        <v>0.7312891767087988</v>
       </c>
       <c r="F110">
-        <v>0.08050824744525539</v>
+        <v>0.01869705076124312</v>
       </c>
       <c r="G110">
-        <v>0.9361116058318676</v>
+        <v>0</v>
       </c>
       <c r="H110">
-        <v>-0.1642466443290533</v>
+        <v>0.6946436305996451</v>
       </c>
       <c r="I110">
-        <v>0.1513398865732254</v>
+        <v>0.7679347228179525</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -5225,28 +5222,28 @@
         <v>43</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C111" t="s">
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E111">
-        <v>5.548848040928378</v>
+        <v>-0.3060314209381971</v>
       </c>
       <c r="F111">
-        <v>129.9089125423122</v>
+        <v>0.03364005833136529</v>
       </c>
       <c r="G111">
-        <v>0.9659300179382395</v>
+        <v>9.266311988506692E-20</v>
       </c>
       <c r="H111">
-        <v>-249.0679418127672</v>
+        <v>-0.3719647237054997</v>
       </c>
       <c r="I111">
-        <v>260.165637894624</v>
+        <v>-0.2400981181708946</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -5254,28 +5251,28 @@
         <v>43</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C112" t="s">
         <v>44</v>
       </c>
       <c r="D112" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E112">
-        <v>22.77214379883186</v>
+        <v>0.0289140866718292</v>
       </c>
       <c r="F112">
-        <v>129.9813568994298</v>
+        <v>0.04085195240043281</v>
       </c>
       <c r="G112">
-        <v>0.8609260504382172</v>
+        <v>0.4790835332387944</v>
       </c>
       <c r="H112">
-        <v>-231.9866343856973</v>
+        <v>-0.05115426873116371</v>
       </c>
       <c r="I112">
-        <v>277.5309219833611</v>
+        <v>0.1089824420748221</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5283,28 +5280,28 @@
         <v>43</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
         <v>44</v>
       </c>
       <c r="D113" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E113">
-        <v>-3.642197729060435</v>
+        <v>0.1135401015306262</v>
       </c>
       <c r="F113">
-        <v>129.9059549680125</v>
+        <v>0.03063946473615572</v>
       </c>
       <c r="G113">
-        <v>0.9776324907709218</v>
+        <v>0.0002108229882860476</v>
       </c>
       <c r="H113">
-        <v>-258.2531908436471</v>
+        <v>0.05348785414217599</v>
       </c>
       <c r="I113">
-        <v>250.9687953855262</v>
+        <v>0.1735923489190765</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5312,28 +5309,28 @@
         <v>43</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C114" t="s">
         <v>44</v>
       </c>
       <c r="D114" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E114">
-        <v>-1.598338125900563</v>
+        <v>-0.009217004040934961</v>
       </c>
       <c r="F114">
-        <v>129.906280298428</v>
+        <v>0.0226682464691812</v>
       </c>
       <c r="G114">
-        <v>0.990183252609351</v>
+        <v>0.6842987178372146</v>
       </c>
       <c r="H114">
-        <v>-256.2099688763847</v>
+        <v>-0.05364595071320735</v>
       </c>
       <c r="I114">
-        <v>253.0132926245835</v>
+        <v>0.03521194263133742</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5341,28 +5338,28 @@
         <v>43</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C115" t="s">
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E115">
-        <v>-1.179547903723482</v>
+        <v>0.6282862353773228</v>
       </c>
       <c r="F115">
-        <v>129.9079813767329</v>
+        <v>0.01547403300823683</v>
       </c>
       <c r="G115">
-        <v>0.9927554094879457</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>-255.7945127064201</v>
+        <v>0.5979576879855946</v>
       </c>
       <c r="I115">
-        <v>253.4354168989731</v>
+        <v>0.6586147827690509</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5370,28 +5367,28 @@
         <v>43</v>
       </c>
       <c r="B116" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C116" t="s">
         <v>44</v>
       </c>
       <c r="D116" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E116">
-        <v>0.5201174763123944</v>
+        <v>-0.2491398449881743</v>
       </c>
       <c r="F116">
-        <v>1.038456736342283</v>
+        <v>0.02721130397629147</v>
       </c>
       <c r="G116">
-        <v>0.6164723424371549</v>
+        <v>5.39824602912469E-20</v>
       </c>
       <c r="H116">
-        <v>-1.515220326421486</v>
+        <v>-0.3024730207540771</v>
       </c>
       <c r="I116">
-        <v>2.555455279046275</v>
+        <v>-0.1958066692222714</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5399,28 +5396,28 @@
         <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C117" t="s">
         <v>44</v>
       </c>
       <c r="D117" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E117">
-        <v>1.880680533592171</v>
+        <v>0.05212187769587537</v>
       </c>
       <c r="F117">
-        <v>1.667511256435842</v>
+        <v>0.03371707036422305</v>
       </c>
       <c r="G117">
-        <v>0.2593888552451064</v>
+        <v>0.1221383303942269</v>
       </c>
       <c r="H117">
-        <v>-1.387581472837214</v>
+        <v>-0.01396236588220461</v>
       </c>
       <c r="I117">
-        <v>5.148942540021557</v>
+        <v>0.1182061212739553</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5428,28 +5425,28 @@
         <v>43</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C118" t="s">
         <v>44</v>
       </c>
       <c r="D118" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E118">
-        <v>0.3661140284979758</v>
+        <v>0.08715491754162295</v>
       </c>
       <c r="F118">
-        <v>1.672261788160053</v>
+        <v>0.0257629602944177</v>
       </c>
       <c r="G118">
-        <v>0.8267018957246043</v>
+        <v>0.0007171056176498318</v>
       </c>
       <c r="H118">
-        <v>-2.911458849018278</v>
+        <v>0.03666044322942884</v>
       </c>
       <c r="I118">
-        <v>3.64368690601423</v>
+        <v>0.1376493918538171</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5457,28 +5454,28 @@
         <v>43</v>
       </c>
       <c r="B119" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C119" t="s">
         <v>44</v>
       </c>
       <c r="D119" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E119">
-        <v>-0.2455405286189433</v>
+        <v>-0.01293267662845301</v>
       </c>
       <c r="F119">
-        <v>1.668750362887774</v>
+        <v>0.01857342151205536</v>
       </c>
       <c r="G119">
-        <v>0.8830212341301098</v>
+        <v>0.4862408643127261</v>
       </c>
       <c r="H119">
-        <v>-3.516231139067127</v>
+        <v>-0.049335913861763</v>
       </c>
       <c r="I119">
-        <v>3.02515008182924</v>
+        <v>0.02347056060485698</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5486,28 +5483,28 @@
         <v>43</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C120" t="s">
         <v>44</v>
       </c>
       <c r="D120" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E120">
-        <v>-0.2070597116992076</v>
+        <v>0.1021213171234772</v>
       </c>
       <c r="F120">
-        <v>1.667034818298269</v>
+        <v>0.004672220841444825</v>
       </c>
       <c r="G120">
-        <v>0.901150279023283</v>
+        <v>6.65023636144392E-106</v>
       </c>
       <c r="H120">
-        <v>-3.474387916538087</v>
+        <v>0.09296393254642792</v>
       </c>
       <c r="I120">
-        <v>3.060268493139672</v>
+        <v>0.1112787017005265</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5515,28 +5512,28 @@
         <v>43</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C121" t="s">
         <v>44</v>
       </c>
       <c r="D121" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E121">
-        <v>-0.03871677735530765</v>
+        <v>-0.0667171953478107</v>
       </c>
       <c r="F121">
-        <v>1.667854757867423</v>
+        <v>0.007118375359488398</v>
       </c>
       <c r="G121">
-        <v>0.9814799552726379</v>
+        <v>7.081352660162438E-21</v>
       </c>
       <c r="H121">
-        <v>-3.30765203421923</v>
+        <v>-0.08066895468084533</v>
       </c>
       <c r="I121">
-        <v>3.230218479508615</v>
+        <v>-0.05276543601477608</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -5544,28 +5541,28 @@
         <v>43</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C122" t="s">
         <v>44</v>
       </c>
       <c r="D122" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E122">
-        <v>-0.0657322930366977</v>
+        <v>0.008296430513341497</v>
       </c>
       <c r="F122">
-        <v>0.053066115011947</v>
+        <v>0.01024097915338189</v>
       </c>
       <c r="G122">
-        <v>0.2154615309962814</v>
+        <v>0.4178707346070463</v>
       </c>
       <c r="H122">
-        <v>-0.1697399672595741</v>
+        <v>-0.01177551979371251</v>
       </c>
       <c r="I122">
-        <v>0.03827538118617871</v>
+        <v>0.0283683808203955</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -5573,28 +5570,28 @@
         <v>43</v>
       </c>
       <c r="B123" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C123" t="s">
         <v>44</v>
       </c>
       <c r="D123" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E123">
-        <v>-74828.48469726639</v>
+        <v>-0.005133096569430335</v>
       </c>
       <c r="F123">
-        <v>2889994.284240374</v>
+        <v>0.008683725324725663</v>
       </c>
       <c r="G123">
-        <v>0.9793432732474506</v>
+        <v>0.5544421144394025</v>
       </c>
       <c r="H123">
-        <v>-5739113.197335011</v>
+        <v>-0.02215288545753102</v>
       </c>
       <c r="I123">
-        <v>5589456.227940478</v>
+        <v>0.01188669231867035</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -5602,28 +5599,28 @@
         <v>43</v>
       </c>
       <c r="B124" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C124" t="s">
         <v>44</v>
       </c>
       <c r="D124" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E124">
-        <v>451520.0415896832</v>
+        <v>0.01301870752067508</v>
       </c>
       <c r="F124">
-        <v>2898318.695782662</v>
+        <v>0.005645463503713187</v>
       </c>
       <c r="G124">
-        <v>0.8762010085926516</v>
+        <v>0.02110797317987164</v>
       </c>
       <c r="H124">
-        <v>-5229080.217863437</v>
+        <v>0.001953802377361926</v>
       </c>
       <c r="I124">
-        <v>6132120.301042803</v>
+        <v>0.02408361266398823</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -5631,28 +5628,28 @@
         <v>43</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C125" t="s">
         <v>44</v>
       </c>
       <c r="D125" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E125">
-        <v>18077.44021072563</v>
+        <v>0.2969101987986706</v>
       </c>
       <c r="F125">
-        <v>2888414.954359802</v>
+        <v>0.02819616321773354</v>
       </c>
       <c r="G125">
-        <v>0.9950063905261524</v>
+        <v>6.272567194331018E-26</v>
       </c>
       <c r="H125">
-        <v>-5643111.842741391</v>
+        <v>0.2416467343896999</v>
       </c>
       <c r="I125">
-        <v>5679266.723162841</v>
+        <v>0.3521736632076414</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -5660,28 +5657,28 @@
         <v>43</v>
       </c>
       <c r="B126" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C126" t="s">
         <v>44</v>
       </c>
       <c r="D126" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E126">
-        <v>129289.7960654707</v>
+        <v>-0.0728256406868454</v>
       </c>
       <c r="F126">
-        <v>2890081.668964487</v>
+        <v>0.04428851504153577</v>
       </c>
       <c r="G126">
-        <v>0.9643179860855474</v>
+        <v>0.1001047612892904</v>
       </c>
       <c r="H126">
-        <v>-5535166.187484335</v>
+        <v>-0.1596295350970159</v>
       </c>
       <c r="I126">
-        <v>5793745.779615276</v>
+        <v>0.01397825372332516</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -5689,28 +5686,28 @@
         <v>43</v>
       </c>
       <c r="B127" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C127" t="s">
         <v>44</v>
       </c>
       <c r="D127" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E127">
-        <v>46343.47200695744</v>
+        <v>0.1980914822970442</v>
       </c>
       <c r="F127">
-        <v>2888729.046101908</v>
+        <v>0.06110447414767291</v>
       </c>
       <c r="G127">
-        <v>0.9872001997619876</v>
+        <v>0.001187569006545004</v>
       </c>
       <c r="H127">
-        <v>-5615461.419447528</v>
+        <v>0.07832891367334649</v>
       </c>
       <c r="I127">
-        <v>5708148.363461442</v>
+        <v>0.3178540509207419</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -5718,28 +5715,28 @@
         <v>43</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C128" t="s">
         <v>44</v>
       </c>
       <c r="D128" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E128">
-        <v>75426.38124897706</v>
+        <v>-0.09873268966948789</v>
       </c>
       <c r="F128">
-        <v>98538.06625395556</v>
+        <v>0.04407227921459313</v>
       </c>
       <c r="G128">
-        <v>0.4440011013922995</v>
+        <v>0.02507504155077243</v>
       </c>
       <c r="H128">
-        <v>-117704.6797149975</v>
+        <v>-0.1851127696466837</v>
       </c>
       <c r="I128">
-        <v>268557.4422129517</v>
+        <v>-0.01235260969229213</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -5747,28 +5744,28 @@
         <v>43</v>
       </c>
       <c r="B129" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C129" t="s">
         <v>44</v>
       </c>
       <c r="D129" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E129">
-        <v>0.6600639986799826</v>
+        <v>0.02104665234127706</v>
       </c>
       <c r="F129">
-        <v>0.6908481881082845</v>
+        <v>0.03283771863448952</v>
       </c>
       <c r="G129">
-        <v>0.3393552297023528</v>
+        <v>0.5215686911247386</v>
       </c>
       <c r="H129">
-        <v>-0.6939735687970077</v>
+        <v>-0.0433140935167822</v>
       </c>
       <c r="I129">
-        <v>2.014101566156973</v>
+        <v>0.08540739819933632</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -5776,28 +5773,28 @@
         <v>43</v>
       </c>
       <c r="B130" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C130" t="s">
         <v>44</v>
       </c>
       <c r="D130" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E130">
-        <v>-0.2348062429093807</v>
+        <v>0.1450025513517406</v>
       </c>
       <c r="F130">
-        <v>0.6912162504008155</v>
+        <v>0.02425293875649443</v>
       </c>
       <c r="G130">
-        <v>0.7340823716903562</v>
+        <v>2.248396118571845E-09</v>
       </c>
       <c r="H130">
-        <v>-1.589565199223799</v>
+        <v>0.09746766486975586</v>
       </c>
       <c r="I130">
-        <v>1.119952713405037</v>
+        <v>0.1925374378337253</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -5805,28 +5802,28 @@
         <v>43</v>
       </c>
       <c r="B131" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C131" t="s">
         <v>44</v>
       </c>
       <c r="D131" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E131">
-        <v>0.1001392647006459</v>
+        <v>-0.04798937248878819</v>
       </c>
       <c r="F131">
-        <v>0.6915305142099607</v>
+        <v>0.03924824616470513</v>
       </c>
       <c r="G131">
-        <v>0.8848623355606682</v>
+        <v>0.2214378101971697</v>
       </c>
       <c r="H131">
-        <v>-1.255235637361341</v>
+        <v>-0.1249145214279725</v>
       </c>
       <c r="I131">
-        <v>1.455514166762633</v>
+        <v>0.02893577645039618</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -5834,28 +5831,28 @@
         <v>43</v>
       </c>
       <c r="B132" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C132" t="s">
         <v>44</v>
       </c>
       <c r="D132" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E132">
-        <v>0.07122517802881691</v>
+        <v>0.0943960395446837</v>
       </c>
       <c r="F132">
-        <v>0.6906924783436718</v>
+        <v>0.0588241716022229</v>
       </c>
       <c r="G132">
-        <v>0.9178666177278576</v>
+        <v>0.1085565055977071</v>
       </c>
       <c r="H132">
-        <v>-1.282507203917491</v>
+        <v>-0.020897218216077</v>
       </c>
       <c r="I132">
-        <v>1.424957559975125</v>
+        <v>0.2096892973054444</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -5863,28 +5860,28 @@
         <v>43</v>
       </c>
       <c r="B133" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C133" t="s">
         <v>44</v>
       </c>
       <c r="D133" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E133">
-        <v>0.1847652795594426</v>
+        <v>-0.09091884925241235</v>
       </c>
       <c r="F133">
-        <v>0.6911050206378032</v>
+        <v>0.03335981908070813</v>
       </c>
       <c r="G133">
-        <v>0.7892015283497416</v>
+        <v>0.006422363770541468</v>
       </c>
       <c r="H133">
-        <v>-1.169775670425462</v>
+        <v>-0.1563028931813724</v>
       </c>
       <c r="I133">
-        <v>1.539306229544348</v>
+        <v>-0.02553480532345233</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -5892,28 +5889,28 @@
         <v>43</v>
       </c>
       <c r="B134" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C134" t="s">
         <v>44</v>
       </c>
       <c r="D134" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E134">
-        <v>-0.00921700404093569</v>
+        <v>0.03137299694702981</v>
       </c>
       <c r="F134">
-        <v>0.0226682464691811</v>
+        <v>0.02834797341302454</v>
       </c>
       <c r="G134">
-        <v>0.68429871783719</v>
+        <v>0.2684191581930715</v>
       </c>
       <c r="H134">
-        <v>-0.05364595071320789</v>
+        <v>-0.02418800997719728</v>
       </c>
       <c r="I134">
-        <v>0.03521194263133652</v>
+        <v>0.08693400387125691</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -5921,7 +5918,7 @@
         <v>43</v>
       </c>
       <c r="B135" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C135" t="s">
         <v>44</v>
@@ -5930,19 +5927,19 @@
         <v>78</v>
       </c>
       <c r="E135">
-        <v>0.5215207066885346</v>
+        <v>-0.07724690991622989</v>
       </c>
       <c r="F135">
-        <v>0.1676983892720567</v>
+        <v>0.004056530228522022</v>
       </c>
       <c r="G135">
-        <v>0.001871677481952087</v>
+        <v>7.566626800084343E-81</v>
       </c>
       <c r="H135">
-        <v>0.1928379034499252</v>
+        <v>-0.08519756306633108</v>
       </c>
       <c r="I135">
-        <v>0.8502035099271439</v>
+        <v>-0.06929625676612869</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -5950,7 +5947,7 @@
         <v>43</v>
       </c>
       <c r="B136" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C136" t="s">
         <v>44</v>
@@ -5959,19 +5956,19 @@
         <v>79</v>
       </c>
       <c r="E136">
-        <v>-0.142374316299386</v>
+        <v>0.04663179666665138</v>
       </c>
       <c r="F136">
-        <v>0.1686811485576504</v>
+        <v>0.005537359260355919</v>
       </c>
       <c r="G136">
-        <v>0.39864480237002</v>
+        <v>3.723104858290448E-17</v>
       </c>
       <c r="H136">
-        <v>-0.4729832923432312</v>
+        <v>0.03577877194689442</v>
       </c>
       <c r="I136">
-        <v>0.1882346597444592</v>
+        <v>0.05748482138640833</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -5979,7 +5976,7 @@
         <v>43</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C137" t="s">
         <v>44</v>
@@ -5988,19 +5985,19 @@
         <v>80</v>
       </c>
       <c r="E137">
-        <v>0.1588874063846637</v>
+        <v>0.00474031964924489</v>
       </c>
       <c r="F137">
-        <v>0.1696082348838405</v>
+        <v>0.008534154711803191</v>
       </c>
       <c r="G137">
-        <v>0.3488662625055297</v>
+        <v>0.5785850247248983</v>
       </c>
       <c r="H137">
-        <v>-0.1735386254690736</v>
+        <v>-0.01198631622438217</v>
       </c>
       <c r="I137">
-        <v>0.4913134382384011</v>
+        <v>0.02146695552287195</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -6008,7 +6005,7 @@
         <v>43</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C138" t="s">
         <v>44</v>
@@ -6017,19 +6014,19 @@
         <v>81</v>
       </c>
       <c r="E138">
-        <v>0.1067655286887886</v>
+        <v>-0.004286761401380142</v>
       </c>
       <c r="F138">
-        <v>0.167218366071189</v>
+        <v>0.004722521030661635</v>
       </c>
       <c r="G138">
-        <v>0.5231614780044167</v>
+        <v>0.3640223013111951</v>
       </c>
       <c r="H138">
-        <v>-0.2209764463643763</v>
+        <v>-0.01354273253770992</v>
       </c>
       <c r="I138">
-        <v>0.4345075037419535</v>
+        <v>0.004969209734949639</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -6037,7 +6034,7 @@
         <v>43</v>
       </c>
       <c r="B139" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C139" t="s">
         <v>44</v>
@@ -6046,19 +6043,19 @@
         <v>82</v>
       </c>
       <c r="E139">
-        <v>0.1939204462304111</v>
+        <v>0.008020413755803719</v>
       </c>
       <c r="F139">
-        <v>0.1685389999680956</v>
+        <v>0.004349980177762477</v>
       </c>
       <c r="G139">
-        <v>0.2498981203159278</v>
+        <v>0.06521496378610396</v>
       </c>
       <c r="H139">
-        <v>-0.1364099236974536</v>
+        <v>-0.0005053907260738795</v>
       </c>
       <c r="I139">
-        <v>0.5242508161582758</v>
+        <v>0.01654621823768132</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -6066,28 +6063,28 @@
         <v>43</v>
       </c>
       <c r="B140" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C140" t="s">
         <v>44</v>
       </c>
       <c r="D140" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E140">
-        <v>-0.01293267662845365</v>
+        <v>1298.852711266856</v>
       </c>
       <c r="F140">
-        <v>0.01857342151205529</v>
+        <v>539.0412807454333</v>
       </c>
       <c r="G140">
-        <v>0.4862408643127029</v>
+        <v>0.01597173689684979</v>
       </c>
       <c r="H140">
-        <v>-0.0493359138617635</v>
+        <v>242.3512148254624</v>
       </c>
       <c r="I140">
-        <v>0.0234705606048562</v>
+        <v>2355.354207708249</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -6095,28 +6092,28 @@
         <v>43</v>
       </c>
       <c r="B141" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C141" t="s">
         <v>44</v>
       </c>
       <c r="D141" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E141">
-        <v>0.1001875943698771</v>
+        <v>4566.525134071791</v>
       </c>
       <c r="F141">
-        <v>0.202459677824482</v>
+        <v>3212.459409625553</v>
       </c>
       <c r="G141">
-        <v>0.6207045328798254</v>
+        <v>0.1551701800006193</v>
       </c>
       <c r="H141">
-        <v>-0.2966260824876903</v>
+        <v>-1729.779610591097</v>
       </c>
       <c r="I141">
-        <v>0.4970012712274445</v>
+        <v>10862.82987873468</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -6124,28 +6121,28 @@
         <v>43</v>
       </c>
       <c r="B142" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C142" t="s">
         <v>44</v>
       </c>
       <c r="D142" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E142">
-        <v>-0.06478347259421054</v>
+        <v>-339.8410341017711</v>
       </c>
       <c r="F142">
-        <v>0.2024850306138875</v>
+        <v>303.141193760284</v>
       </c>
       <c r="G142">
-        <v>0.7490122725591715</v>
+        <v>0.2622601228328064</v>
       </c>
       <c r="H142">
-        <v>-0.4616468400059203</v>
+        <v>-933.9868561024059</v>
       </c>
       <c r="I142">
-        <v>0.3320798948174993</v>
+        <v>254.3047878988637</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -6153,28 +6150,28 @@
         <v>43</v>
       </c>
       <c r="B143" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C143" t="s">
         <v>44</v>
       </c>
       <c r="D143" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E143">
-        <v>0.01023015326694155</v>
+        <v>175.9465799854406</v>
       </c>
       <c r="F143">
-        <v>0.2026185626144762</v>
+        <v>335.2754492587764</v>
       </c>
       <c r="G143">
-        <v>0.9597321460321661</v>
+        <v>0.5997346232085194</v>
       </c>
       <c r="H143">
-        <v>-0.3868949320567058</v>
+        <v>-481.1812254622476</v>
       </c>
       <c r="I143">
-        <v>0.4073552385905889</v>
+        <v>833.0743854331288</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -6182,782 +6179,28 @@
         <v>43</v>
       </c>
       <c r="B144" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C144" t="s">
         <v>44</v>
       </c>
       <c r="D144" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E144">
-        <v>0.001933722753600135</v>
+        <v>-256.0708611125942</v>
       </c>
       <c r="F144">
-        <v>0.2024303247788858</v>
+        <v>600.411240006836</v>
       </c>
       <c r="G144">
-        <v>0.9923782957568649</v>
+        <v>0.6697490479046113</v>
       </c>
       <c r="H144">
-        <v>-0.3948224231917621</v>
+        <v>-1432.855267439027</v>
       </c>
       <c r="I144">
-        <v>0.3986898686989624</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9">
-      <c r="A145" t="s">
-        <v>43</v>
-      </c>
-      <c r="B145" t="s">
-        <v>19</v>
-      </c>
-      <c r="C145" t="s">
-        <v>44</v>
-      </c>
-      <c r="D145" t="s">
-        <v>82</v>
-      </c>
-      <c r="E145">
-        <v>-0.003199373815830464</v>
-      </c>
-      <c r="F145">
-        <v>0.2025568640052744</v>
-      </c>
-      <c r="G145">
-        <v>0.9873979840388695</v>
-      </c>
-      <c r="H145">
-        <v>-0.4002035320875459</v>
-      </c>
-      <c r="I145">
-        <v>0.393804784455885</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9">
-      <c r="A146" t="s">
-        <v>43</v>
-      </c>
-      <c r="B146" t="s">
-        <v>19</v>
-      </c>
-      <c r="C146" t="s">
-        <v>44</v>
-      </c>
-      <c r="D146" t="s">
-        <v>83</v>
-      </c>
-      <c r="E146">
-        <v>0.01301870752067498</v>
-      </c>
-      <c r="F146">
-        <v>0.005645463503713164</v>
-      </c>
-      <c r="G146">
-        <v>0.02110797317987211</v>
-      </c>
-      <c r="H146">
-        <v>0.001953802377361868</v>
-      </c>
-      <c r="I146">
-        <v>0.02408361266398808</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9">
-      <c r="A147" t="s">
-        <v>43</v>
-      </c>
-      <c r="B147" t="s">
-        <v>20</v>
-      </c>
-      <c r="C147" t="s">
-        <v>44</v>
-      </c>
-      <c r="D147" t="s">
-        <v>78</v>
-      </c>
-      <c r="E147">
-        <v>-0.01152284281744822</v>
-      </c>
-      <c r="F147">
-        <v>4.042172075885884</v>
-      </c>
-      <c r="G147">
-        <v>0.9977255085246146</v>
-      </c>
-      <c r="H147">
-        <v>-7.934034530867287</v>
-      </c>
-      <c r="I147">
-        <v>7.910988845232391</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9">
-      <c r="A148" t="s">
-        <v>43</v>
-      </c>
-      <c r="B148" t="s">
-        <v>20</v>
-      </c>
-      <c r="C148" t="s">
-        <v>44</v>
-      </c>
-      <c r="D148" t="s">
-        <v>79</v>
-      </c>
-      <c r="E148">
-        <v>0.2356074009292737</v>
-      </c>
-      <c r="F148">
-        <v>4.042245906364694</v>
-      </c>
-      <c r="G148">
-        <v>0.9535206108454313</v>
-      </c>
-      <c r="H148">
-        <v>-7.687048992199994</v>
-      </c>
-      <c r="I148">
-        <v>8.158263794058541</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9">
-      <c r="A149" t="s">
-        <v>43</v>
-      </c>
-      <c r="B149" t="s">
-        <v>20</v>
-      </c>
-      <c r="C149" t="s">
-        <v>44</v>
-      </c>
-      <c r="D149" t="s">
-        <v>80</v>
-      </c>
-      <c r="E149">
-        <v>0.5065245239131636</v>
-      </c>
-      <c r="F149">
-        <v>4.042458594568733</v>
-      </c>
-      <c r="G149">
-        <v>0.9002851783760809</v>
-      </c>
-      <c r="H149">
-        <v>-7.416548730435957</v>
-      </c>
-      <c r="I149">
-        <v>8.429597778262284</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9">
-      <c r="A150" t="s">
-        <v>43</v>
-      </c>
-      <c r="B150" t="s">
-        <v>20</v>
-      </c>
-      <c r="C150" t="s">
-        <v>44</v>
-      </c>
-      <c r="D150" t="s">
-        <v>81</v>
-      </c>
-      <c r="E150">
-        <v>0.3084330416161181</v>
-      </c>
-      <c r="F150">
-        <v>4.042105982248443</v>
-      </c>
-      <c r="G150">
-        <v>0.9391764195511929</v>
-      </c>
-      <c r="H150">
-        <v>-7.613949105284728</v>
-      </c>
-      <c r="I150">
-        <v>8.230815188516965</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9">
-      <c r="A151" t="s">
-        <v>43</v>
-      </c>
-      <c r="B151" t="s">
-        <v>20</v>
-      </c>
-      <c r="C151" t="s">
-        <v>44</v>
-      </c>
-      <c r="D151" t="s">
-        <v>82</v>
-      </c>
-      <c r="E151">
-        <v>0.2097003519466311</v>
-      </c>
-      <c r="F151">
-        <v>4.042252536274446</v>
-      </c>
-      <c r="G151">
-        <v>0.9586266187107996</v>
-      </c>
-      <c r="H151">
-        <v>-7.712969035566971</v>
-      </c>
-      <c r="I151">
-        <v>8.132369739460232</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9">
-      <c r="A152" t="s">
-        <v>43</v>
-      </c>
-      <c r="B152" t="s">
-        <v>20</v>
-      </c>
-      <c r="C152" t="s">
-        <v>44</v>
-      </c>
-      <c r="D152" t="s">
-        <v>83</v>
-      </c>
-      <c r="E152">
-        <v>0.02104665234127659</v>
-      </c>
-      <c r="F152">
-        <v>0.03283771863448939</v>
-      </c>
-      <c r="G152">
-        <v>0.5215686911247464</v>
-      </c>
-      <c r="H152">
-        <v>-0.04331409351678242</v>
-      </c>
-      <c r="I152">
-        <v>0.0854073981993356</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9">
-      <c r="A153" t="s">
-        <v>43</v>
-      </c>
-      <c r="B153" t="s">
-        <v>21</v>
-      </c>
-      <c r="C153" t="s">
-        <v>44</v>
-      </c>
-      <c r="D153" t="s">
-        <v>78</v>
-      </c>
-      <c r="E153">
-        <v>-0.03137299694702543</v>
-      </c>
-      <c r="F153">
-        <v>0.8947943967751777</v>
-      </c>
-      <c r="G153">
-        <v>0.9720305556335496</v>
-      </c>
-      <c r="H153">
-        <v>-1.785137788194617</v>
-      </c>
-      <c r="I153">
-        <v>1.722391794300566</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9">
-      <c r="A154" t="s">
-        <v>43</v>
-      </c>
-      <c r="B154" t="s">
-        <v>21</v>
-      </c>
-      <c r="C154" t="s">
-        <v>44</v>
-      </c>
-      <c r="D154" t="s">
-        <v>79</v>
-      </c>
-      <c r="E154">
-        <v>0.1283861758099778</v>
-      </c>
-      <c r="F154">
-        <v>0.8950949954291174</v>
-      </c>
-      <c r="G154">
-        <v>0.8859482086542759</v>
-      </c>
-      <c r="H154">
-        <v>-1.625967777973137</v>
-      </c>
-      <c r="I154">
-        <v>1.882740129593092</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9">
-      <c r="A155" t="s">
-        <v>43</v>
-      </c>
-      <c r="B155" t="s">
-        <v>21</v>
-      </c>
-      <c r="C155" t="s">
-        <v>44</v>
-      </c>
-      <c r="D155" t="s">
-        <v>80</v>
-      </c>
-      <c r="E155">
-        <v>0.2707715878434497</v>
-      </c>
-      <c r="F155">
-        <v>0.896147938117747</v>
-      </c>
-      <c r="G155">
-        <v>0.7625373026612176</v>
-      </c>
-      <c r="H155">
-        <v>-1.485646095687163</v>
-      </c>
-      <c r="I155">
-        <v>2.027189271374063</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9">
-      <c r="A156" t="s">
-        <v>43</v>
-      </c>
-      <c r="B156" t="s">
-        <v>21</v>
-      </c>
-      <c r="C156" t="s">
-        <v>44</v>
-      </c>
-      <c r="D156" t="s">
-        <v>81</v>
-      </c>
-      <c r="E156">
-        <v>0.1763755482987656</v>
-      </c>
-      <c r="F156">
-        <v>0.8945844214120052</v>
-      </c>
-      <c r="G156">
-        <v>0.8437029580653098</v>
-      </c>
-      <c r="H156">
-        <v>-1.576977698799367</v>
-      </c>
-      <c r="I156">
-        <v>1.929728795396898</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9">
-      <c r="A157" t="s">
-        <v>43</v>
-      </c>
-      <c r="B157" t="s">
-        <v>21</v>
-      </c>
-      <c r="C157" t="s">
-        <v>44</v>
-      </c>
-      <c r="D157" t="s">
-        <v>82</v>
-      </c>
-      <c r="E157">
-        <v>0.0854566990463536</v>
-      </c>
-      <c r="F157">
-        <v>0.8949035178291247</v>
-      </c>
-      <c r="G157">
-        <v>0.9239235363452356</v>
-      </c>
-      <c r="H157">
-        <v>-1.668521965536929</v>
-      </c>
-      <c r="I157">
-        <v>1.839435363629636</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9">
-      <c r="A158" t="s">
-        <v>43</v>
-      </c>
-      <c r="B158" t="s">
-        <v>21</v>
-      </c>
-      <c r="C158" t="s">
-        <v>44</v>
-      </c>
-      <c r="D158" t="s">
-        <v>83</v>
-      </c>
-      <c r="E158">
-        <v>0.0313729969470296</v>
-      </c>
-      <c r="F158">
-        <v>0.02834797341302443</v>
-      </c>
-      <c r="G158">
-        <v>0.2684191581930727</v>
-      </c>
-      <c r="H158">
-        <v>-0.02418800997719728</v>
-      </c>
-      <c r="I158">
-        <v>0.08693400387125648</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9">
-      <c r="A159" t="s">
-        <v>43</v>
-      </c>
-      <c r="B159" t="s">
-        <v>22</v>
-      </c>
-      <c r="C159" t="s">
-        <v>44</v>
-      </c>
-      <c r="D159" t="s">
-        <v>78</v>
-      </c>
-      <c r="E159">
-        <v>-0.06998994715846395</v>
-      </c>
-      <c r="F159">
-        <v>0.04781731928592453</v>
-      </c>
-      <c r="G159">
-        <v>0.1432774394327555</v>
-      </c>
-      <c r="H159">
-        <v>-0.1637101707961286</v>
-      </c>
-      <c r="I159">
-        <v>0.02373027647920067</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9">
-      <c r="A160" t="s">
-        <v>43</v>
-      </c>
-      <c r="B160" t="s">
-        <v>22</v>
-      </c>
-      <c r="C160" t="s">
-        <v>44</v>
-      </c>
-      <c r="D160" t="s">
-        <v>79</v>
-      </c>
-      <c r="E160">
-        <v>0.03937483390888542</v>
-      </c>
-      <c r="F160">
-        <v>0.04788330303635917</v>
-      </c>
-      <c r="G160">
-        <v>0.4109014969605207</v>
-      </c>
-      <c r="H160">
-        <v>-0.05447471550319597</v>
-      </c>
-      <c r="I160">
-        <v>0.1332243833209668</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9">
-      <c r="A161" t="s">
-        <v>43</v>
-      </c>
-      <c r="B161" t="s">
-        <v>22</v>
-      </c>
-      <c r="C161" t="s">
-        <v>44</v>
-      </c>
-      <c r="D161" t="s">
-        <v>80</v>
-      </c>
-      <c r="E161">
-        <v>-0.00251664310852109</v>
-      </c>
-      <c r="F161">
-        <v>0.04835828364506665</v>
-      </c>
-      <c r="G161">
-        <v>0.9584955355165712</v>
-      </c>
-      <c r="H161">
-        <v>-0.09729713740702405</v>
-      </c>
-      <c r="I161">
-        <v>0.09226385118998186</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9">
-      <c r="A162" t="s">
-        <v>43</v>
-      </c>
-      <c r="B162" t="s">
-        <v>22</v>
-      </c>
-      <c r="C162" t="s">
-        <v>44</v>
-      </c>
-      <c r="D162" t="s">
-        <v>81</v>
-      </c>
-      <c r="E162">
-        <v>-0.007256962757765945</v>
-      </c>
-      <c r="F162">
-        <v>0.04770609123094292</v>
-      </c>
-      <c r="G162">
-        <v>0.8790937422921308</v>
-      </c>
-      <c r="H162">
-        <v>-0.1007591834135961</v>
-      </c>
-      <c r="I162">
-        <v>0.08624525789806427</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9">
-      <c r="A163" t="s">
-        <v>43</v>
-      </c>
-      <c r="B163" t="s">
-        <v>22</v>
-      </c>
-      <c r="C163" t="s">
-        <v>44</v>
-      </c>
-      <c r="D163" t="s">
-        <v>82</v>
-      </c>
-      <c r="E163">
-        <v>-0.01154372415914611</v>
-      </c>
-      <c r="F163">
-        <v>0.04781793282483224</v>
-      </c>
-      <c r="G163">
-        <v>0.809237411726385</v>
-      </c>
-      <c r="H163">
-        <v>-0.1052651503109729</v>
-      </c>
-      <c r="I163">
-        <v>0.08217770199268074</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9">
-      <c r="A164" t="s">
-        <v>43</v>
-      </c>
-      <c r="B164" t="s">
-        <v>22</v>
-      </c>
-      <c r="C164" t="s">
-        <v>44</v>
-      </c>
-      <c r="D164" t="s">
-        <v>83</v>
-      </c>
-      <c r="E164">
-        <v>0.008020413755803771</v>
-      </c>
-      <c r="F164">
-        <v>0.004349980177762456</v>
-      </c>
-      <c r="G164">
-        <v>0.06521496378610095</v>
-      </c>
-      <c r="H164">
-        <v>-0.0005053907260737858</v>
-      </c>
-      <c r="I164">
-        <v>0.01654621823768133</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9">
-      <c r="A165" t="s">
-        <v>43</v>
-      </c>
-      <c r="B165" t="s">
-        <v>23</v>
-      </c>
-      <c r="C165" t="s">
-        <v>44</v>
-      </c>
-      <c r="D165" t="s">
-        <v>78</v>
-      </c>
-      <c r="E165">
-        <v>1139.967562422161</v>
-      </c>
-      <c r="F165">
-        <v>27995.77243266509</v>
-      </c>
-      <c r="G165">
-        <v>0.9675196949425966</v>
-      </c>
-      <c r="H165">
-        <v>-53730.73812498071</v>
-      </c>
-      <c r="I165">
-        <v>56010.67324982503</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9">
-      <c r="A166" t="s">
-        <v>43</v>
-      </c>
-      <c r="B166" t="s">
-        <v>23</v>
-      </c>
-      <c r="C166" t="s">
-        <v>44</v>
-      </c>
-      <c r="D166" t="s">
-        <v>79</v>
-      </c>
-      <c r="E166">
-        <v>4725.410282916476</v>
-      </c>
-      <c r="F166">
-        <v>28190.04119985375</v>
-      </c>
-      <c r="G166">
-        <v>0.866876777749799</v>
-      </c>
-      <c r="H166">
-        <v>-50526.05519149717</v>
-      </c>
-      <c r="I166">
-        <v>59976.87575733012</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9">
-      <c r="A167" t="s">
-        <v>43</v>
-      </c>
-      <c r="B167" t="s">
-        <v>23</v>
-      </c>
-      <c r="C167" t="s">
-        <v>44</v>
-      </c>
-      <c r="D167" t="s">
-        <v>80</v>
-      </c>
-      <c r="E167">
-        <v>-180.9558852570743</v>
-      </c>
-      <c r="F167">
-        <v>27990.90303796541</v>
-      </c>
-      <c r="G167">
-        <v>0.9948418634035252</v>
-      </c>
-      <c r="H167">
-        <v>-55042.11773442207</v>
-      </c>
-      <c r="I167">
-        <v>54680.20596390792</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9">
-      <c r="A168" t="s">
-        <v>43</v>
-      </c>
-      <c r="B168" t="s">
-        <v>23</v>
-      </c>
-      <c r="C168" t="s">
-        <v>44</v>
-      </c>
-      <c r="D168" t="s">
-        <v>81</v>
-      </c>
-      <c r="E168">
-        <v>158.8851488446963</v>
-      </c>
-      <c r="F168">
-        <v>27989.90822586905</v>
-      </c>
-      <c r="G168">
-        <v>0.9954708202199559</v>
-      </c>
-      <c r="H168">
-        <v>-54700.32690444004</v>
-      </c>
-      <c r="I168">
-        <v>55018.09720212944</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9">
-      <c r="A169" t="s">
-        <v>43</v>
-      </c>
-      <c r="B169" t="s">
-        <v>23</v>
-      </c>
-      <c r="C169" t="s">
-        <v>44</v>
-      </c>
-      <c r="D169" t="s">
-        <v>82</v>
-      </c>
-      <c r="E169">
-        <v>334.8317288301375</v>
-      </c>
-      <c r="F169">
-        <v>27991.56258732806</v>
-      </c>
-      <c r="G169">
-        <v>0.9904560277724772</v>
-      </c>
-      <c r="H169">
-        <v>-54527.62281333166</v>
-      </c>
-      <c r="I169">
-        <v>55197.28627099194</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9">
-      <c r="A170" t="s">
-        <v>43</v>
-      </c>
-      <c r="B170" t="s">
-        <v>23</v>
-      </c>
-      <c r="C170" t="s">
-        <v>44</v>
-      </c>
-      <c r="D170" t="s">
-        <v>83</v>
-      </c>
-      <c r="E170">
-        <v>-256.0708611125975</v>
-      </c>
-      <c r="F170">
-        <v>600.4112400068296</v>
-      </c>
-      <c r="G170">
-        <v>0.669749047904604</v>
-      </c>
-      <c r="H170">
-        <v>-1432.855267439018</v>
-      </c>
-      <c r="I170">
-        <v>920.7135452138231</v>
+        <v>920.7135452138389</v>
       </c>
     </row>
   </sheetData>
@@ -6978,33 +6221,33 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s">
         <v>36</v>
       </c>
       <c r="C1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" t="s">
         <v>86</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>87</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>88</v>
-      </c>
-      <c r="F1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2">
         <v>592</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2">
         <v>49.35401878167119</v>
@@ -7013,7 +6256,7 @@
         <v>0.6952339291357703</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
